--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Python documents\Pere_kpoda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\père kpoda\env\Pere_kpoda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A29396-CAE9-45D9-AE3C-A86C413D8FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Graphique1" sheetId="9" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1029">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -813,9 +812,6 @@
     <t>L'intégration des technologies au sein de la relation banque-client:cas de la plateforme Omniplus à ECOBANK CI</t>
   </si>
   <si>
-    <t>Banque et assurane</t>
-  </si>
-  <si>
     <t>ECOBANK</t>
   </si>
   <si>
@@ -1011,9 +1007,6 @@
     <t>Analyse des effets de la covid-19 sur la performance des entreprises du secteur informel</t>
   </si>
   <si>
-    <t>économie du développement</t>
-  </si>
-  <si>
     <t>KONE Salif</t>
   </si>
   <si>
@@ -1128,9 +1121,6 @@
     <t>Dévoloppement financier et croissance économique: cas de la Côte d'Ivoire</t>
   </si>
   <si>
-    <t>Economie de développement</t>
-  </si>
-  <si>
     <t>AKA Brou</t>
   </si>
   <si>
@@ -1722,18 +1712,12 @@
     <t>SACOH Dorcas</t>
   </si>
   <si>
-    <t>Effets des chocs conjoncturelles sur la banlance commerciale des pays de la CEDEAO</t>
-  </si>
-  <si>
     <t>Siombin Nangoti Ali</t>
   </si>
   <si>
     <t>COULIBALY Siombin Nangoti Ali</t>
   </si>
   <si>
-    <t>Contribution de la cellule de remediaton a la mise à jour des données clientèles: Cas de la Bridge Bank Group Ci</t>
-  </si>
-  <si>
     <t>Bridge Bank</t>
   </si>
   <si>
@@ -1761,9 +1745,6 @@
     <t>KOUADIO Aguely Jean</t>
   </si>
   <si>
-    <t>Evaluation des risques dans une société de Gestion Immoilière: Une approche d'audit pour la prévention et la détection des risques de fraudes dans la société Beta</t>
-  </si>
-  <si>
     <t>Chintchon Aminata</t>
   </si>
   <si>
@@ -1872,9 +1853,6 @@
     <t>Effet de l'implémentation du logiciel ODOO sur les résultats comptables de MOYE SARL : une étude exploratoire</t>
   </si>
   <si>
-    <t>Audit et controle</t>
-  </si>
-  <si>
     <t>MOYE-SARL</t>
   </si>
   <si>
@@ -2619,9 +2597,6 @@
     <t>0556040441</t>
   </si>
   <si>
-    <t>L'impact de l'inétgration des nouvelles technologies sur le processus de compensation bancaire: cas de AFG BANK</t>
-  </si>
-  <si>
     <t>AFG BANK</t>
   </si>
   <si>
@@ -2958,9 +2933,6 @@
     <t xml:space="preserve">Negociation et gestion des credit commerciaux a court terme: Cas de la banque populaire de la CI </t>
   </si>
   <si>
-    <t>Prestation de sinistre</t>
-  </si>
-  <si>
     <t>Manuel de procédure</t>
   </si>
   <si>
@@ -3043,12 +3015,108 @@
   </si>
   <si>
     <t>Gestion des risques bancaires</t>
+  </si>
+  <si>
+    <t>Risque sinistre</t>
+  </si>
+  <si>
+    <t>Analyse des coûts</t>
+  </si>
+  <si>
+    <t>Cycle de vie de crédit</t>
+  </si>
+  <si>
+    <t>Assistance comptable</t>
+  </si>
+  <si>
+    <t>Risque et conformité</t>
+  </si>
+  <si>
+    <t>Effets des chocs conjoncturelles sur la balance commerciale des pays de la CEDEAO</t>
+  </si>
+  <si>
+    <t>Contribution de la cellule de remediaton à la mise à jour des données clientèles: Cas de la Bridge Bank Group Ci</t>
+  </si>
+  <si>
+    <t>Mise à jour des données clientèles</t>
+  </si>
+  <si>
+    <t>Evaluation des risques dans une société de Gestion Immobilière: Une approche d'audit pour la prévention et la détection des risques de fraudes dans la société Beta</t>
+  </si>
+  <si>
+    <t>Evaluation des risques</t>
+  </si>
+  <si>
+    <t>Commercialisation des produits</t>
+  </si>
+  <si>
+    <t>Risque de change</t>
+  </si>
+  <si>
+    <t>Relation: particulier et impayé</t>
+  </si>
+  <si>
+    <t>Performance financière</t>
+  </si>
+  <si>
+    <t>Système de recouvrement</t>
+  </si>
+  <si>
+    <t>Assistance funeraille</t>
+  </si>
+  <si>
+    <t>Rupture de contrat</t>
+  </si>
+  <si>
+    <t>Prime impayé</t>
+  </si>
+  <si>
+    <t>Cartographie des risques</t>
+  </si>
+  <si>
+    <t>Audit Public</t>
+  </si>
+  <si>
+    <t>Conformité de l'information financière</t>
+  </si>
+  <si>
+    <t>Système d'évaluation de la conformité</t>
+  </si>
+  <si>
+    <t>Return on equity</t>
+  </si>
+  <si>
+    <t>Audit légal</t>
+  </si>
+  <si>
+    <t>Cartographie d'octroi de crédit</t>
+  </si>
+  <si>
+    <t>Financement bancaire</t>
+  </si>
+  <si>
+    <t>2025-15-04 00:00:00</t>
+  </si>
+  <si>
+    <t>Education financière</t>
+  </si>
+  <si>
+    <t>Stratégie marketing</t>
+  </si>
+  <si>
+    <t>L'impact de l'intégration des nouvelles technologies sur le processus de compensation bancaire: cas de AFG BANK</t>
+  </si>
+  <si>
+    <t>Ralentissement du traitement d'information</t>
+  </si>
+  <si>
+    <t>Système de pilotage de performance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
@@ -3101,13 +3169,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3229,47 +3303,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -4493,7 +4526,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4534,7 +4567,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="45794.60682789352" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="45794.60682789352" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N187" sheet="Sheet1"/>
   </cacheSource>
@@ -7458,7 +7491,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="Tableau croisé dynamique5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tableau croisé dynamique5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:C76" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="13">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -8170,16 +8203,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:C76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -8187,10 +8220,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -8201,7 +8234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -8212,7 +8245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -8223,18 +8256,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -8245,40 +8278,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -8289,40 +8322,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -8333,40 +8366,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -8377,7 +8410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -8388,18 +8421,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -8410,40 +8443,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -8454,51 +8487,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -8509,7 +8542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -8520,7 +8553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -8531,40 +8564,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -8575,7 +8608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -8586,7 +8619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -8597,7 +8630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -8608,7 +8641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -8619,7 +8652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -8630,40 +8663,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -8674,7 +8707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -8685,18 +8718,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -8707,7 +8740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -8718,40 +8751,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -8762,29 +8795,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C57">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -8795,18 +8828,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -8817,7 +8850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -8828,40 +8861,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -8872,18 +8905,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -8894,7 +8927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>51</v>
       </c>
@@ -8905,51 +8938,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C69">
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>51</v>
       </c>
@@ -8960,7 +8993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>51</v>
       </c>
@@ -8971,23 +9004,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C75">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -8999,28 +9032,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:N187"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="142.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" customWidth="1"/>
-    <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.5703125" customWidth="1"/>
-    <col min="10" max="10" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.54296875" customWidth="1"/>
+    <col min="8" max="8" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.54296875" customWidth="1"/>
+    <col min="10" max="10" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9046,7 +9079,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -9064,8 +9097,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
         <v>44123</v>
       </c>
       <c r="B2" t="s">
@@ -9081,13 +9114,13 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="H2" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="I2" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -9102,8 +9135,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>44123</v>
       </c>
       <c r="B3" t="s">
@@ -9119,13 +9152,13 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="H3" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="I3" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -9140,8 +9173,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
         <v>44120</v>
       </c>
       <c r="B4" t="s">
@@ -9157,13 +9190,13 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H4" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="I4" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -9178,8 +9211,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>44120</v>
       </c>
       <c r="B5" t="s">
@@ -9195,13 +9228,13 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H5" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="I5" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -9216,8 +9249,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
         <v>44166</v>
       </c>
       <c r="B6" t="s">
@@ -9233,13 +9266,13 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H6" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="I6" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -9254,8 +9287,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>44167</v>
       </c>
       <c r="B7" t="s">
@@ -9271,13 +9304,13 @@
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="H7" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="I7" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -9292,8 +9325,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
         <v>44167</v>
       </c>
       <c r="B8" t="s">
@@ -9309,13 +9342,13 @@
         <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H8" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="I8" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -9330,8 +9363,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>44167</v>
       </c>
       <c r="B9" t="s">
@@ -9347,16 +9380,16 @@
         <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="H9" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J9" t="s">
         <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M9" s="2">
         <v>44186</v>
@@ -9365,8 +9398,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
@@ -9382,10 +9415,10 @@
         <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="H10" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J10" t="s">
         <v>51</v>
@@ -9400,8 +9433,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
@@ -9417,10 +9450,10 @@
         <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H11" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J11" t="s">
         <v>51</v>
@@ -9435,8 +9468,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B12" t="s">
@@ -9452,10 +9485,10 @@
         <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="H12" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="J12" t="s">
         <v>70</v>
@@ -9467,8 +9500,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B13" t="s">
@@ -9484,10 +9517,10 @@
         <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="H13" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -9502,8 +9535,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B14" t="s">
@@ -9519,10 +9552,10 @@
         <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="H14" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -9537,8 +9570,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B15" t="s">
@@ -9554,10 +9587,10 @@
         <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="H15" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -9569,8 +9602,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B16" t="s">
@@ -9586,10 +9619,10 @@
         <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H16" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="J16" t="s">
         <v>51</v>
@@ -9604,8 +9637,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B17" t="s">
@@ -9621,10 +9654,10 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H17" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="J17" t="s">
         <v>51</v>
@@ -9639,8 +9672,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -9656,10 +9689,10 @@
         <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H18" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J18" t="s">
         <v>51</v>
@@ -9674,8 +9707,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B19" t="s">
@@ -9706,8 +9739,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B20" t="s">
@@ -9723,10 +9756,10 @@
         <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="H20" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J20" t="s">
         <v>51</v>
@@ -9741,8 +9774,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B21" t="s">
@@ -9758,10 +9791,10 @@
         <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="H21" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="J21" t="s">
         <v>51</v>
@@ -9776,8 +9809,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B22" t="s">
@@ -9793,10 +9826,10 @@
         <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H22" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J22" t="s">
         <v>51</v>
@@ -9811,8 +9844,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B23" t="s">
@@ -9828,10 +9861,10 @@
         <v>127</v>
       </c>
       <c r="G23" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="H23" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -9846,8 +9879,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B24" t="s">
@@ -9863,10 +9896,10 @@
         <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="H24" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J24" t="s">
         <v>51</v>
@@ -9881,8 +9914,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B25" t="s">
@@ -9898,10 +9931,10 @@
         <v>138</v>
       </c>
       <c r="G25" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H25" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
@@ -9916,8 +9949,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B26" t="s">
@@ -9933,10 +9966,10 @@
         <v>143</v>
       </c>
       <c r="G26" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H26" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -9951,8 +9984,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B27" t="s">
@@ -9968,10 +10001,10 @@
         <v>149</v>
       </c>
       <c r="G27" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H27" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J27" t="s">
         <v>51</v>
@@ -9986,8 +10019,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B28" t="s">
@@ -10003,10 +10036,10 @@
         <v>153</v>
       </c>
       <c r="G28" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="H28" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -10018,8 +10051,8 @@
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B29" t="s">
@@ -10032,13 +10065,13 @@
         <v>158</v>
       </c>
       <c r="F29" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="G29" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="H29" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -10047,8 +10080,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B30" t="s">
@@ -10064,10 +10097,10 @@
         <v>162</v>
       </c>
       <c r="G30" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H30" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
@@ -10076,8 +10109,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B31" t="s">
@@ -10093,10 +10126,10 @@
         <v>167</v>
       </c>
       <c r="G31" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="H31" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="J31" t="s">
         <v>51</v>
@@ -10105,8 +10138,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B32" t="s">
@@ -10122,10 +10155,10 @@
         <v>172</v>
       </c>
       <c r="G32" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="H32" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
@@ -10134,8 +10167,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B33" t="s">
@@ -10148,13 +10181,13 @@
         <v>176</v>
       </c>
       <c r="F33" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="G33" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="H33" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="J33" t="s">
         <v>51</v>
@@ -10163,8 +10196,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B34" t="s">
@@ -10180,17 +10213,17 @@
         <v>182</v>
       </c>
       <c r="G34" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="H34" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B35" t="s">
@@ -10206,10 +10239,10 @@
         <v>186</v>
       </c>
       <c r="G35" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="H35" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
@@ -10218,8 +10251,8 @@
         <v>187</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
         <v>188</v>
       </c>
       <c r="B36" t="s">
@@ -10241,8 +10274,8 @@
         <v>44503</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
         <v>188</v>
       </c>
       <c r="B37" t="s">
@@ -10270,8 +10303,8 @@
         <v>44504</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
         <v>199</v>
       </c>
       <c r="B38" t="s">
@@ -10296,8 +10329,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
         <v>206</v>
       </c>
       <c r="B39" t="s">
@@ -10310,13 +10343,13 @@
         <v>209</v>
       </c>
       <c r="F39" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="G39" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="H39" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
@@ -10325,8 +10358,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B40" t="s">
@@ -10342,10 +10375,10 @@
         <v>215</v>
       </c>
       <c r="G40" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="H40" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
@@ -10354,8 +10387,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B41" t="s">
@@ -10371,10 +10404,10 @@
         <v>220</v>
       </c>
       <c r="G41" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H41" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J41" t="s">
         <v>51</v>
@@ -10383,8 +10416,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B42" t="s">
@@ -10400,10 +10433,10 @@
         <v>224</v>
       </c>
       <c r="G42" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H42" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
@@ -10412,8 +10445,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B43" t="s">
@@ -10426,13 +10459,13 @@
         <v>228</v>
       </c>
       <c r="F43" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="G43" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H43" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J43" t="s">
         <v>51</v>
@@ -10441,8 +10474,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B44" t="s">
@@ -10458,10 +10491,10 @@
         <v>232</v>
       </c>
       <c r="G44" t="s">
-        <v>977</v>
+        <v>997</v>
       </c>
       <c r="H44" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J44" t="s">
         <v>51</v>
@@ -10470,8 +10503,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
         <v>233</v>
       </c>
       <c r="B45" t="s">
@@ -10487,10 +10520,10 @@
         <v>237</v>
       </c>
       <c r="G45" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H45" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J45" t="s">
         <v>51</v>
@@ -10502,8 +10535,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
         <v>233</v>
       </c>
       <c r="B46" t="s">
@@ -10519,10 +10552,10 @@
         <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H46" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="J46" t="s">
         <v>17</v>
@@ -10531,8 +10564,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
         <v>233</v>
       </c>
       <c r="B47" t="s">
@@ -10548,10 +10581,10 @@
         <v>247</v>
       </c>
       <c r="G47" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H47" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
@@ -10563,8 +10596,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
         <v>44524</v>
       </c>
       <c r="B48" t="s">
@@ -10580,10 +10613,10 @@
         <v>252</v>
       </c>
       <c r="G48" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="H48" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
@@ -10595,8 +10628,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
         <v>44191</v>
       </c>
       <c r="B49" t="s">
@@ -10612,17 +10645,17 @@
         <v>257</v>
       </c>
       <c r="G49" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="H49" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="J49" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
         <v>44526</v>
       </c>
       <c r="B50" t="s">
@@ -10638,106 +10671,106 @@
         <v>261</v>
       </c>
       <c r="G50" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="H50" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="J50" t="s">
         <v>51</v>
       </c>
       <c r="K50" t="s">
+        <v>262</v>
+      </c>
+      <c r="L50" t="s">
         <v>263</v>
       </c>
-      <c r="L50" t="s">
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>44191</v>
+      </c>
+      <c r="B51" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>44191</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>265</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>266</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
         <v>267</v>
       </c>
-      <c r="F51" t="s">
-        <v>268</v>
-      </c>
       <c r="G51" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="H51" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J51" t="s">
         <v>51</v>
       </c>
       <c r="K51" t="s">
+        <v>268</v>
+      </c>
+      <c r="L51" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>44612</v>
+      </c>
+      <c r="B52" t="s">
         <v>269</v>
       </c>
-      <c r="L51" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>44612</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>270</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>271</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>272</v>
       </c>
-      <c r="F52" t="s">
-        <v>273</v>
-      </c>
       <c r="G52" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="H52" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J52" t="s">
         <v>17</v>
       </c>
       <c r="K52" t="s">
+        <v>273</v>
+      </c>
+      <c r="L52" t="s">
         <v>274</v>
       </c>
-      <c r="L52" t="s">
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B53" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>44620</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>276</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>277</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
         <v>278</v>
       </c>
-      <c r="F53" t="s">
-        <v>279</v>
-      </c>
       <c r="G53" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="H53" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J53" t="s">
         <v>51</v>
@@ -10746,155 +10779,155 @@
         <v>98</v>
       </c>
       <c r="L53" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
         <v>44620</v>
       </c>
       <c r="B54" t="s">
         <v>88</v>
       </c>
       <c r="C54" t="s">
+        <v>279</v>
+      </c>
+      <c r="D54" t="s">
         <v>280</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>281</v>
       </c>
-      <c r="F54" t="s">
-        <v>282</v>
-      </c>
       <c r="G54" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="H54" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J54" t="s">
         <v>51</v>
       </c>
       <c r="K54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L54" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
         <v>44255</v>
       </c>
       <c r="B55" t="s">
+        <v>282</v>
+      </c>
+      <c r="C55" t="s">
         <v>283</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>284</v>
       </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
         <v>285</v>
       </c>
-      <c r="F55" t="s">
-        <v>286</v>
-      </c>
       <c r="G55" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="H55" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="J55" t="s">
         <v>51</v>
       </c>
       <c r="K55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L55" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A56" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B56" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>44255</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>288</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>289</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
         <v>290</v>
       </c>
-      <c r="F56" t="s">
-        <v>291</v>
-      </c>
       <c r="G56" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H56" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="J56" t="s">
         <v>51</v>
       </c>
       <c r="K56" t="s">
+        <v>291</v>
+      </c>
+      <c r="L56" t="s">
         <v>292</v>
       </c>
-      <c r="L56" t="s">
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B57" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>44255</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>294</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>295</v>
       </c>
-      <c r="D57" t="s">
-        <v>296</v>
-      </c>
       <c r="F57" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="G57" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="H57" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
       </c>
       <c r="L57" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A58" s="4">
         <v>44255</v>
       </c>
       <c r="B58" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" t="s">
         <v>297</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>298</v>
       </c>
-      <c r="D58" t="s">
+      <c r="F58" t="s">
         <v>299</v>
       </c>
-      <c r="F58" t="s">
-        <v>300</v>
-      </c>
       <c r="G58" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="H58" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -10903,62 +10936,62 @@
         <v>98</v>
       </c>
       <c r="L58" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A59" s="4">
         <v>44255</v>
       </c>
       <c r="B59" t="s">
+        <v>300</v>
+      </c>
+      <c r="C59" t="s">
         <v>301</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>302</v>
       </c>
-      <c r="D59" t="s">
+      <c r="F59" t="s">
         <v>303</v>
       </c>
-      <c r="F59" t="s">
-        <v>304</v>
-      </c>
       <c r="G59" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="H59" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J59" t="s">
         <v>51</v>
       </c>
       <c r="K59" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L59" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60" s="4">
         <v>44620</v>
       </c>
       <c r="B60" t="s">
+        <v>304</v>
+      </c>
+      <c r="C60" t="s">
         <v>305</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>306</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
         <v>307</v>
       </c>
-      <c r="F60" t="s">
-        <v>308</v>
-      </c>
       <c r="G60" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="H60" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="J60" t="s">
         <v>51</v>
@@ -10967,439 +11000,439 @@
         <v>114</v>
       </c>
       <c r="L60" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
         <v>44620</v>
       </c>
       <c r="B61" t="s">
+        <v>308</v>
+      </c>
+      <c r="C61" t="s">
         <v>309</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>310</v>
       </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
         <v>311</v>
       </c>
-      <c r="F61" t="s">
-        <v>312</v>
-      </c>
       <c r="G61" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="H61" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J61" t="s">
         <v>51</v>
       </c>
       <c r="K61" t="s">
+        <v>312</v>
+      </c>
+      <c r="L61" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A62" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B62" t="s">
         <v>313</v>
       </c>
-      <c r="L61" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>44620</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>314</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>315</v>
       </c>
-      <c r="D62" t="s">
+      <c r="F62" t="s">
         <v>316</v>
       </c>
-      <c r="F62" t="s">
-        <v>317</v>
-      </c>
       <c r="G62" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="H62" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J62" t="s">
         <v>51</v>
       </c>
       <c r="L62" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A63" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B63" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>44620</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>319</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>320</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>321</v>
       </c>
-      <c r="F63" t="s">
-        <v>322</v>
-      </c>
       <c r="G63" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="H63" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J63" t="s">
         <v>51</v>
       </c>
       <c r="K63" t="s">
+        <v>322</v>
+      </c>
+      <c r="L63" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A64" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B64" t="s">
         <v>323</v>
       </c>
-      <c r="L63" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>44620</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>324</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>325</v>
       </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
         <v>326</v>
-      </c>
-      <c r="F64" t="s">
-        <v>327</v>
       </c>
       <c r="J64" t="s">
         <v>70</v>
       </c>
       <c r="L64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A65" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B65" t="s">
+        <v>328</v>
+      </c>
+      <c r="C65" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>44620</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="D65" t="s">
         <v>330</v>
       </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
         <v>331</v>
       </c>
-      <c r="D65" t="s">
-        <v>332</v>
-      </c>
-      <c r="F65" t="s">
-        <v>333</v>
-      </c>
       <c r="G65" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="H65" t="s">
-        <v>935</v>
+        <v>996</v>
       </c>
       <c r="J65" t="s">
         <v>51</v>
       </c>
       <c r="K65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L65" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A66" s="4">
         <v>44620</v>
       </c>
       <c r="B66" t="s">
+        <v>332</v>
+      </c>
+      <c r="C66" t="s">
+        <v>333</v>
+      </c>
+      <c r="D66" t="s">
         <v>334</v>
       </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
         <v>335</v>
       </c>
-      <c r="D66" t="s">
-        <v>336</v>
-      </c>
-      <c r="F66" t="s">
-        <v>337</v>
-      </c>
       <c r="G66" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
       <c r="H66" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="J66" t="s">
         <v>51</v>
       </c>
       <c r="L66" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>44623</v>
+      </c>
+      <c r="B67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C67" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>44623</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="D67" t="s">
         <v>339</v>
       </c>
-      <c r="C67" t="s">
+      <c r="F67" t="s">
         <v>340</v>
-      </c>
-      <c r="D67" t="s">
-        <v>341</v>
-      </c>
-      <c r="F67" t="s">
-        <v>342</v>
       </c>
       <c r="J67" t="s">
         <v>70</v>
       </c>
       <c r="L67" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>44833</v>
+      </c>
+      <c r="B68" t="s">
+        <v>342</v>
+      </c>
+      <c r="C68" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>44833</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="D68" t="s">
         <v>344</v>
-      </c>
-      <c r="C68" t="s">
-        <v>345</v>
-      </c>
-      <c r="D68" t="s">
-        <v>346</v>
       </c>
       <c r="E68">
         <v>767469615</v>
       </c>
       <c r="F68" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="G68" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="H68" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J68" t="s">
         <v>51</v>
       </c>
       <c r="K68" t="s">
+        <v>345</v>
+      </c>
+      <c r="L68" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
+        <v>44833</v>
+      </c>
+      <c r="B69" t="s">
+        <v>346</v>
+      </c>
+      <c r="C69" t="s">
         <v>347</v>
       </c>
-      <c r="L68" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>44833</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>348</v>
       </c>
-      <c r="C69" t="s">
+      <c r="F69" t="s">
         <v>349</v>
       </c>
-      <c r="D69" t="s">
-        <v>350</v>
-      </c>
-      <c r="F69" t="s">
-        <v>351</v>
-      </c>
       <c r="G69" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="H69" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L69" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A70" s="4">
         <v>44844</v>
       </c>
       <c r="B70" t="s">
         <v>254</v>
       </c>
       <c r="C70" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D70" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E70">
         <v>102989154</v>
       </c>
       <c r="F70" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G70" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
       <c r="H70" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
       </c>
       <c r="K70" t="s">
+        <v>354</v>
+      </c>
+      <c r="L70" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A71" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B71" t="s">
         <v>356</v>
       </c>
-      <c r="L70" t="s">
+      <c r="C71" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>44620</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
         <v>358</v>
       </c>
-      <c r="C71" t="s">
+      <c r="F71" t="s">
         <v>359</v>
       </c>
-      <c r="D71" t="s">
-        <v>360</v>
-      </c>
-      <c r="F71" t="s">
-        <v>361</v>
-      </c>
       <c r="G71" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="H71" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
       </c>
       <c r="L71" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A72" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B72" t="s">
+        <v>361</v>
+      </c>
+      <c r="C72" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>44844</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="D72" t="s">
         <v>363</v>
-      </c>
-      <c r="C72" t="s">
-        <v>364</v>
-      </c>
-      <c r="D72" t="s">
-        <v>365</v>
       </c>
       <c r="E72">
         <v>787347707</v>
       </c>
       <c r="F72" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J72" t="s">
         <v>70</v>
       </c>
       <c r="L72" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B73" t="s">
+        <v>366</v>
+      </c>
+      <c r="C73" t="s">
+        <v>367</v>
+      </c>
+      <c r="D73" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>44844</v>
-      </c>
-      <c r="B73" t="s">
-        <v>369</v>
-      </c>
-      <c r="C73" t="s">
-        <v>370</v>
-      </c>
-      <c r="D73" t="s">
-        <v>371</v>
       </c>
       <c r="E73">
         <v>141583425</v>
       </c>
       <c r="F73" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="J73" t="s">
         <v>70</v>
       </c>
       <c r="L73" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A74" s="4">
         <v>44844</v>
       </c>
       <c r="B74" t="s">
         <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D74" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E74">
         <v>758422493</v>
       </c>
       <c r="F74" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J74" t="s">
         <v>70</v>
       </c>
       <c r="L74" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A75" s="4">
         <v>44944</v>
       </c>
       <c r="B75" t="s">
+        <v>374</v>
+      </c>
+      <c r="C75" t="s">
+        <v>375</v>
+      </c>
+      <c r="D75" t="s">
+        <v>376</v>
+      </c>
+      <c r="F75" t="s">
         <v>377</v>
       </c>
-      <c r="C75" t="s">
-        <v>378</v>
-      </c>
-      <c r="D75" t="s">
-        <v>379</v>
-      </c>
-      <c r="F75" t="s">
-        <v>380</v>
-      </c>
       <c r="G75" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="H75" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="J75" t="s">
         <v>51</v>
@@ -11408,676 +11441,676 @@
         <v>98</v>
       </c>
       <c r="L75" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A76" s="4">
+        <v>44945</v>
+      </c>
+      <c r="B76" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" t="s">
+        <v>380</v>
+      </c>
+      <c r="D76" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>44945</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
         <v>382</v>
-      </c>
-      <c r="C76" t="s">
-        <v>383</v>
-      </c>
-      <c r="D76" t="s">
-        <v>384</v>
-      </c>
-      <c r="F76" t="s">
-        <v>385</v>
       </c>
       <c r="J76" t="s">
         <v>70</v>
       </c>
       <c r="L76" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A77" s="4">
         <v>44945</v>
       </c>
       <c r="B77" t="s">
+        <v>383</v>
+      </c>
+      <c r="C77" t="s">
+        <v>384</v>
+      </c>
+      <c r="D77" t="s">
+        <v>385</v>
+      </c>
+      <c r="F77" t="s">
         <v>386</v>
       </c>
-      <c r="C77" t="s">
-        <v>387</v>
-      </c>
-      <c r="D77" t="s">
-        <v>388</v>
-      </c>
-      <c r="F77" t="s">
-        <v>389</v>
-      </c>
       <c r="G77" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H77" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
       </c>
       <c r="L77" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A78" s="4">
         <v>44946</v>
       </c>
       <c r="B78" t="s">
         <v>88</v>
       </c>
       <c r="C78" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D78" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F78" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G78" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H78" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J78" t="s">
         <v>17</v>
       </c>
       <c r="L78" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A79" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B79" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" t="s">
+        <v>392</v>
+      </c>
+      <c r="D79" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>44844</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="F79" t="s">
         <v>394</v>
-      </c>
-      <c r="C79" t="s">
-        <v>395</v>
-      </c>
-      <c r="D79" t="s">
-        <v>396</v>
-      </c>
-      <c r="F79" t="s">
-        <v>397</v>
       </c>
       <c r="J79" t="s">
         <v>70</v>
       </c>
       <c r="L79" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A80" s="4">
         <v>44952</v>
       </c>
       <c r="B80" t="s">
         <v>100</v>
       </c>
       <c r="C80" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D80" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F80" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J80" t="s">
         <v>70</v>
       </c>
       <c r="L80" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A81" s="4">
         <v>44620</v>
       </c>
       <c r="B81" t="s">
         <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D81" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F81" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G81" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="H81" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="J81" t="s">
         <v>17</v>
       </c>
       <c r="L81" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A82" s="4">
         <v>44957</v>
       </c>
       <c r="B82" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C82" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D82" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E82">
         <v>767469615</v>
       </c>
       <c r="F82" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G82" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="H82" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
       </c>
       <c r="K82" t="s">
+        <v>406</v>
+      </c>
+      <c r="L82" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A83" s="4">
+        <v>45013</v>
+      </c>
+      <c r="B83" t="s">
+        <v>407</v>
+      </c>
+      <c r="C83" t="s">
+        <v>408</v>
+      </c>
+      <c r="D83" t="s">
         <v>409</v>
       </c>
-      <c r="L82" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>45013</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="F83" t="s">
         <v>410</v>
-      </c>
-      <c r="C83" t="s">
-        <v>411</v>
-      </c>
-      <c r="D83" t="s">
-        <v>412</v>
-      </c>
-      <c r="F83" t="s">
-        <v>413</v>
       </c>
       <c r="J83" t="s">
         <v>70</v>
       </c>
       <c r="L83" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84" s="4">
+        <v>45013</v>
+      </c>
+      <c r="B84" t="s">
+        <v>412</v>
+      </c>
+      <c r="C84" t="s">
+        <v>413</v>
+      </c>
+      <c r="D84" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>45013</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="F84" t="s">
         <v>415</v>
-      </c>
-      <c r="C84" t="s">
-        <v>416</v>
-      </c>
-      <c r="D84" t="s">
-        <v>417</v>
-      </c>
-      <c r="F84" t="s">
-        <v>418</v>
       </c>
       <c r="J84" t="s">
         <v>70</v>
       </c>
       <c r="L84" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A85" s="4">
         <v>45386</v>
       </c>
       <c r="B85" t="s">
+        <v>416</v>
+      </c>
+      <c r="C85" t="s">
+        <v>417</v>
+      </c>
+      <c r="D85" t="s">
+        <v>418</v>
+      </c>
+      <c r="F85" t="s">
         <v>419</v>
       </c>
-      <c r="C85" t="s">
-        <v>420</v>
-      </c>
-      <c r="D85" t="s">
-        <v>421</v>
-      </c>
-      <c r="F85" t="s">
-        <v>422</v>
-      </c>
       <c r="G85" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="H85" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="J85" t="s">
         <v>51</v>
       </c>
       <c r="K85" t="s">
+        <v>420</v>
+      </c>
+      <c r="L85" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A86" s="4">
+        <v>45103</v>
+      </c>
+      <c r="B86" t="s">
+        <v>422</v>
+      </c>
+      <c r="C86" t="s">
         <v>423</v>
       </c>
-      <c r="L85" t="s">
+      <c r="D86" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>45103</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="F86" t="s">
         <v>425</v>
       </c>
-      <c r="C86" t="s">
-        <v>426</v>
-      </c>
-      <c r="D86" t="s">
-        <v>427</v>
-      </c>
-      <c r="F86" t="s">
-        <v>428</v>
-      </c>
       <c r="G86" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="H86" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="J86" t="s">
         <v>51</v>
       </c>
       <c r="K86" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="L86" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A87" s="4">
         <v>45107</v>
       </c>
       <c r="B87" t="s">
         <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D87" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F87" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J87" t="s">
         <v>70</v>
       </c>
       <c r="L87" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A88" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B88" t="s">
+        <v>432</v>
+      </c>
+      <c r="C88" t="s">
+        <v>433</v>
+      </c>
+      <c r="D88" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>45107</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="F88" t="s">
         <v>435</v>
-      </c>
-      <c r="C88" t="s">
-        <v>436</v>
-      </c>
-      <c r="D88" t="s">
-        <v>437</v>
-      </c>
-      <c r="F88" t="s">
-        <v>438</v>
       </c>
       <c r="J88" t="s">
         <v>70</v>
       </c>
       <c r="L88" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89" s="4">
         <v>45107</v>
       </c>
       <c r="B89" t="s">
+        <v>436</v>
+      </c>
+      <c r="C89" t="s">
+        <v>437</v>
+      </c>
+      <c r="D89" t="s">
+        <v>438</v>
+      </c>
+      <c r="F89" t="s">
         <v>439</v>
-      </c>
-      <c r="C89" t="s">
-        <v>440</v>
-      </c>
-      <c r="D89" t="s">
-        <v>441</v>
-      </c>
-      <c r="F89" t="s">
-        <v>442</v>
       </c>
       <c r="J89" t="s">
         <v>70</v>
       </c>
       <c r="L89" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A90" s="4">
         <v>45107</v>
       </c>
       <c r="B90" t="s">
+        <v>440</v>
+      </c>
+      <c r="C90" t="s">
+        <v>441</v>
+      </c>
+      <c r="D90" t="s">
+        <v>442</v>
+      </c>
+      <c r="F90" t="s">
         <v>443</v>
       </c>
-      <c r="C90" t="s">
-        <v>444</v>
-      </c>
-      <c r="D90" t="s">
-        <v>445</v>
-      </c>
-      <c r="F90" t="s">
-        <v>446</v>
-      </c>
       <c r="G90" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="H90" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
       </c>
       <c r="L90" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A91" s="4">
         <v>45107</v>
       </c>
       <c r="B91" t="s">
         <v>59</v>
       </c>
       <c r="C91" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D91" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F91" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G91" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="H91" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J91" t="s">
         <v>17</v>
       </c>
       <c r="K91" t="s">
+        <v>448</v>
+      </c>
+      <c r="L91" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A92" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B92" t="s">
+        <v>449</v>
+      </c>
+      <c r="C92" t="s">
+        <v>450</v>
+      </c>
+      <c r="D92" t="s">
         <v>451</v>
       </c>
-      <c r="L91" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>45107</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="F92" t="s">
         <v>452</v>
-      </c>
-      <c r="C92" t="s">
-        <v>453</v>
-      </c>
-      <c r="D92" t="s">
-        <v>454</v>
-      </c>
-      <c r="F92" t="s">
-        <v>455</v>
       </c>
       <c r="J92" t="s">
         <v>70</v>
       </c>
       <c r="L92" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A93" s="4">
         <v>45110</v>
       </c>
       <c r="B93" t="s">
+        <v>453</v>
+      </c>
+      <c r="C93" t="s">
+        <v>454</v>
+      </c>
+      <c r="D93" t="s">
+        <v>455</v>
+      </c>
+      <c r="F93" t="s">
         <v>456</v>
       </c>
-      <c r="C93" t="s">
-        <v>457</v>
-      </c>
-      <c r="D93" t="s">
-        <v>458</v>
-      </c>
-      <c r="F93" t="s">
-        <v>459</v>
-      </c>
       <c r="G93" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="H93" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J93" t="s">
         <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="L93" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A94" s="4">
         <v>45110</v>
       </c>
       <c r="B94" t="s">
         <v>179</v>
       </c>
       <c r="C94" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D94" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G94" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H94" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J94" t="s">
         <v>17</v>
       </c>
       <c r="K94" t="s">
+        <v>461</v>
+      </c>
+      <c r="L94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B95" t="s">
+        <v>463</v>
+      </c>
+      <c r="C95" t="s">
         <v>464</v>
       </c>
-      <c r="L94" t="s">
+      <c r="D95" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>45110</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="F95" t="s">
         <v>466</v>
       </c>
-      <c r="C95" t="s">
-        <v>467</v>
-      </c>
-      <c r="D95" t="s">
-        <v>468</v>
-      </c>
-      <c r="F95" t="s">
-        <v>469</v>
-      </c>
       <c r="G95" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="H95" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="J95" t="s">
         <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="L95" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B96" t="s">
+        <v>468</v>
+      </c>
+      <c r="C96" t="s">
+        <v>469</v>
+      </c>
+      <c r="D96" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>45110</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="F96" t="s">
         <v>471</v>
       </c>
-      <c r="C96" t="s">
-        <v>472</v>
-      </c>
-      <c r="D96" t="s">
-        <v>473</v>
-      </c>
-      <c r="F96" t="s">
-        <v>474</v>
-      </c>
       <c r="G96" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="H96" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J96" t="s">
         <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L96" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A97" s="4">
         <v>45110</v>
       </c>
       <c r="B97" t="s">
+        <v>472</v>
+      </c>
+      <c r="C97" t="s">
+        <v>473</v>
+      </c>
+      <c r="D97" t="s">
+        <v>474</v>
+      </c>
+      <c r="F97" t="s">
         <v>475</v>
       </c>
-      <c r="C97" t="s">
-        <v>476</v>
-      </c>
-      <c r="D97" t="s">
-        <v>477</v>
-      </c>
-      <c r="F97" t="s">
-        <v>478</v>
-      </c>
       <c r="G97" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H97" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J97" t="s">
         <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L97" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A98" s="4">
         <v>45110</v>
       </c>
       <c r="B98" t="s">
+        <v>476</v>
+      </c>
+      <c r="C98" t="s">
+        <v>477</v>
+      </c>
+      <c r="D98" t="s">
+        <v>478</v>
+      </c>
+      <c r="F98" t="s">
         <v>479</v>
       </c>
-      <c r="C98" t="s">
-        <v>480</v>
-      </c>
-      <c r="D98" t="s">
-        <v>481</v>
-      </c>
-      <c r="F98" t="s">
-        <v>482</v>
-      </c>
       <c r="G98" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H98" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J98" t="s">
         <v>17</v>
       </c>
       <c r="K98" t="s">
+        <v>480</v>
+      </c>
+      <c r="L98" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A99" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B99" t="s">
+        <v>481</v>
+      </c>
+      <c r="C99" t="s">
+        <v>482</v>
+      </c>
+      <c r="D99" t="s">
         <v>483</v>
       </c>
-      <c r="L98" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>45110</v>
-      </c>
-      <c r="B99" t="s">
+      <c r="F99" t="s">
         <v>484</v>
       </c>
-      <c r="C99" t="s">
-        <v>485</v>
-      </c>
-      <c r="D99" t="s">
-        <v>486</v>
-      </c>
-      <c r="F99" t="s">
-        <v>487</v>
-      </c>
       <c r="G99" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="H99" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="J99" t="s">
         <v>51</v>
@@ -12086,24 +12119,24 @@
         <v>114</v>
       </c>
       <c r="L99" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A100" s="4">
         <v>45110</v>
       </c>
       <c r="B100" t="s">
+        <v>485</v>
+      </c>
+      <c r="C100" t="s">
+        <v>486</v>
+      </c>
+      <c r="D100" t="s">
+        <v>487</v>
+      </c>
+      <c r="F100" t="s">
         <v>488</v>
-      </c>
-      <c r="C100" t="s">
-        <v>489</v>
-      </c>
-      <c r="D100" t="s">
-        <v>490</v>
-      </c>
-      <c r="F100" t="s">
-        <v>491</v>
       </c>
       <c r="G100" t="s">
         <v>17</v>
@@ -12115,24 +12148,24 @@
         <v>17</v>
       </c>
       <c r="L100" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A101" s="4">
         <v>45111</v>
       </c>
       <c r="B101" t="s">
+        <v>489</v>
+      </c>
+      <c r="C101" t="s">
+        <v>490</v>
+      </c>
+      <c r="D101" t="s">
+        <v>491</v>
+      </c>
+      <c r="F101" t="s">
         <v>492</v>
-      </c>
-      <c r="C101" t="s">
-        <v>493</v>
-      </c>
-      <c r="D101" t="s">
-        <v>494</v>
-      </c>
-      <c r="F101" t="s">
-        <v>495</v>
       </c>
       <c r="G101" t="s">
         <v>17</v>
@@ -12144,27 +12177,27 @@
         <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L101" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A102" s="4">
+        <v>45112</v>
+      </c>
+      <c r="B102" t="s">
+        <v>494</v>
+      </c>
+      <c r="C102" t="s">
+        <v>495</v>
+      </c>
+      <c r="D102" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>45112</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="F102" t="s">
         <v>497</v>
-      </c>
-      <c r="C102" t="s">
-        <v>498</v>
-      </c>
-      <c r="D102" t="s">
-        <v>499</v>
-      </c>
-      <c r="F102" t="s">
-        <v>500</v>
       </c>
       <c r="G102" t="s">
         <v>17</v>
@@ -12176,259 +12209,253 @@
         <v>17</v>
       </c>
       <c r="K102" t="s">
+        <v>498</v>
+      </c>
+      <c r="L102" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A103" s="4">
+        <v>45113</v>
+      </c>
+      <c r="B103" t="s">
+        <v>499</v>
+      </c>
+      <c r="C103" t="s">
+        <v>500</v>
+      </c>
+      <c r="D103" t="s">
         <v>501</v>
       </c>
-      <c r="L102" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="F103" t="s">
         <v>502</v>
-      </c>
-      <c r="C103" t="s">
-        <v>503</v>
-      </c>
-      <c r="D103" t="s">
-        <v>504</v>
-      </c>
-      <c r="F103" t="s">
-        <v>505</v>
       </c>
       <c r="J103" t="s">
         <v>70</v>
       </c>
       <c r="L103" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A104" s="4">
+        <v>45116</v>
+      </c>
+      <c r="B104" t="s">
+        <v>504</v>
+      </c>
+      <c r="C104" t="s">
+        <v>505</v>
+      </c>
+      <c r="D104" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>45116</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="F104" t="s">
         <v>507</v>
-      </c>
-      <c r="C104" t="s">
-        <v>508</v>
-      </c>
-      <c r="D104" t="s">
-        <v>509</v>
-      </c>
-      <c r="F104" t="s">
-        <v>510</v>
       </c>
       <c r="J104" t="s">
         <v>70</v>
       </c>
       <c r="L104" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A105" s="4">
+        <v>45240</v>
+      </c>
+      <c r="B105" t="s">
+        <v>337</v>
+      </c>
+      <c r="C105" t="s">
+        <v>509</v>
+      </c>
+      <c r="D105" t="s">
+        <v>510</v>
+      </c>
+      <c r="F105" t="s">
         <v>511</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>45240</v>
-      </c>
-      <c r="B105" t="s">
-        <v>339</v>
-      </c>
-      <c r="C105" t="s">
-        <v>512</v>
-      </c>
-      <c r="D105" t="s">
-        <v>513</v>
-      </c>
-      <c r="F105" t="s">
-        <v>514</v>
       </c>
       <c r="J105" t="s">
         <v>70</v>
       </c>
       <c r="L105" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A106" s="4">
         <v>45240</v>
       </c>
       <c r="B106" t="s">
         <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D106" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F106" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G106" t="s">
-        <v>51</v>
+        <v>997</v>
       </c>
       <c r="H106" t="s">
-        <v>262</v>
+        <v>934</v>
       </c>
       <c r="J106" t="s">
         <v>51</v>
       </c>
       <c r="K106" t="s">
+        <v>515</v>
+      </c>
+      <c r="L106" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A107" s="4">
+        <v>45240</v>
+      </c>
+      <c r="B107" t="s">
+        <v>517</v>
+      </c>
+      <c r="C107" t="s">
         <v>518</v>
       </c>
-      <c r="L106" t="s">
+      <c r="D107" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>45240</v>
-      </c>
-      <c r="B107" t="s">
+      <c r="F107" t="s">
         <v>520</v>
-      </c>
-      <c r="C107" t="s">
-        <v>521</v>
-      </c>
-      <c r="D107" t="s">
-        <v>522</v>
-      </c>
-      <c r="F107" t="s">
-        <v>523</v>
-      </c>
-      <c r="G107" t="s">
-        <v>328</v>
-      </c>
-      <c r="H107" t="s">
-        <v>328</v>
       </c>
       <c r="J107" t="s">
         <v>70</v>
       </c>
       <c r="L107" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A108" s="4">
         <v>45296</v>
       </c>
       <c r="B108" t="s">
+        <v>521</v>
+      </c>
+      <c r="C108" t="s">
+        <v>522</v>
+      </c>
+      <c r="D108" t="s">
+        <v>523</v>
+      </c>
+      <c r="F108" t="s">
         <v>524</v>
       </c>
-      <c r="C108" t="s">
-        <v>525</v>
-      </c>
-      <c r="D108" t="s">
-        <v>526</v>
-      </c>
-      <c r="F108" t="s">
-        <v>527</v>
-      </c>
       <c r="G108" t="s">
-        <v>17</v>
+        <v>998</v>
       </c>
       <c r="H108" t="s">
-        <v>17</v>
+        <v>931</v>
       </c>
       <c r="J108" t="s">
         <v>17</v>
       </c>
       <c r="K108" t="s">
+        <v>525</v>
+      </c>
+      <c r="L108" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A109" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B109" t="s">
+        <v>526</v>
+      </c>
+      <c r="C109" t="s">
+        <v>527</v>
+      </c>
+      <c r="D109" t="s">
         <v>528</v>
       </c>
-      <c r="L108" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>45385</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="F109" t="s">
         <v>529</v>
       </c>
-      <c r="C109" t="s">
-        <v>530</v>
-      </c>
-      <c r="D109" t="s">
-        <v>531</v>
-      </c>
-      <c r="F109" t="s">
-        <v>532</v>
-      </c>
       <c r="G109" t="s">
-        <v>51</v>
+        <v>999</v>
       </c>
       <c r="H109" t="s">
-        <v>262</v>
+        <v>996</v>
       </c>
       <c r="J109" t="s">
         <v>51</v>
       </c>
       <c r="K109" t="s">
+        <v>530</v>
+      </c>
+      <c r="L109" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A110" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B110" t="s">
+        <v>532</v>
+      </c>
+      <c r="C110" t="s">
         <v>533</v>
       </c>
-      <c r="L109" t="s">
+      <c r="D110" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="F110" t="s">
+        <v>535</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H110" t="s">
+        <v>931</v>
+      </c>
+      <c r="J110" t="s">
+        <v>17</v>
+      </c>
+      <c r="K110" t="s">
+        <v>536</v>
+      </c>
+      <c r="L110" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A111" s="4">
         <v>45385</v>
       </c>
-      <c r="B110" t="s">
-        <v>535</v>
-      </c>
-      <c r="C110" t="s">
-        <v>536</v>
-      </c>
-      <c r="D110" t="s">
-        <v>537</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="B111" t="s">
         <v>538</v>
       </c>
-      <c r="G110" t="s">
-        <v>328</v>
-      </c>
-      <c r="H110" t="s">
-        <v>328</v>
-      </c>
-      <c r="J110" t="s">
-        <v>70</v>
-      </c>
-      <c r="K110" t="s">
+      <c r="C111" t="s">
         <v>539</v>
       </c>
-      <c r="L110" t="s">
+      <c r="D111" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>45385</v>
-      </c>
-      <c r="B111" t="s">
+      <c r="F111" t="s">
         <v>541</v>
       </c>
-      <c r="C111" t="s">
-        <v>542</v>
-      </c>
-      <c r="D111" t="s">
-        <v>543</v>
-      </c>
-      <c r="F111" t="s">
-        <v>544</v>
-      </c>
       <c r="G111" t="s">
-        <v>51</v>
+        <v>936</v>
       </c>
       <c r="H111" t="s">
-        <v>262</v>
+        <v>937</v>
       </c>
       <c r="J111" t="s">
         <v>51</v>
@@ -12437,300 +12464,276 @@
         <v>98</v>
       </c>
       <c r="L111" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A112" s="4">
         <v>45385</v>
       </c>
       <c r="B112" t="s">
+        <v>542</v>
+      </c>
+      <c r="C112" t="s">
+        <v>543</v>
+      </c>
+      <c r="D112" t="s">
+        <v>544</v>
+      </c>
+      <c r="F112" t="s">
         <v>545</v>
-      </c>
-      <c r="C112" t="s">
-        <v>546</v>
-      </c>
-      <c r="D112" t="s">
-        <v>547</v>
-      </c>
-      <c r="F112" t="s">
-        <v>548</v>
-      </c>
-      <c r="G112" t="s">
-        <v>328</v>
-      </c>
-      <c r="H112" t="s">
-        <v>328</v>
       </c>
       <c r="J112" t="s">
         <v>70</v>
       </c>
       <c r="L112" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A113" s="4">
         <v>45385</v>
       </c>
       <c r="B113" t="s">
+        <v>546</v>
+      </c>
+      <c r="C113" t="s">
+        <v>547</v>
+      </c>
+      <c r="D113" t="s">
+        <v>548</v>
+      </c>
+      <c r="F113" t="s">
         <v>549</v>
-      </c>
-      <c r="C113" t="s">
-        <v>550</v>
-      </c>
-      <c r="D113" t="s">
-        <v>551</v>
-      </c>
-      <c r="F113" t="s">
-        <v>552</v>
-      </c>
-      <c r="G113" t="s">
-        <v>328</v>
-      </c>
-      <c r="H113" t="s">
-        <v>328</v>
       </c>
       <c r="J113" t="s">
         <v>70</v>
       </c>
       <c r="L113" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A114" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B114" t="s">
+        <v>551</v>
+      </c>
+      <c r="C114" t="s">
+        <v>552</v>
+      </c>
+      <c r="D114" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>45385</v>
-      </c>
-      <c r="B114" t="s">
+      <c r="F114" t="s">
         <v>554</v>
       </c>
-      <c r="C114" t="s">
-        <v>555</v>
-      </c>
-      <c r="D114" t="s">
-        <v>556</v>
-      </c>
-      <c r="F114" t="s">
-        <v>557</v>
-      </c>
       <c r="G114" t="s">
-        <v>51</v>
+        <v>1001</v>
       </c>
       <c r="H114" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J114" t="s">
         <v>51</v>
       </c>
       <c r="L114" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A115" s="4">
         <v>45385</v>
       </c>
       <c r="B115" t="s">
+        <v>555</v>
+      </c>
+      <c r="C115" t="s">
+        <v>556</v>
+      </c>
+      <c r="D115" t="s">
+        <v>557</v>
+      </c>
+      <c r="F115" t="s">
         <v>558</v>
-      </c>
-      <c r="C115" t="s">
-        <v>559</v>
-      </c>
-      <c r="D115" t="s">
-        <v>560</v>
-      </c>
-      <c r="F115" t="s">
-        <v>561</v>
-      </c>
-      <c r="G115" t="s">
-        <v>328</v>
-      </c>
-      <c r="H115" t="s">
-        <v>328</v>
       </c>
       <c r="J115" t="s">
         <v>70</v>
       </c>
       <c r="L115" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A116" s="4">
         <v>45385</v>
       </c>
       <c r="B116" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C116" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D116" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F116" t="s">
-        <v>565</v>
-      </c>
-      <c r="G116" t="s">
-        <v>17</v>
-      </c>
-      <c r="H116" t="s">
-        <v>17</v>
+        <v>1002</v>
       </c>
       <c r="J116" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="L116" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A117" s="4">
         <v>45386</v>
       </c>
       <c r="B117" t="s">
         <v>179</v>
       </c>
       <c r="C117" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D117" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F117" t="s">
-        <v>568</v>
+        <v>1003</v>
       </c>
       <c r="G117" t="s">
-        <v>51</v>
+        <v>1004</v>
       </c>
       <c r="H117" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J117" t="s">
         <v>51</v>
       </c>
       <c r="K117" t="s">
+        <v>564</v>
+      </c>
+      <c r="L117" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A118" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B118" t="s">
+        <v>566</v>
+      </c>
+      <c r="C118" t="s">
+        <v>567</v>
+      </c>
+      <c r="D118" t="s">
+        <v>568</v>
+      </c>
+      <c r="F118" t="s">
         <v>569</v>
       </c>
-      <c r="L117" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>45386</v>
-      </c>
-      <c r="B118" t="s">
-        <v>571</v>
-      </c>
-      <c r="C118" t="s">
-        <v>572</v>
-      </c>
-      <c r="D118" t="s">
-        <v>573</v>
-      </c>
-      <c r="F118" t="s">
-        <v>574</v>
-      </c>
       <c r="G118" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="H118" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="J118" t="s">
         <v>51</v>
       </c>
       <c r="K118" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="L118" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A119" s="4">
         <v>45386</v>
       </c>
       <c r="B119" t="s">
+        <v>453</v>
+      </c>
+      <c r="C119" t="s">
+        <v>454</v>
+      </c>
+      <c r="D119" t="s">
+        <v>455</v>
+      </c>
+      <c r="F119" t="s">
         <v>456</v>
       </c>
-      <c r="C119" t="s">
-        <v>457</v>
-      </c>
-      <c r="D119" t="s">
-        <v>458</v>
-      </c>
-      <c r="F119" t="s">
-        <v>459</v>
-      </c>
       <c r="G119" t="s">
-        <v>17</v>
+        <v>994</v>
       </c>
       <c r="H119" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J119" t="s">
         <v>17</v>
       </c>
       <c r="K119" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="L119" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A120" s="4">
         <v>45386</v>
       </c>
       <c r="B120" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C120" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D120" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F120" t="s">
-        <v>578</v>
+        <v>1005</v>
       </c>
       <c r="G120" t="s">
-        <v>17</v>
+        <v>1006</v>
       </c>
       <c r="H120" t="s">
-        <v>17</v>
+        <v>927</v>
       </c>
       <c r="J120" t="s">
         <v>17</v>
       </c>
       <c r="L120" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A121" s="4">
         <v>45386</v>
       </c>
       <c r="B121" t="s">
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D121" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="F121" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="G121" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H121" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J121" t="s">
         <v>17</v>
@@ -12739,91 +12742,85 @@
         <v>18</v>
       </c>
       <c r="L121" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A122" s="4">
         <v>45387</v>
       </c>
       <c r="B122" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C122" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D122" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="F122" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="G122" t="s">
-        <v>17</v>
+        <v>939</v>
       </c>
       <c r="H122" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J122" t="s">
         <v>17</v>
       </c>
       <c r="K122" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="L122" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A123" s="4">
         <v>45394</v>
       </c>
       <c r="B123" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C123" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D123" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F123" t="s">
-        <v>591</v>
-      </c>
-      <c r="G123" t="s">
-        <v>328</v>
-      </c>
-      <c r="H123" t="s">
-        <v>328</v>
+        <v>585</v>
       </c>
       <c r="J123" t="s">
         <v>70</v>
       </c>
       <c r="L123" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A124" s="4">
         <v>45469</v>
       </c>
       <c r="B124" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C124" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D124" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F124" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="G124" t="s">
-        <v>51</v>
+        <v>927</v>
       </c>
       <c r="H124" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J124" t="s">
         <v>51</v>
@@ -12832,164 +12829,164 @@
         <v>29</v>
       </c>
       <c r="L124" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A125" s="4">
         <v>45481</v>
       </c>
       <c r="B125" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C125" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D125" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F125" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="G125" t="s">
-        <v>51</v>
+        <v>1007</v>
       </c>
       <c r="H125" t="s">
-        <v>51</v>
+        <v>954</v>
       </c>
       <c r="J125" t="s">
         <v>51</v>
       </c>
       <c r="L125" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126" s="4">
         <v>45483</v>
       </c>
       <c r="B126" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C126" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D126" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E126" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F126" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="G126" t="s">
-        <v>51</v>
+        <v>962</v>
       </c>
       <c r="H126" t="s">
-        <v>51</v>
+        <v>963</v>
       </c>
       <c r="J126" t="s">
         <v>51</v>
       </c>
       <c r="K126" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L126" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>607</v>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A127" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B127" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C127" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D127" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F127" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G127" t="s">
-        <v>51</v>
+        <v>1008</v>
       </c>
       <c r="H127" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J127" t="s">
         <v>51</v>
       </c>
       <c r="K127" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L127" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>607</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A128" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B128" t="s">
         <v>115</v>
       </c>
       <c r="C128" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D128" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E128" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="F128" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="G128" t="s">
-        <v>615</v>
+        <v>962</v>
       </c>
       <c r="H128" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J128" t="s">
         <v>17</v>
       </c>
       <c r="K128" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="L128" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>607</v>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A129" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B129" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C129" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="D129" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="E129" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="F129" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="G129" t="s">
-        <v>51</v>
+        <v>936</v>
       </c>
       <c r="H129" t="s">
-        <v>51</v>
+        <v>937</v>
       </c>
       <c r="J129" t="s">
         <v>51</v>
@@ -12998,202 +12995,202 @@
         <v>98</v>
       </c>
       <c r="L129" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A130" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B130" t="s">
+        <v>616</v>
+      </c>
+      <c r="C130" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>607</v>
-      </c>
-      <c r="B130" t="s">
-        <v>623</v>
-      </c>
-      <c r="C130" t="s">
-        <v>624</v>
-      </c>
       <c r="D130" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="E130" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="F130" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="G130" t="s">
-        <v>51</v>
+        <v>1009</v>
       </c>
       <c r="H130" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J130" t="s">
         <v>51</v>
       </c>
       <c r="L130" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>607</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A131" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B131" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C131" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="D131" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="E131" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="F131" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="G131" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="H131" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="J131" t="s">
         <v>51</v>
       </c>
       <c r="K131" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="L131" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A132" s="5" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>607</v>
-      </c>
       <c r="B132" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C132" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="D132" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="E132" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="F132" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="G132" t="s">
-        <v>17</v>
+        <v>1010</v>
       </c>
       <c r="H132" t="s">
-        <v>17</v>
+        <v>931</v>
       </c>
       <c r="J132" t="s">
         <v>17</v>
       </c>
       <c r="L132" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>607</v>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A133" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B133" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C133" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="D133" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="E133" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="F133" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="G133" t="s">
-        <v>51</v>
+        <v>1011</v>
       </c>
       <c r="H133" t="s">
-        <v>51</v>
+        <v>950</v>
       </c>
       <c r="J133" t="s">
         <v>51</v>
       </c>
       <c r="K133" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="L133" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>607</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A134" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B134" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="C134" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="D134" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="E134" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="F134" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="G134" t="s">
-        <v>51</v>
+        <v>1012</v>
       </c>
       <c r="H134" t="s">
-        <v>51</v>
+        <v>934</v>
       </c>
       <c r="J134" t="s">
         <v>51</v>
       </c>
       <c r="K134" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L134" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>607</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A135" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B135" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C135" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="D135" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="E135" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="F135" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="G135" t="s">
-        <v>51</v>
+        <v>936</v>
       </c>
       <c r="H135" t="s">
-        <v>51</v>
+        <v>937</v>
       </c>
       <c r="J135" t="s">
         <v>51</v>
@@ -13202,1180 +13199,1150 @@
         <v>98</v>
       </c>
       <c r="L135" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>607</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A136" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B136" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C136" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="D136" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="E136" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="F136" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="G136" t="s">
-        <v>51</v>
+        <v>927</v>
       </c>
       <c r="H136" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J136" t="s">
         <v>51</v>
       </c>
       <c r="K136" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="L136" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>607</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A137" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B137" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="C137" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="D137" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E137" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="F137" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="G137" t="s">
-        <v>51</v>
+        <v>992</v>
       </c>
       <c r="H137" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="J137" t="s">
         <v>51</v>
       </c>
       <c r="K137" t="s">
+        <v>658</v>
+      </c>
+      <c r="L137" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A138" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B138" t="s">
+        <v>661</v>
+      </c>
+      <c r="C138" t="s">
+        <v>662</v>
+      </c>
+      <c r="D138" t="s">
+        <v>663</v>
+      </c>
+      <c r="E138" t="s">
+        <v>664</v>
+      </c>
+      <c r="F138" t="s">
         <v>665</v>
       </c>
-      <c r="L137" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>667</v>
-      </c>
-      <c r="B138" t="s">
-        <v>668</v>
-      </c>
-      <c r="C138" t="s">
-        <v>669</v>
-      </c>
-      <c r="D138" t="s">
-        <v>670</v>
-      </c>
-      <c r="E138" t="s">
-        <v>671</v>
-      </c>
-      <c r="F138" t="s">
-        <v>672</v>
-      </c>
       <c r="G138" t="s">
-        <v>51</v>
+        <v>1013</v>
       </c>
       <c r="H138" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="J138" t="s">
         <v>51</v>
       </c>
       <c r="K138" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="L138" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>667</v>
+        <v>666</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A139" s="5" t="s">
+        <v>660</v>
       </c>
       <c r="B139" t="s">
         <v>240</v>
       </c>
       <c r="C139" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="D139" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="E139" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="F139" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="G139" t="s">
-        <v>51</v>
+        <v>962</v>
       </c>
       <c r="H139" t="s">
-        <v>51</v>
+        <v>963</v>
       </c>
       <c r="J139" t="s">
         <v>51</v>
       </c>
       <c r="L139" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>667</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A140" s="5" t="s">
+        <v>660</v>
       </c>
       <c r="B140" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C140" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="D140" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="E140" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="F140" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="G140" t="s">
-        <v>51</v>
+        <v>1014</v>
       </c>
       <c r="H140" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="J140" t="s">
         <v>51</v>
       </c>
       <c r="L140" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>683</v>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A141" s="5" t="s">
+        <v>676</v>
       </c>
       <c r="B141" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="C141" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="D141" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="E141" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="F141" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>1015</v>
       </c>
       <c r="H141" t="s">
-        <v>17</v>
+        <v>927</v>
       </c>
       <c r="J141" t="s">
         <v>17</v>
       </c>
       <c r="L141" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>690</v>
+        <v>682</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A142" s="5" t="s">
+        <v>683</v>
       </c>
       <c r="B142" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C142" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="D142" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="E142" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="F142" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="G142" t="s">
-        <v>17</v>
+        <v>939</v>
       </c>
       <c r="H142" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J142" t="s">
         <v>17</v>
       </c>
       <c r="K142" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="L142" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>698</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A143" s="5" t="s">
+        <v>691</v>
       </c>
       <c r="B143" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="C143" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="D143" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="F143" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="G143" t="s">
-        <v>17</v>
+        <v>1016</v>
       </c>
       <c r="H143" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J143" t="s">
         <v>17</v>
       </c>
       <c r="L143" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A144" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B144" t="s">
+        <v>697</v>
+      </c>
+      <c r="C144" t="s">
         <v>698</v>
       </c>
-      <c r="B144" t="s">
-        <v>704</v>
-      </c>
-      <c r="C144" t="s">
-        <v>705</v>
-      </c>
       <c r="D144" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="F144" t="s">
-        <v>707</v>
-      </c>
-      <c r="G144" t="s">
-        <v>367</v>
-      </c>
-      <c r="H144" t="s">
-        <v>367</v>
+        <v>700</v>
       </c>
       <c r="J144" t="s">
         <v>70</v>
       </c>
       <c r="L144" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A145" s="4">
         <v>45490</v>
       </c>
       <c r="B145" t="s">
         <v>72</v>
       </c>
       <c r="C145" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="D145" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="E145" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="F145" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="G145" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H145" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J145" t="s">
         <v>17</v>
       </c>
       <c r="K145" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="L145" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A146" s="4">
         <v>45490</v>
       </c>
       <c r="B146" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="C146" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="D146" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="E146" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="F146" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>1017</v>
       </c>
       <c r="H146" t="s">
-        <v>17</v>
+        <v>940</v>
       </c>
       <c r="J146" t="s">
         <v>17</v>
       </c>
       <c r="L146" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A147" s="4">
         <v>45490</v>
       </c>
       <c r="B147" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C147" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="D147" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="E147" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="F147" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>956</v>
       </c>
       <c r="H147" t="s">
-        <v>17</v>
+        <v>931</v>
       </c>
       <c r="J147" t="s">
         <v>17</v>
       </c>
       <c r="L147" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A148" s="4">
         <v>45490</v>
       </c>
       <c r="B148" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="C148" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="D148" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="E148" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="F148" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="G148" t="s">
-        <v>51</v>
+        <v>927</v>
       </c>
       <c r="H148" t="s">
-        <v>262</v>
+        <v>996</v>
       </c>
       <c r="J148" t="s">
         <v>51</v>
       </c>
       <c r="K148" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="L148" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A149" s="4">
         <v>45492</v>
       </c>
       <c r="B149" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C149" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="D149" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="E149" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="F149" t="s">
-        <v>734</v>
-      </c>
-      <c r="G149" t="s">
-        <v>328</v>
-      </c>
-      <c r="H149" t="s">
-        <v>328</v>
+        <v>727</v>
       </c>
       <c r="J149" t="s">
         <v>70</v>
       </c>
       <c r="L149" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A150" s="4">
         <v>45492</v>
       </c>
       <c r="B150" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C150" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D150" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="E150" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="F150" t="s">
-        <v>738</v>
-      </c>
-      <c r="G150" t="s">
-        <v>328</v>
-      </c>
-      <c r="H150" t="s">
-        <v>328</v>
+        <v>731</v>
       </c>
       <c r="J150" t="s">
         <v>70</v>
       </c>
       <c r="L150" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A151" s="4">
         <v>45498</v>
       </c>
       <c r="B151" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="C151" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D151" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="F151" t="s">
-        <v>743</v>
-      </c>
-      <c r="G151" t="s">
-        <v>328</v>
-      </c>
-      <c r="H151" t="s">
-        <v>328</v>
+        <v>736</v>
       </c>
       <c r="J151" t="s">
         <v>70</v>
       </c>
       <c r="L151" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A152" s="4">
         <v>45650</v>
       </c>
       <c r="B152" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C152" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="D152" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="E152" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="F152" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="G152" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H152" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J152" t="s">
         <v>17</v>
       </c>
       <c r="K152" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="L152" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A153" s="4">
         <v>45632</v>
       </c>
       <c r="B153" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C153" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="D153" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="E153" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="F153" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="G153" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H153" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J153" t="s">
         <v>17</v>
       </c>
       <c r="L153" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A154" s="4">
         <v>45632</v>
       </c>
       <c r="B154" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="C154" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="D154" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="E154" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="F154" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="G154" t="s">
-        <v>17</v>
+        <v>939</v>
       </c>
       <c r="H154" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J154" t="s">
         <v>17</v>
       </c>
       <c r="K154" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="L154" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A155" s="4">
         <v>45632</v>
       </c>
       <c r="B155" t="s">
         <v>94</v>
       </c>
       <c r="C155" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="D155" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="E155" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="F155" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="G155" t="s">
-        <v>17</v>
+        <v>978</v>
       </c>
       <c r="H155" t="s">
-        <v>17</v>
+        <v>931</v>
       </c>
       <c r="J155" t="s">
         <v>17</v>
       </c>
       <c r="L155" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A156" s="4">
         <v>45632</v>
       </c>
       <c r="B156" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="C156" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="D156" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="E156" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="F156" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="G156" t="s">
-        <v>17</v>
+        <v>943</v>
       </c>
       <c r="H156" t="s">
-        <v>17</v>
+        <v>944</v>
       </c>
       <c r="J156" t="s">
         <v>17</v>
       </c>
       <c r="L156" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A157" s="4">
         <v>45632</v>
       </c>
       <c r="B157" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C157" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="D157" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="E157" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="F157" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="G157" t="s">
-        <v>17</v>
+        <v>939</v>
       </c>
       <c r="H157" t="s">
-        <v>17</v>
+        <v>927</v>
       </c>
       <c r="J157" t="s">
         <v>17</v>
       </c>
       <c r="K157" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="L157" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A158" s="4">
         <v>45635</v>
       </c>
       <c r="B158" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="C158" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="D158" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="E158" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="F158" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G158" t="s">
-        <v>17</v>
+        <v>1018</v>
       </c>
       <c r="H158" t="s">
-        <v>17</v>
+        <v>940</v>
       </c>
       <c r="J158" t="s">
         <v>17</v>
       </c>
       <c r="K158" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="L158" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A159" s="4">
         <v>45635</v>
       </c>
       <c r="B159" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C159" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="D159" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="E159" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F159" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="G159" t="s">
-        <v>51</v>
+        <v>927</v>
       </c>
       <c r="H159" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J159" t="s">
         <v>51</v>
       </c>
       <c r="K159" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L159" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A160" s="4">
         <v>45761</v>
       </c>
       <c r="B160" t="s">
         <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="D160" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="E160" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F160" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="G160" t="s">
-        <v>17</v>
+        <v>1019</v>
       </c>
       <c r="H160" t="s">
-        <v>17</v>
+        <v>927</v>
       </c>
       <c r="J160" t="s">
         <v>17</v>
       </c>
       <c r="L160" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A161" s="4">
         <v>45761</v>
       </c>
       <c r="B161" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="C161" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="D161" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="E161" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="F161" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="G161" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H161" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J161" t="s">
         <v>17</v>
       </c>
       <c r="K161" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="L161" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A162" s="4">
         <v>45761</v>
       </c>
       <c r="B162" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C162" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="D162" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="E162" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="F162" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="G162" t="s">
-        <v>17</v>
+        <v>1020</v>
       </c>
       <c r="H162" t="s">
-        <v>17</v>
+        <v>944</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A163" s="4">
         <v>45762</v>
       </c>
       <c r="B163" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="C163" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="D163" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="E163" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="F163" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="G163" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H163" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J163" t="s">
         <v>17</v>
       </c>
       <c r="L163" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A164" s="4">
         <v>45386</v>
       </c>
       <c r="B164" t="s">
         <v>100</v>
       </c>
       <c r="C164" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="D164" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E164" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="F164" t="s">
-        <v>578</v>
+        <v>1005</v>
       </c>
       <c r="G164" t="s">
-        <v>17</v>
+        <v>1006</v>
       </c>
       <c r="H164" t="s">
-        <v>17</v>
+        <v>927</v>
       </c>
       <c r="J164" t="s">
         <v>17</v>
       </c>
       <c r="L164" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A165" s="4">
         <v>45761</v>
       </c>
       <c r="B165" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C165" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="D165" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="E165" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="F165" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="G165" t="s">
-        <v>17</v>
+        <v>1021</v>
       </c>
       <c r="H165" t="s">
-        <v>17</v>
+        <v>927</v>
       </c>
       <c r="J165" t="s">
         <v>17</v>
       </c>
       <c r="K165" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="L165" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A166" s="4">
         <v>45762</v>
       </c>
       <c r="B166" t="s">
         <v>244</v>
       </c>
       <c r="C166" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="D166" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="F166" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="G166" t="s">
-        <v>17</v>
+        <v>943</v>
       </c>
       <c r="H166" t="s">
-        <v>17</v>
+        <v>944</v>
       </c>
       <c r="J166" t="s">
         <v>17</v>
       </c>
       <c r="L166" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A167" s="4">
         <v>45762</v>
       </c>
       <c r="B167" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="C167" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="D167" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="E167" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="F167" t="s">
-        <v>824</v>
-      </c>
-      <c r="G167" t="s">
-        <v>328</v>
-      </c>
-      <c r="H167" t="s">
-        <v>328</v>
+        <v>817</v>
       </c>
       <c r="J167" t="s">
         <v>70</v>
       </c>
       <c r="L167" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A168" s="4">
         <v>45762</v>
       </c>
       <c r="B168" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="C168" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="D168" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="E168" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="F168" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="G168" t="s">
-        <v>17</v>
+        <v>994</v>
       </c>
       <c r="H168" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J168" t="s">
         <v>17</v>
       </c>
       <c r="L168" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A169" s="4">
         <v>45762</v>
       </c>
       <c r="B169" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="C169" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="D169" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="E169" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="F169" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G169" t="s">
-        <v>17</v>
+        <v>1022</v>
       </c>
       <c r="H169" t="s">
-        <v>17</v>
+        <v>937</v>
       </c>
       <c r="J169" t="s">
         <v>17</v>
       </c>
       <c r="L169" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
-        <v>45397</v>
+        <v>827</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A170" s="4" t="s">
+        <v>1023</v>
       </c>
       <c r="B170" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="C170" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="D170" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="E170" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="F170" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="G170" t="s">
-        <v>51</v>
+        <v>1024</v>
       </c>
       <c r="H170" t="s">
-        <v>51</v>
+        <v>934</v>
       </c>
       <c r="J170" t="s">
         <v>51</v>
       </c>
       <c r="L170" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
-        <v>45397</v>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A171" s="4" t="s">
+        <v>1023</v>
       </c>
       <c r="B171" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="C171" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="D171" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="E171" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="F171" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="G171" t="s">
-        <v>51</v>
+        <v>997</v>
       </c>
       <c r="H171" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J171" t="s">
         <v>51</v>
@@ -14384,537 +14351,519 @@
         <v>83</v>
       </c>
       <c r="L171" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
-        <v>45397</v>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A172" s="4" t="s">
+        <v>1023</v>
       </c>
       <c r="B172" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C172" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D172" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="E172" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="F172" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="G172" t="s">
-        <v>51</v>
+        <v>1025</v>
       </c>
       <c r="H172" t="s">
-        <v>51</v>
+        <v>954</v>
       </c>
       <c r="J172" t="s">
         <v>51</v>
       </c>
       <c r="K172" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="L172" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>45397</v>
+        <v>843</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A173" s="4" t="s">
+        <v>1023</v>
       </c>
       <c r="B173" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="C173" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="D173" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="E173" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="F173" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="G173" t="s">
-        <v>17</v>
+        <v>935</v>
       </c>
       <c r="H173" t="s">
-        <v>17</v>
+        <v>935</v>
       </c>
       <c r="J173" t="s">
         <v>17</v>
       </c>
       <c r="L173" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>45397</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A174" s="4" t="s">
+        <v>1023</v>
       </c>
       <c r="B174" t="s">
         <v>40</v>
       </c>
       <c r="C174" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="D174" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="E174" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="F174" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="G174" t="s">
-        <v>17</v>
+        <v>941</v>
       </c>
       <c r="H174" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J174" t="s">
         <v>17</v>
       </c>
       <c r="L174" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A175" s="4">
         <v>45762</v>
       </c>
       <c r="B175" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="C175" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D175" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="E175" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="F175" t="s">
-        <v>864</v>
+        <v>1026</v>
       </c>
       <c r="G175" t="s">
-        <v>51</v>
+        <v>962</v>
       </c>
       <c r="H175" t="s">
-        <v>51</v>
+        <v>963</v>
       </c>
       <c r="J175" t="s">
         <v>51</v>
       </c>
       <c r="K175" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="L175" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A176" s="4">
         <v>45762</v>
       </c>
       <c r="B176" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C176" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="D176" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="E176" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="F176" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="G176" t="s">
-        <v>17</v>
+        <v>939</v>
       </c>
       <c r="H176" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J176" t="s">
         <v>17</v>
       </c>
       <c r="K176" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="L176" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A177" s="4">
         <v>45762</v>
       </c>
       <c r="B177" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="C177" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="D177" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="E177" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="F177" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="G177" t="s">
-        <v>17</v>
+        <v>939</v>
       </c>
       <c r="H177" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J177" t="s">
         <v>17</v>
       </c>
       <c r="K177" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="L177" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A178" s="4">
         <v>45762</v>
       </c>
       <c r="B178" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="C178" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="D178" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E178" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F178" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="G178" t="s">
-        <v>17</v>
+        <v>943</v>
       </c>
       <c r="H178" t="s">
-        <v>17</v>
+        <v>944</v>
       </c>
       <c r="J178" t="s">
         <v>17</v>
       </c>
       <c r="L178" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A179" s="4">
         <v>45762</v>
       </c>
       <c r="B179" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="C179" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="D179" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="E179" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="F179" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="G179" t="s">
-        <v>17</v>
+        <v>969</v>
       </c>
       <c r="H179" t="s">
-        <v>17</v>
+        <v>956</v>
       </c>
       <c r="J179" t="s">
         <v>17</v>
       </c>
       <c r="L179" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A180" s="4">
         <v>45762</v>
       </c>
       <c r="B180" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C180" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="D180" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="E180" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="F180" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="G180" t="s">
-        <v>17</v>
+        <v>943</v>
       </c>
       <c r="H180" t="s">
-        <v>17</v>
+        <v>944</v>
       </c>
       <c r="J180" t="s">
         <v>17</v>
       </c>
       <c r="L180" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A181" s="4">
         <v>45762</v>
       </c>
       <c r="B181" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="C181" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D181" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="E181" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="F181" t="s">
-        <v>797</v>
-      </c>
-      <c r="G181" t="s">
-        <v>328</v>
-      </c>
-      <c r="H181" t="s">
-        <v>328</v>
+        <v>790</v>
       </c>
       <c r="J181" t="s">
         <v>70</v>
       </c>
       <c r="L181" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A182" s="4">
         <v>45762</v>
       </c>
       <c r="B182" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="C182" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="D182" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="E182" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="F182" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="G182" t="s">
-        <v>51</v>
+        <v>1027</v>
       </c>
       <c r="H182" t="s">
-        <v>51</v>
+        <v>934</v>
       </c>
       <c r="J182" t="s">
         <v>51</v>
       </c>
       <c r="K182" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="L182" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A183" s="4">
         <v>45762</v>
       </c>
       <c r="B183" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="C183" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="D183" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="E183" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="F183" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="G183" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="H183" t="s">
-        <v>51</v>
+        <v>960</v>
       </c>
       <c r="J183" t="s">
         <v>51</v>
       </c>
       <c r="K183" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="L183" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A184" s="4">
         <v>45762</v>
       </c>
       <c r="B184" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="C184" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D184" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="F184" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="G184" t="s">
-        <v>51</v>
+        <v>927</v>
       </c>
       <c r="H184" t="s">
-        <v>51</v>
+        <v>996</v>
       </c>
       <c r="J184" t="s">
         <v>51</v>
       </c>
       <c r="K184" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="L184" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A185" s="4">
         <v>45763</v>
       </c>
       <c r="B185" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="C185" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="D185" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="E185" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="F185" t="s">
-        <v>917</v>
-      </c>
-      <c r="G185" t="s">
-        <v>328</v>
-      </c>
-      <c r="H185" t="s">
-        <v>328</v>
+        <v>909</v>
       </c>
       <c r="J185" t="s">
         <v>70</v>
       </c>
       <c r="L185" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A186" s="4">
         <v>45764</v>
       </c>
       <c r="B186" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="C186" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="D186" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="F186" t="s">
-        <v>922</v>
-      </c>
-      <c r="G186" t="s">
-        <v>328</v>
-      </c>
-      <c r="H186" t="s">
-        <v>328</v>
+        <v>914</v>
       </c>
       <c r="J186" t="s">
         <v>70</v>
       </c>
       <c r="L186" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A187" s="4">
         <v>45764</v>
       </c>
       <c r="B187" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="C187" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="D187" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="E187" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="F187" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="G187" t="s">
-        <v>17</v>
+        <v>1028</v>
       </c>
       <c r="H187" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="J187" t="s">
         <v>17</v>
       </c>
       <c r="K187" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="L187" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
     </row>
   </sheetData>

--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="1045">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -353,9 +353,6 @@
     <t>Disparité départementales de pauvreté en Côte d'Ivoire : une analyse à partir de l'économétrie spatiale</t>
   </si>
   <si>
-    <t>Pauvreté</t>
-  </si>
-  <si>
     <t>MEL</t>
   </si>
   <si>
@@ -617,12 +614,6 @@
     <t xml:space="preserve">Analyse et Diagnostic du processus de bancarisation du secteur informel : cas de la Côte d'ivoire </t>
   </si>
   <si>
-    <t xml:space="preserve">bancarisation du secteur informel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economie informel </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 2021-11-05 00:00:00</t>
   </si>
   <si>
@@ -635,15 +626,6 @@
     <t xml:space="preserve">DJEDJE Marcelle Noura </t>
   </si>
   <si>
-    <t xml:space="preserve">L'employabilité des jeunes demandeurs d'emploi en Côte d'ivoire </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employabilité des jeunes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economie Social </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 2021-11 -22 00:00:00</t>
   </si>
   <si>
@@ -2813,12 +2795,6 @@
     <t xml:space="preserve">Audit immobilier </t>
   </si>
   <si>
-    <t>Les énergies renouvelables</t>
-  </si>
-  <si>
-    <t>Développement durable</t>
-  </si>
-  <si>
     <t xml:space="preserve">Comptabilité et gestion financière </t>
   </si>
   <si>
@@ -3111,6 +3087,78 @@
   </si>
   <si>
     <t>Système de pilotage de performance</t>
+  </si>
+  <si>
+    <t>Environnement et croissance</t>
+  </si>
+  <si>
+    <t>Croissance économique et productivité globale</t>
+  </si>
+  <si>
+    <t>Mesure et analyse de la pauvreté</t>
+  </si>
+  <si>
+    <t>Bien être et pauvreté</t>
+  </si>
+  <si>
+    <t>Developpement économique</t>
+  </si>
+  <si>
+    <t>Secteur formel et informel</t>
+  </si>
+  <si>
+    <t>L'employabilité des jeunes demandeurs d'emploi en Côte d'ivoire</t>
+  </si>
+  <si>
+    <t>Capital humain</t>
+  </si>
+  <si>
+    <t>Economie du travail</t>
+  </si>
+  <si>
+    <t>Croissance Economique et Productivité Aggregée</t>
+  </si>
+  <si>
+    <t>Mesure de la croissance Économique et productivité globale</t>
+  </si>
+  <si>
+    <t>Développement économique</t>
+  </si>
+  <si>
+    <t>Développement financier et marchés financiers</t>
+  </si>
+  <si>
+    <t>Economie agricole</t>
+  </si>
+  <si>
+    <t>Micro-Analyse des Entreprises Agricoles et des Ménages Agricoles</t>
+  </si>
+  <si>
+    <t>Economie environnemental</t>
+  </si>
+  <si>
+    <t>Environnement et Développement</t>
+  </si>
+  <si>
+    <t>Croissance économique des économies ouvertes</t>
+  </si>
+  <si>
+    <t>Commerce International</t>
+  </si>
+  <si>
+    <t>Commerce et environnement</t>
+  </si>
+  <si>
+    <t>Dépenses du gouvernement national et Politiques économique</t>
+  </si>
+  <si>
+    <t>Fiscalité, Subventions et Revenus</t>
+  </si>
+  <si>
+    <t>Economie publique</t>
+  </si>
+  <si>
+    <t>Institutions et Services Financiers</t>
   </si>
 </sst>
 </file>
@@ -4527,7 +4575,7 @@
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr/>
+  <sheetPr codeName="Graphique1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -8204,6 +8252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Feuil2"/>
   <dimension ref="A3:C76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8220,7 +8269,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -8250,7 +8299,7 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -8261,7 +8310,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -8283,7 +8332,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -8294,7 +8343,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -8305,7 +8354,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -8327,7 +8376,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -8338,7 +8387,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -8349,7 +8398,7 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -8360,7 +8409,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -8371,7 +8420,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -8382,7 +8431,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -8393,7 +8442,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -8404,7 +8453,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -8426,7 +8475,7 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -8437,7 +8486,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -8448,7 +8497,7 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -8459,7 +8508,7 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -8470,7 +8519,7 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -8481,7 +8530,7 @@
         <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -8492,7 +8541,7 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -8503,7 +8552,7 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -8514,7 +8563,7 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -8525,7 +8574,7 @@
         <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -8536,7 +8585,7 @@
         <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -8547,7 +8596,7 @@
         <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -8558,7 +8607,7 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -8569,7 +8618,7 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -8580,7 +8629,7 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -8591,7 +8640,7 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -8602,7 +8651,7 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -8613,7 +8662,7 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -8635,7 +8684,7 @@
         <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -8668,7 +8717,7 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -8679,7 +8728,7 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -8690,7 +8739,7 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -8701,7 +8750,7 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -8723,7 +8772,7 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -8745,7 +8794,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -8756,7 +8805,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -8767,7 +8816,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -8778,7 +8827,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -8789,7 +8838,7 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -8800,7 +8849,7 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -8811,7 +8860,7 @@
         <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C57">
         <v>6</v>
@@ -8822,7 +8871,7 @@
         <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -8833,7 +8882,7 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -8866,7 +8915,7 @@
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -8877,7 +8926,7 @@
         <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -8888,7 +8937,7 @@
         <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -8899,7 +8948,7 @@
         <v>51</v>
       </c>
       <c r="B65" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -8910,7 +8959,7 @@
         <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -8932,7 +8981,7 @@
         <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -8943,7 +8992,7 @@
         <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -8954,7 +9003,7 @@
         <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -8965,7 +9014,7 @@
         <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -8976,7 +9025,7 @@
         <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -9009,7 +9058,7 @@
         <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -9020,7 +9069,7 @@
         <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -9037,20 +9086,20 @@
   <dimension ref="A1:N187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="142.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.54296875" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="144" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="56.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="50.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -9079,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -9114,13 +9163,13 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="H2" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="I2" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -9152,19 +9201,19 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H3" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="I3" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M3" s="2">
         <v>44146</v>
@@ -9190,13 +9239,13 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="H4" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="I4" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -9228,13 +9277,13 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H5" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="I5" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -9266,13 +9315,13 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H6" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="I6" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -9304,13 +9353,13 @@
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H7" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="I7" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -9342,13 +9391,13 @@
         <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="H8" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="I8" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -9380,16 +9429,16 @@
         <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="H9" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J9" t="s">
         <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M9" s="2">
         <v>44186</v>
@@ -9415,10 +9464,10 @@
         <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H10" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J10" t="s">
         <v>51</v>
@@ -9450,10 +9499,10 @@
         <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H11" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J11" t="s">
         <v>51</v>
@@ -9485,10 +9534,10 @@
         <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>929</v>
+        <v>1021</v>
       </c>
       <c r="H12" t="s">
-        <v>930</v>
+        <v>1022</v>
       </c>
       <c r="J12" t="s">
         <v>70</v>
@@ -9517,10 +9566,10 @@
         <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="H13" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -9552,10 +9601,10 @@
         <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="H14" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -9587,10 +9636,10 @@
         <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H15" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -9619,10 +9668,10 @@
         <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H16" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J16" t="s">
         <v>51</v>
@@ -9654,10 +9703,10 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H17" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J17" t="s">
         <v>51</v>
@@ -9689,10 +9738,10 @@
         <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="H18" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J18" t="s">
         <v>51</v>
@@ -9724,10 +9773,10 @@
         <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>1023</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>1024</v>
       </c>
       <c r="J19" t="s">
         <v>70</v>
@@ -9744,28 +9793,28 @@
         <v>78</v>
       </c>
       <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
         <v>110</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>111</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>112</v>
       </c>
-      <c r="F20" t="s">
-        <v>113</v>
-      </c>
       <c r="G20" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="H20" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J20" t="s">
         <v>51</v>
       </c>
       <c r="K20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M20" t="s">
         <v>58</v>
@@ -9779,22 +9828,22 @@
         <v>78</v>
       </c>
       <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
         <v>115</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>116</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>117</v>
       </c>
-      <c r="F21" t="s">
-        <v>118</v>
-      </c>
       <c r="G21" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="H21" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="J21" t="s">
         <v>51</v>
@@ -9814,28 +9863,28 @@
         <v>78</v>
       </c>
       <c r="B22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
         <v>119</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>120</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>121</v>
       </c>
-      <c r="F22" t="s">
-        <v>122</v>
-      </c>
       <c r="G22" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H22" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J22" t="s">
         <v>51</v>
       </c>
       <c r="K22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M22" t="s">
         <v>64</v>
@@ -9849,28 +9898,28 @@
         <v>78</v>
       </c>
       <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
         <v>124</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>125</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>126</v>
       </c>
-      <c r="F23" t="s">
-        <v>127</v>
-      </c>
       <c r="G23" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="H23" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M23" t="s">
         <v>77</v>
@@ -9881,31 +9930,31 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
         <v>129</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>130</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>131</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>132</v>
       </c>
-      <c r="F24" t="s">
-        <v>133</v>
-      </c>
       <c r="G24" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H24" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J24" t="s">
         <v>51</v>
       </c>
       <c r="K24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M24" t="s">
         <v>58</v>
@@ -9916,31 +9965,31 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
         <v>135</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>136</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>137</v>
       </c>
-      <c r="F25" t="s">
-        <v>138</v>
-      </c>
       <c r="G25" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H25" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M25" t="s">
         <v>84</v>
@@ -9951,95 +10000,95 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
         <v>140</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>141</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>142</v>
       </c>
-      <c r="F26" t="s">
-        <v>143</v>
-      </c>
       <c r="G26" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H26" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M26" t="s">
         <v>58</v>
       </c>
       <c r="N26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
         <v>146</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>147</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>148</v>
       </c>
-      <c r="F27" t="s">
-        <v>149</v>
-      </c>
       <c r="G27" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H27" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J27" t="s">
         <v>51</v>
       </c>
       <c r="K27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M27" t="s">
         <v>58</v>
       </c>
       <c r="N27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
         <v>150</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>151</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>152</v>
       </c>
-      <c r="F28" t="s">
-        <v>153</v>
-      </c>
       <c r="G28" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="H28" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -10048,30 +10097,30 @@
         <v>64</v>
       </c>
       <c r="N28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
         <v>155</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>156</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>157</v>
       </c>
-      <c r="D29" t="s">
-        <v>158</v>
-      </c>
       <c r="F29" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="G29" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H29" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -10082,141 +10131,141 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" t="s">
         <v>159</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>160</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>161</v>
       </c>
-      <c r="F30" t="s">
-        <v>162</v>
-      </c>
       <c r="G30" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H30" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
       </c>
       <c r="K30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" t="s">
         <v>164</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>165</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>166</v>
       </c>
-      <c r="F31" t="s">
-        <v>167</v>
-      </c>
       <c r="G31" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H31" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J31" t="s">
         <v>51</v>
       </c>
       <c r="K31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" t="s">
         <v>169</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>170</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>171</v>
       </c>
-      <c r="F32" t="s">
-        <v>172</v>
-      </c>
       <c r="G32" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="H32" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" t="s">
         <v>174</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>175</v>
       </c>
-      <c r="D33" t="s">
-        <v>176</v>
-      </c>
       <c r="F33" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="G33" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="H33" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="J33" t="s">
         <v>51</v>
       </c>
       <c r="K33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" t="s">
         <v>178</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>179</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>180</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>181</v>
       </c>
-      <c r="F34" t="s">
-        <v>182</v>
-      </c>
       <c r="G34" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="H34" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
@@ -10224,48 +10273,54 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" t="s">
         <v>183</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>184</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>185</v>
       </c>
-      <c r="F35" t="s">
-        <v>186</v>
-      </c>
       <c r="G35" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="H35" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" t="s">
         <v>188</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>189</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>190</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>191</v>
       </c>
-      <c r="F36" t="s">
-        <v>192</v>
+      <c r="G36" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1024</v>
       </c>
       <c r="J36" t="s">
         <v>70</v>
@@ -10276,25 +10331,25 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" t="s">
         <v>193</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>194</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>195</v>
       </c>
-      <c r="F37" t="s">
-        <v>196</v>
-      </c>
       <c r="G37" t="s">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>1025</v>
       </c>
       <c r="J37" t="s">
         <v>70</v>
@@ -10305,25 +10360,25 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>197</v>
+      </c>
+      <c r="C38" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" t="s">
         <v>199</v>
       </c>
-      <c r="B38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C38" t="s">
-        <v>201</v>
-      </c>
-      <c r="D38" t="s">
-        <v>202</v>
-      </c>
       <c r="F38" t="s">
-        <v>203</v>
+        <v>1027</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>1028</v>
       </c>
       <c r="H38" t="s">
-        <v>205</v>
+        <v>1029</v>
       </c>
       <c r="J38" t="s">
         <v>70</v>
@@ -10331,83 +10386,83 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D39" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F39" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="G39" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H39" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F40" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G40" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="H40" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
         <v>211</v>
       </c>
-      <c r="B41" t="s">
-        <v>217</v>
-      </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D41" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F41" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G41" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H41" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J41" t="s">
         <v>51</v>
@@ -10418,54 +10473,54 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D42" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F42" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G42" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H42" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F43" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="G43" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H43" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J43" t="s">
         <v>51</v>
@@ -10476,25 +10531,25 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C44" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D44" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F44" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G44" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="H44" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J44" t="s">
         <v>51</v>
@@ -10505,95 +10560,95 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B45" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C45" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D45" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F45" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G45" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H45" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J45" t="s">
         <v>51</v>
       </c>
       <c r="K45" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D46" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F46" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G46" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H46" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J46" t="s">
         <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C47" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D47" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F47" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G47" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H47" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="L47" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
@@ -10601,31 +10656,31 @@
         <v>44524</v>
       </c>
       <c r="B48" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C48" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D48" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F48" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G48" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="H48" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="L48" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
@@ -10633,22 +10688,22 @@
         <v>44191</v>
       </c>
       <c r="B49" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D49" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F49" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G49" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="H49" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J49" t="s">
         <v>51</v>
@@ -10659,31 +10714,31 @@
         <v>44526</v>
       </c>
       <c r="B50" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D50" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F50" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G50" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="H50" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="J50" t="s">
         <v>51</v>
       </c>
       <c r="K50" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="L50" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
@@ -10691,31 +10746,31 @@
         <v>44191</v>
       </c>
       <c r="B51" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C51" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F51" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G51" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="H51" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J51" t="s">
         <v>51</v>
       </c>
       <c r="K51" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L51" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
@@ -10723,31 +10778,31 @@
         <v>44612</v>
       </c>
       <c r="B52" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C52" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D52" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F52" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G52" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="H52" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J52" t="s">
         <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L52" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
@@ -10755,22 +10810,22 @@
         <v>44620</v>
       </c>
       <c r="B53" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C53" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D53" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F53" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G53" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="H53" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J53" t="s">
         <v>51</v>
@@ -10779,7 +10834,7 @@
         <v>98</v>
       </c>
       <c r="L53" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
@@ -10790,28 +10845,28 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D54" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F54" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G54" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="H54" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J54" t="s">
         <v>51</v>
       </c>
       <c r="K54" t="s">
+        <v>262</v>
+      </c>
+      <c r="L54" t="s">
         <v>268</v>
-      </c>
-      <c r="L54" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
@@ -10819,31 +10874,31 @@
         <v>44255</v>
       </c>
       <c r="B55" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C55" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D55" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F55" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="G55" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="H55" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J55" t="s">
         <v>51</v>
       </c>
       <c r="K55" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L55" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
@@ -10851,31 +10906,31 @@
         <v>44255</v>
       </c>
       <c r="B56" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D56" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F56" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="G56" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="H56" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J56" t="s">
         <v>51</v>
       </c>
       <c r="K56" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="L56" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
@@ -10883,28 +10938,28 @@
         <v>44255</v>
       </c>
       <c r="B57" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C57" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D57" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F57" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="G57" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="H57" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
       </c>
       <c r="L57" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
@@ -10912,22 +10967,22 @@
         <v>44255</v>
       </c>
       <c r="B58" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C58" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D58" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F58" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G58" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="H58" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -10936,7 +10991,7 @@
         <v>98</v>
       </c>
       <c r="L58" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
@@ -10944,31 +10999,31 @@
         <v>44255</v>
       </c>
       <c r="B59" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C59" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D59" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F59" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G59" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H59" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J59" t="s">
         <v>51</v>
       </c>
       <c r="K59" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="L59" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
@@ -10976,31 +11031,31 @@
         <v>44620</v>
       </c>
       <c r="B60" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C60" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D60" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F60" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G60" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="H60" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J60" t="s">
         <v>51</v>
       </c>
       <c r="K60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L60" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
@@ -11008,31 +11063,31 @@
         <v>44620</v>
       </c>
       <c r="B61" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C61" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D61" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F61" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G61" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="H61" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J61" t="s">
         <v>51</v>
       </c>
       <c r="K61" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="L61" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
@@ -11040,28 +11095,28 @@
         <v>44620</v>
       </c>
       <c r="B62" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C62" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D62" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F62" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G62" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="H62" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J62" t="s">
         <v>51</v>
       </c>
       <c r="L62" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
@@ -11069,31 +11124,31 @@
         <v>44620</v>
       </c>
       <c r="B63" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C63" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F63" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G63" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="H63" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J63" t="s">
         <v>51</v>
       </c>
       <c r="K63" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L63" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
@@ -11101,22 +11156,28 @@
         <v>44620</v>
       </c>
       <c r="B64" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C64" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="F64" t="s">
-        <v>326</v>
+        <v>320</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1025</v>
       </c>
       <c r="J64" t="s">
         <v>70</v>
       </c>
       <c r="L64" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
@@ -11124,31 +11185,31 @@
         <v>44620</v>
       </c>
       <c r="B65" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C65" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D65" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F65" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="G65" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="H65" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J65" t="s">
         <v>51</v>
       </c>
       <c r="K65" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L65" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
@@ -11156,28 +11217,28 @@
         <v>44620</v>
       </c>
       <c r="B66" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C66" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F66" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G66" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="H66" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J66" t="s">
         <v>51</v>
       </c>
       <c r="L66" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
@@ -11185,22 +11246,28 @@
         <v>44623</v>
       </c>
       <c r="B67" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C67" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D67" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F67" t="s">
-        <v>340</v>
+        <v>334</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1030</v>
       </c>
       <c r="J67" t="s">
         <v>70</v>
       </c>
       <c r="L67" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
@@ -11208,34 +11275,34 @@
         <v>44833</v>
       </c>
       <c r="B68" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C68" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D68" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E68">
         <v>767469615</v>
       </c>
       <c r="F68" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="G68" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="H68" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J68" t="s">
         <v>51</v>
       </c>
       <c r="K68" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="L68" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
@@ -11243,31 +11310,31 @@
         <v>44833</v>
       </c>
       <c r="B69" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C69" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D69" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F69" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G69" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="H69" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="L69" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
@@ -11275,34 +11342,34 @@
         <v>44844</v>
       </c>
       <c r="B70" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C70" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D70" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E70">
         <v>102989154</v>
       </c>
       <c r="F70" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G70" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="H70" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L70" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
@@ -11310,28 +11377,28 @@
         <v>44620</v>
       </c>
       <c r="B71" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C71" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D71" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="F71" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G71" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="H71" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
       </c>
       <c r="L71" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
@@ -11339,25 +11406,31 @@
         <v>44844</v>
       </c>
       <c r="B72" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C72" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D72" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E72">
         <v>787347707</v>
       </c>
       <c r="F72" t="s">
-        <v>364</v>
+        <v>358</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1032</v>
       </c>
       <c r="J72" t="s">
         <v>70</v>
       </c>
       <c r="L72" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
@@ -11365,25 +11438,31 @@
         <v>44844</v>
       </c>
       <c r="B73" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C73" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D73" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E73">
         <v>141583425</v>
       </c>
       <c r="F73" t="s">
-        <v>369</v>
+        <v>363</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1034</v>
       </c>
       <c r="J73" t="s">
         <v>70</v>
       </c>
       <c r="L73" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
@@ -11391,25 +11470,31 @@
         <v>44844</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D74" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E74">
         <v>758422493</v>
       </c>
       <c r="F74" t="s">
-        <v>373</v>
+        <v>367</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1036</v>
       </c>
       <c r="J74" t="s">
         <v>70</v>
       </c>
       <c r="L74" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
@@ -11417,22 +11502,22 @@
         <v>44944</v>
       </c>
       <c r="B75" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C75" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D75" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F75" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G75" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="H75" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="J75" t="s">
         <v>51</v>
@@ -11441,7 +11526,7 @@
         <v>98</v>
       </c>
       <c r="L75" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
@@ -11449,22 +11534,28 @@
         <v>44945</v>
       </c>
       <c r="B76" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C76" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D76" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="F76" t="s">
-        <v>382</v>
+        <v>376</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1039</v>
       </c>
       <c r="J76" t="s">
         <v>70</v>
       </c>
       <c r="L76" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
@@ -11472,28 +11563,28 @@
         <v>44945</v>
       </c>
       <c r="B77" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C77" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D77" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F77" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G77" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="H77" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
       </c>
       <c r="L77" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
@@ -11504,25 +11595,25 @@
         <v>88</v>
       </c>
       <c r="C78" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D78" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="F78" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G78" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H78" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J78" t="s">
         <v>17</v>
       </c>
       <c r="L78" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
@@ -11530,22 +11621,28 @@
         <v>44844</v>
       </c>
       <c r="B79" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C79" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D79" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F79" t="s">
-        <v>394</v>
+        <v>388</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1039</v>
       </c>
       <c r="J79" t="s">
         <v>70</v>
       </c>
       <c r="L79" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
@@ -11556,19 +11653,25 @@
         <v>100</v>
       </c>
       <c r="C80" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D80" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="F80" t="s">
-        <v>397</v>
+        <v>391</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1043</v>
       </c>
       <c r="J80" t="s">
         <v>70</v>
       </c>
       <c r="L80" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
@@ -11579,25 +11682,25 @@
         <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D81" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="F81" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="G81" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="H81" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J81" t="s">
         <v>17</v>
       </c>
       <c r="L81" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
@@ -11605,34 +11708,34 @@
         <v>44957</v>
       </c>
       <c r="B82" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C82" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D82" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E82">
         <v>767469615</v>
       </c>
       <c r="F82" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="G82" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="H82" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
       </c>
       <c r="K82" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="L82" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
@@ -11640,22 +11743,28 @@
         <v>45013</v>
       </c>
       <c r="B83" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D83" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="F83" t="s">
-        <v>410</v>
+        <v>404</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H83" t="s">
+        <v>1043</v>
       </c>
       <c r="J83" t="s">
         <v>70</v>
       </c>
       <c r="L83" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
@@ -11663,22 +11772,28 @@
         <v>45013</v>
       </c>
       <c r="B84" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C84" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D84" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="F84" t="s">
-        <v>415</v>
+        <v>409</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H84" t="s">
+        <v>1034</v>
       </c>
       <c r="J84" t="s">
         <v>70</v>
       </c>
       <c r="L84" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
@@ -11686,31 +11801,31 @@
         <v>45386</v>
       </c>
       <c r="B85" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C85" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D85" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F85" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G85" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="H85" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J85" t="s">
         <v>51</v>
       </c>
       <c r="K85" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="L85" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
@@ -11718,31 +11833,31 @@
         <v>45103</v>
       </c>
       <c r="B86" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C86" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="F86" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="G86" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="H86" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J86" t="s">
         <v>51</v>
       </c>
       <c r="K86" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L86" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
@@ -11753,19 +11868,25 @@
         <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D87" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="F87" t="s">
-        <v>430</v>
+        <v>424</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H87" t="s">
+        <v>1025</v>
       </c>
       <c r="J87" t="s">
         <v>70</v>
       </c>
       <c r="L87" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
@@ -11773,22 +11894,22 @@
         <v>45107</v>
       </c>
       <c r="B88" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C88" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D88" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="F88" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="J88" t="s">
         <v>70</v>
       </c>
       <c r="L88" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
@@ -11796,22 +11917,22 @@
         <v>45107</v>
       </c>
       <c r="B89" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C89" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D89" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F89" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="J89" t="s">
         <v>70</v>
       </c>
       <c r="L89" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
@@ -11819,28 +11940,28 @@
         <v>45107</v>
       </c>
       <c r="B90" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C90" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D90" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="F90" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G90" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H90" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
       </c>
       <c r="L90" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
@@ -11851,28 +11972,28 @@
         <v>59</v>
       </c>
       <c r="C91" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F91" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="G91" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="H91" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J91" t="s">
         <v>17</v>
       </c>
       <c r="K91" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="L91" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
@@ -11880,22 +12001,22 @@
         <v>45107</v>
       </c>
       <c r="B92" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C92" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D92" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F92" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="J92" t="s">
         <v>70</v>
       </c>
       <c r="L92" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
@@ -11903,31 +12024,31 @@
         <v>45110</v>
       </c>
       <c r="B93" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C93" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D93" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F93" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="G93" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="H93" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J93" t="s">
         <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="L93" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
@@ -11935,31 +12056,31 @@
         <v>45110</v>
       </c>
       <c r="B94" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C94" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D94" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="F94" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="G94" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H94" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J94" t="s">
         <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="L94" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
@@ -11967,31 +12088,31 @@
         <v>45110</v>
       </c>
       <c r="B95" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C95" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D95" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="F95" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="G95" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="H95" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="J95" t="s">
         <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L95" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
@@ -11999,31 +12120,31 @@
         <v>45110</v>
       </c>
       <c r="B96" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C96" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D96" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="F96" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="G96" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="H96" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J96" t="s">
         <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="L96" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
@@ -12031,31 +12152,31 @@
         <v>45110</v>
       </c>
       <c r="B97" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C97" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D97" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F97" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="G97" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H97" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J97" t="s">
         <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="L97" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
@@ -12063,31 +12184,31 @@
         <v>45110</v>
       </c>
       <c r="B98" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C98" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D98" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F98" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G98" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H98" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J98" t="s">
         <v>17</v>
       </c>
       <c r="K98" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="L98" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
@@ -12095,31 +12216,31 @@
         <v>45110</v>
       </c>
       <c r="B99" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C99" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D99" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="F99" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="G99" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="H99" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J99" t="s">
         <v>51</v>
       </c>
       <c r="K99" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L99" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
@@ -12127,16 +12248,16 @@
         <v>45110</v>
       </c>
       <c r="B100" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C100" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D100" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="F100" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="G100" t="s">
         <v>17</v>
@@ -12148,7 +12269,7 @@
         <v>17</v>
       </c>
       <c r="L100" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
@@ -12156,16 +12277,16 @@
         <v>45111</v>
       </c>
       <c r="B101" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C101" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D101" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F101" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="G101" t="s">
         <v>17</v>
@@ -12177,10 +12298,10 @@
         <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="L101" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
@@ -12188,16 +12309,16 @@
         <v>45112</v>
       </c>
       <c r="B102" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C102" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D102" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F102" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="G102" t="s">
         <v>17</v>
@@ -12209,10 +12330,10 @@
         <v>17</v>
       </c>
       <c r="K102" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="L102" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
@@ -12220,22 +12341,22 @@
         <v>45113</v>
       </c>
       <c r="B103" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C103" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D103" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F103" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="J103" t="s">
         <v>70</v>
       </c>
       <c r="L103" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
@@ -12243,22 +12364,22 @@
         <v>45116</v>
       </c>
       <c r="B104" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C104" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D104" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F104" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J104" t="s">
         <v>70</v>
       </c>
       <c r="L104" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
@@ -12266,22 +12387,22 @@
         <v>45240</v>
       </c>
       <c r="B105" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C105" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D105" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F105" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="J105" t="s">
         <v>70</v>
       </c>
       <c r="L105" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
@@ -12292,28 +12413,28 @@
         <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D106" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="F106" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G106" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="H106" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J106" t="s">
         <v>51</v>
       </c>
       <c r="K106" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="L106" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
@@ -12321,22 +12442,22 @@
         <v>45240</v>
       </c>
       <c r="B107" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C107" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D107" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F107" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="J107" t="s">
         <v>70</v>
       </c>
       <c r="L107" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
@@ -12344,31 +12465,31 @@
         <v>45296</v>
       </c>
       <c r="B108" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C108" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D108" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F108" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="G108" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="H108" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J108" t="s">
         <v>17</v>
       </c>
       <c r="K108" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="L108" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
@@ -12376,31 +12497,31 @@
         <v>45385</v>
       </c>
       <c r="B109" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C109" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D109" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F109" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="G109" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="H109" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J109" t="s">
         <v>51</v>
       </c>
       <c r="K109" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="L109" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
@@ -12408,31 +12529,31 @@
         <v>45385</v>
       </c>
       <c r="B110" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C110" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D110" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F110" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G110" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="H110" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J110" t="s">
         <v>17</v>
       </c>
       <c r="K110" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="L110" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
@@ -12440,22 +12561,22 @@
         <v>45385</v>
       </c>
       <c r="B111" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C111" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D111" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="F111" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G111" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H111" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J111" t="s">
         <v>51</v>
@@ -12464,7 +12585,7 @@
         <v>98</v>
       </c>
       <c r="L111" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
@@ -12472,22 +12593,22 @@
         <v>45385</v>
       </c>
       <c r="B112" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C112" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="D112" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="F112" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J112" t="s">
         <v>70</v>
       </c>
       <c r="L112" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
@@ -12495,22 +12616,22 @@
         <v>45385</v>
       </c>
       <c r="B113" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C113" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D113" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="F113" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="J113" t="s">
         <v>70</v>
       </c>
       <c r="L113" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
@@ -12518,28 +12639,28 @@
         <v>45385</v>
       </c>
       <c r="B114" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C114" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D114" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="F114" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G114" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="H114" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J114" t="s">
         <v>51</v>
       </c>
       <c r="L114" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
@@ -12547,22 +12668,22 @@
         <v>45385</v>
       </c>
       <c r="B115" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C115" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D115" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="F115" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="J115" t="s">
         <v>70</v>
       </c>
       <c r="L115" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
@@ -12570,22 +12691,22 @@
         <v>45385</v>
       </c>
       <c r="B116" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C116" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D116" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F116" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="J116" t="s">
         <v>70</v>
       </c>
       <c r="L116" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
@@ -12593,31 +12714,31 @@
         <v>45386</v>
       </c>
       <c r="B117" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C117" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D117" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F117" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G117" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="H117" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J117" t="s">
         <v>51</v>
       </c>
       <c r="K117" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="L117" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
@@ -12625,31 +12746,31 @@
         <v>45386</v>
       </c>
       <c r="B118" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C118" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D118" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F118" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="G118" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="H118" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J118" t="s">
         <v>51</v>
       </c>
       <c r="K118" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L118" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
@@ -12657,31 +12778,31 @@
         <v>45386</v>
       </c>
       <c r="B119" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C119" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D119" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F119" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="G119" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="H119" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J119" t="s">
         <v>17</v>
       </c>
       <c r="K119" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="L119" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
@@ -12689,28 +12810,28 @@
         <v>45386</v>
       </c>
       <c r="B120" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C120" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D120" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="F120" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G120" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="H120" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J120" t="s">
         <v>17</v>
       </c>
       <c r="L120" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
@@ -12721,19 +12842,19 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D121" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="F121" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="G121" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H121" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J121" t="s">
         <v>17</v>
@@ -12742,7 +12863,7 @@
         <v>18</v>
       </c>
       <c r="L121" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
@@ -12750,31 +12871,31 @@
         <v>45387</v>
       </c>
       <c r="B122" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C122" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D122" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F122" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="G122" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H122" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J122" t="s">
         <v>17</v>
       </c>
       <c r="K122" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="L122" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
@@ -12782,22 +12903,22 @@
         <v>45394</v>
       </c>
       <c r="B123" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C123" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D123" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="F123" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="J123" t="s">
         <v>70</v>
       </c>
       <c r="L123" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
@@ -12805,22 +12926,22 @@
         <v>45469</v>
       </c>
       <c r="B124" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C124" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D124" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="F124" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G124" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H124" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J124" t="s">
         <v>51</v>
@@ -12829,7 +12950,7 @@
         <v>29</v>
       </c>
       <c r="L124" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
@@ -12837,28 +12958,28 @@
         <v>45481</v>
       </c>
       <c r="B125" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C125" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D125" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="F125" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G125" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="H125" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="J125" t="s">
         <v>51</v>
       </c>
       <c r="L125" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
@@ -12866,127 +12987,127 @@
         <v>45483</v>
       </c>
       <c r="B126" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C126" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D126" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="E126" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F126" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="G126" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="H126" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="J126" t="s">
         <v>51</v>
       </c>
       <c r="K126" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L126" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B127" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C127" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D127" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="F127" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="G127" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="H127" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J127" t="s">
         <v>51</v>
       </c>
       <c r="K127" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="L127" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="B128" t="s">
+        <v>114</v>
+      </c>
+      <c r="C128" t="s">
+        <v>599</v>
+      </c>
+      <c r="D128" t="s">
+        <v>600</v>
+      </c>
+      <c r="E128" t="s">
         <v>601</v>
       </c>
-      <c r="B128" t="s">
-        <v>115</v>
-      </c>
-      <c r="C128" t="s">
-        <v>605</v>
-      </c>
-      <c r="D128" t="s">
-        <v>606</v>
-      </c>
-      <c r="E128" t="s">
-        <v>607</v>
-      </c>
       <c r="F128" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="G128" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="H128" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J128" t="s">
         <v>17</v>
       </c>
       <c r="K128" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="L128" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B129" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C129" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D129" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="E129" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="F129" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="G129" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H129" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J129" t="s">
         <v>51</v>
@@ -12995,202 +13116,202 @@
         <v>98</v>
       </c>
       <c r="L129" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B130" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C130" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D130" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="E130" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="F130" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="G130" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="H130" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J130" t="s">
         <v>51</v>
       </c>
       <c r="L130" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B131" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C131" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D131" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E131" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="F131" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="G131" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="H131" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J131" t="s">
         <v>51</v>
       </c>
       <c r="K131" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="L131" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B132" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C132" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D132" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E132" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="F132" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="G132" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="H132" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J132" t="s">
         <v>17</v>
       </c>
       <c r="L132" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B133" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C133" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="D133" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="E133" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F133" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="G133" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="H133" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="J133" t="s">
         <v>51</v>
       </c>
       <c r="K133" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="L133" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B134" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C134" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D134" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E134" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="F134" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="G134" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="H134" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J134" t="s">
         <v>51</v>
       </c>
       <c r="K134" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="L134" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B135" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C135" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D135" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="E135" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="F135" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G135" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H135" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J135" t="s">
         <v>51</v>
@@ -13199,295 +13320,295 @@
         <v>98</v>
       </c>
       <c r="L135" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B136" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C136" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D136" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E136" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="F136" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="G136" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H136" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J136" t="s">
         <v>51</v>
       </c>
       <c r="K136" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L136" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B137" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C137" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D137" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E137" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F137" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="G137" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="H137" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J137" t="s">
         <v>51</v>
       </c>
       <c r="K137" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="L137" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B138" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C138" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="D138" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E138" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="F138" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="G138" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="H138" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J138" t="s">
         <v>51</v>
       </c>
       <c r="K138" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="L138" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B139" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C139" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D139" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E139" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="F139" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="G139" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="H139" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="J139" t="s">
         <v>51</v>
       </c>
       <c r="L139" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B140" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="C140" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D140" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="E140" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F140" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="G140" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="H140" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J140" t="s">
         <v>51</v>
       </c>
       <c r="L140" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B141" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C141" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D141" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E141" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="F141" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="G141" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="H141" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J141" t="s">
         <v>17</v>
       </c>
       <c r="L141" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B142" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C142" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D142" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E142" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="F142" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G142" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H142" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J142" t="s">
         <v>17</v>
       </c>
       <c r="K142" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="L142" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B143" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C143" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D143" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="F143" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="G143" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="H143" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J143" t="s">
         <v>17</v>
       </c>
       <c r="L143" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B144" t="s">
         <v>691</v>
       </c>
-      <c r="B144" t="s">
-        <v>697</v>
-      </c>
       <c r="C144" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="D144" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="F144" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="J144" t="s">
         <v>70</v>
       </c>
       <c r="L144" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.35">
@@ -13498,31 +13619,31 @@
         <v>72</v>
       </c>
       <c r="C145" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D145" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E145" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="F145" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="G145" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H145" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J145" t="s">
         <v>17</v>
       </c>
       <c r="K145" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="L145" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.35">
@@ -13530,31 +13651,31 @@
         <v>45490</v>
       </c>
       <c r="B146" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C146" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D146" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="E146" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="F146" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="G146" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="H146" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J146" t="s">
         <v>17</v>
       </c>
       <c r="L146" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.35">
@@ -13562,31 +13683,31 @@
         <v>45490</v>
       </c>
       <c r="B147" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C147" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D147" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="E147" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="F147" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G147" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="H147" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J147" t="s">
         <v>17</v>
       </c>
       <c r="L147" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
@@ -13594,34 +13715,34 @@
         <v>45490</v>
       </c>
       <c r="B148" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="C148" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D148" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E148" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="F148" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="G148" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H148" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J148" t="s">
         <v>51</v>
       </c>
       <c r="K148" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="L148" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.35">
@@ -13629,25 +13750,25 @@
         <v>45492</v>
       </c>
       <c r="B149" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C149" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D149" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E149" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="F149" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="J149" t="s">
         <v>70</v>
       </c>
       <c r="L149" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
@@ -13655,25 +13776,25 @@
         <v>45492</v>
       </c>
       <c r="B150" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C150" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D150" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E150" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="F150" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J150" t="s">
         <v>70</v>
       </c>
       <c r="L150" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.35">
@@ -13681,22 +13802,22 @@
         <v>45498</v>
       </c>
       <c r="B151" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C151" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="D151" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="F151" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="J151" t="s">
         <v>70</v>
       </c>
       <c r="L151" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.35">
@@ -13704,34 +13825,34 @@
         <v>45650</v>
       </c>
       <c r="B152" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C152" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="D152" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E152" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="F152" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="G152" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H152" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J152" t="s">
         <v>17</v>
       </c>
       <c r="K152" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="L152" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.35">
@@ -13739,31 +13860,31 @@
         <v>45632</v>
       </c>
       <c r="B153" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C153" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="D153" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="E153" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="F153" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G153" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H153" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J153" t="s">
         <v>17</v>
       </c>
       <c r="L153" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.35">
@@ -13771,34 +13892,34 @@
         <v>45632</v>
       </c>
       <c r="B154" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C154" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="D154" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="E154" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="F154" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="G154" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H154" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J154" t="s">
         <v>17</v>
       </c>
       <c r="K154" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="L154" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.35">
@@ -13809,28 +13930,28 @@
         <v>94</v>
       </c>
       <c r="C155" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="D155" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="E155" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="F155" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="G155" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="H155" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="J155" t="s">
         <v>17</v>
       </c>
       <c r="L155" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.35">
@@ -13838,31 +13959,31 @@
         <v>45632</v>
       </c>
       <c r="B156" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C156" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D156" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="E156" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="F156" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G156" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H156" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="J156" t="s">
         <v>17</v>
       </c>
       <c r="L156" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.35">
@@ -13870,34 +13991,34 @@
         <v>45632</v>
       </c>
       <c r="B157" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C157" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="D157" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E157" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F157" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="G157" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H157" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J157" t="s">
         <v>17</v>
       </c>
       <c r="K157" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="L157" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.35">
@@ -13905,34 +14026,34 @@
         <v>45635</v>
       </c>
       <c r="B158" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C158" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="D158" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="E158" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="F158" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="G158" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="H158" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="J158" t="s">
         <v>17</v>
       </c>
       <c r="K158" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="L158" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.35">
@@ -13940,34 +14061,34 @@
         <v>45635</v>
       </c>
       <c r="B159" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C159" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="D159" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="E159" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="F159" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="G159" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H159" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J159" t="s">
         <v>51</v>
       </c>
       <c r="K159" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L159" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.35">
@@ -13978,28 +14099,28 @@
         <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="D160" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="E160" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="F160" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="G160" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="H160" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J160" t="s">
         <v>17</v>
       </c>
       <c r="L160" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.35">
@@ -14007,34 +14128,34 @@
         <v>45761</v>
       </c>
       <c r="B161" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="C161" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="D161" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="E161" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="F161" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="G161" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H161" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J161" t="s">
         <v>17</v>
       </c>
       <c r="K161" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="L161" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.35">
@@ -14042,31 +14163,31 @@
         <v>45761</v>
       </c>
       <c r="B162" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C162" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="D162" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="E162" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="F162" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="G162" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="H162" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.35">
@@ -14074,31 +14195,31 @@
         <v>45762</v>
       </c>
       <c r="B163" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="C163" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="D163" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="E163" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="F163" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="G163" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H163" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J163" t="s">
         <v>17</v>
       </c>
       <c r="L163" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.35">
@@ -14109,28 +14230,28 @@
         <v>100</v>
       </c>
       <c r="C164" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="D164" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="E164" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="F164" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="G164" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="H164" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J164" t="s">
         <v>17</v>
       </c>
       <c r="L164" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.35">
@@ -14138,34 +14259,34 @@
         <v>45761</v>
       </c>
       <c r="B165" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C165" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="D165" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="E165" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="F165" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="G165" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="H165" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="J165" t="s">
         <v>17</v>
       </c>
       <c r="K165" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="L165" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.35">
@@ -14173,28 +14294,28 @@
         <v>45762</v>
       </c>
       <c r="B166" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C166" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="D166" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="F166" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="G166" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H166" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="J166" t="s">
         <v>17</v>
       </c>
       <c r="L166" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.35">
@@ -14202,25 +14323,25 @@
         <v>45762</v>
       </c>
       <c r="B167" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C167" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="D167" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E167" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F167" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="J167" t="s">
         <v>70</v>
       </c>
       <c r="L167" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.35">
@@ -14228,31 +14349,31 @@
         <v>45762</v>
       </c>
       <c r="B168" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="C168" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="D168" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="E168" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="F168" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="G168" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="H168" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J168" t="s">
         <v>17</v>
       </c>
       <c r="L168" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.35">
@@ -14260,89 +14381,89 @@
         <v>45762</v>
       </c>
       <c r="B169" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C169" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="D169" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="E169" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="F169" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="G169" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="H169" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="J169" t="s">
         <v>17</v>
       </c>
       <c r="L169" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="B170" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C170" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="D170" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="E170" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="F170" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="G170" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="H170" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J170" t="s">
         <v>51</v>
       </c>
       <c r="L170" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="B171" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C171" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="D171" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="E171" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="F171" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="G171" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="H171" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J171" t="s">
         <v>51</v>
@@ -14351,106 +14472,106 @@
         <v>83</v>
       </c>
       <c r="L171" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="B172" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C172" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="D172" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E172" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="F172" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="G172" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="H172" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="J172" t="s">
         <v>51</v>
       </c>
       <c r="K172" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="L172" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="B173" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="C173" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="D173" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="E173" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="F173" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="G173" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H173" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="J173" t="s">
         <v>17</v>
       </c>
       <c r="L173" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="B174" t="s">
         <v>40</v>
       </c>
       <c r="C174" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="D174" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="E174" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="F174" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="G174" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H174" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J174" t="s">
         <v>17</v>
       </c>
       <c r="L174" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.35">
@@ -14458,34 +14579,34 @@
         <v>45762</v>
       </c>
       <c r="B175" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="C175" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D175" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="E175" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="F175" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="G175" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="H175" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="J175" t="s">
         <v>51</v>
       </c>
       <c r="K175" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="L175" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.35">
@@ -14493,34 +14614,34 @@
         <v>45762</v>
       </c>
       <c r="B176" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C176" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="D176" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E176" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="F176" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="G176" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H176" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J176" t="s">
         <v>17</v>
       </c>
       <c r="K176" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="L176" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.35">
@@ -14528,34 +14649,34 @@
         <v>45762</v>
       </c>
       <c r="B177" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C177" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="D177" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="E177" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="F177" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="G177" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H177" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J177" t="s">
         <v>17</v>
       </c>
       <c r="K177" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="L177" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.35">
@@ -14563,31 +14684,31 @@
         <v>45762</v>
       </c>
       <c r="B178" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="C178" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="D178" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="E178" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="F178" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="G178" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H178" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="J178" t="s">
         <v>17</v>
       </c>
       <c r="L178" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.35">
@@ -14595,31 +14716,31 @@
         <v>45762</v>
       </c>
       <c r="B179" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="C179" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="D179" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="E179" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="F179" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="G179" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="H179" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="J179" t="s">
         <v>17</v>
       </c>
       <c r="L179" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.35">
@@ -14627,31 +14748,31 @@
         <v>45762</v>
       </c>
       <c r="B180" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C180" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="D180" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="E180" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="F180" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="G180" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H180" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="J180" t="s">
         <v>17</v>
       </c>
       <c r="L180" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.35">
@@ -14659,25 +14780,25 @@
         <v>45762</v>
       </c>
       <c r="B181" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="C181" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="D181" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="E181" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="F181" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="J181" t="s">
         <v>70</v>
       </c>
       <c r="L181" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.35">
@@ -14685,34 +14806,34 @@
         <v>45762</v>
       </c>
       <c r="B182" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="C182" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="D182" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="E182" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="F182" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="G182" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="H182" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="J182" t="s">
         <v>51</v>
       </c>
       <c r="K182" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="L182" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.35">
@@ -14720,34 +14841,34 @@
         <v>45762</v>
       </c>
       <c r="B183" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C183" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="D183" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="E183" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="F183" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="G183" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="H183" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="J183" t="s">
         <v>51</v>
       </c>
       <c r="K183" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="L183" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.35">
@@ -14755,31 +14876,31 @@
         <v>45762</v>
       </c>
       <c r="B184" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="C184" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="D184" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="F184" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="G184" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="H184" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="J184" t="s">
         <v>51</v>
       </c>
       <c r="K184" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="L184" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.35">
@@ -14787,25 +14908,25 @@
         <v>45763</v>
       </c>
       <c r="B185" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="C185" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="D185" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="E185" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="F185" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="J185" t="s">
         <v>70</v>
       </c>
       <c r="L185" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.35">
@@ -14813,22 +14934,22 @@
         <v>45764</v>
       </c>
       <c r="B186" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="C186" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="D186" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="F186" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="J186" t="s">
         <v>70</v>
       </c>
       <c r="L186" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.35">
@@ -14836,34 +14957,34 @@
         <v>45764</v>
       </c>
       <c r="B187" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="C187" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="D187" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="E187" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="F187" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="G187" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="H187" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J187" t="s">
         <v>17</v>
       </c>
       <c r="K187" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="L187" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="1064">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -1364,9 +1364,6 @@
     <t>KOTTY Kotty Paul Marie</t>
   </si>
   <si>
-    <t>Analyse du marché de la téléphonie mobile en Côte d'Ivoire:dynamique du marché et performance des opérateurs</t>
-  </si>
-  <si>
     <t>ABIE</t>
   </si>
   <si>
@@ -2201,9 +2198,6 @@
     <t>MEYER Sopie Laeticia</t>
   </si>
   <si>
-    <t>Analyse des déterminants de l'accès au financement des producteurs de noix de cajou dans la region du gontougo en Côte d'Ivoir</t>
-  </si>
-  <si>
     <t>ZOUNGRANA Placide</t>
   </si>
   <si>
@@ -2417,9 +2411,6 @@
     <t>OUATTARA Sienfoungo Marie-Louise</t>
   </si>
   <si>
-    <t>0748</t>
-  </si>
-  <si>
     <t>Jeanne Liliane Kousso</t>
   </si>
   <si>
@@ -2777,33 +2768,18 @@
     <t>Nombre de Prenom</t>
   </si>
   <si>
-    <t>Spécialité</t>
-  </si>
-  <si>
-    <t>Audit financier sectoriel</t>
-  </si>
-  <si>
-    <t>Comptabilité publique et gestion financière institutionnelle</t>
-  </si>
-  <si>
     <t xml:space="preserve">Optimisation des processus de trésorérie </t>
   </si>
   <si>
     <t>Gestion des risques</t>
   </si>
   <si>
-    <t xml:space="preserve">Audit immobilier </t>
-  </si>
-  <si>
     <t xml:space="preserve">Comptabilité et gestion financière </t>
   </si>
   <si>
     <t>Analyse du réseau des soins</t>
   </si>
   <si>
-    <t>Gestion de la trésorérie</t>
-  </si>
-  <si>
     <t>Bancassurance</t>
   </si>
   <si>
@@ -3159,6 +3135,87 @@
   </si>
   <si>
     <t>Institutions et Services Financiers</t>
+  </si>
+  <si>
+    <t>Analyse démographique</t>
+  </si>
+  <si>
+    <t>Démographie économique</t>
+  </si>
+  <si>
+    <t>Commerce de détail et de gros; e-Commerce</t>
+  </si>
+  <si>
+    <t>Analyse sectorielle</t>
+  </si>
+  <si>
+    <t>Analyse du marché de la téléphonie mobile en Côte d'Ivoire : dynamique du marché et performance des opérateurs</t>
+  </si>
+  <si>
+    <t>Economie industrielle</t>
+  </si>
+  <si>
+    <t>Structure de marché, stratégie de cabinet et performance de marché</t>
+  </si>
+  <si>
+    <t>Agriculture; Ressources naturelles; Autres Produits Primaires</t>
+  </si>
+  <si>
+    <t>Sources d'énergie alternatives</t>
+  </si>
+  <si>
+    <t>Développement durable</t>
+  </si>
+  <si>
+    <t>Institutions et macroéconomie</t>
+  </si>
+  <si>
+    <t>Macroéconomie</t>
+  </si>
+  <si>
+    <t>Administration Publique et Vérifications du Secteur Public</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Institutions et croissance</t>
+  </si>
+  <si>
+    <t>Climat; catastrophes naturelles et réchauffement Global</t>
+  </si>
+  <si>
+    <t>Ajustement du compte courant; mouvements de capital à court terme</t>
+  </si>
+  <si>
+    <t>Finance internationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Economie du genre; discrimination non-travail</t>
+  </si>
+  <si>
+    <t>Analyse des déterminants de l'accès au financement des producteurs de noix de cajou dans la region du gontougo en Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Études de commerce, pays et industrie</t>
+  </si>
+  <si>
+    <t>Inégalité de Revenu</t>
+  </si>
+  <si>
+    <t>Technologie agricole; services d'extension agricole</t>
+  </si>
+  <si>
+    <t>Effet des transferts de fond des migrants sur la croissance économique en Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Transfert de fonds des migrants</t>
+  </si>
+  <si>
+    <t>Economie internationale</t>
+  </si>
+  <si>
+    <t>Investissement International; Mouvements de Capitaux à Long Terme</t>
+  </si>
+  <si>
+    <t>07-48-24-99-96</t>
   </si>
 </sst>
 </file>
@@ -3168,7 +3225,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3180,6 +3237,26 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1B1B1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3217,7 +3294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3229,6 +3306,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4617,7 +4699,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="45794.60682789352" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:N187" sheet="Sheet1"/>
+    <worksheetSource ref="A1:M187" sheet="Sheet1"/>
   </cacheSource>
   <cacheFields count="13">
     <cacheField name="Date de dépôt" numFmtId="0">
@@ -8269,7 +8351,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -8376,7 +8458,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -8398,7 +8480,7 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -8431,7 +8513,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -8442,7 +8524,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -8475,7 +8557,7 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -8497,7 +8579,7 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -8508,7 +8590,7 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -8519,7 +8601,7 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -8541,7 +8623,7 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -8552,7 +8634,7 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -8563,7 +8645,7 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -8618,7 +8700,7 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -8629,7 +8711,7 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -8640,7 +8722,7 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -8717,7 +8799,7 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -8728,7 +8810,7 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -8739,7 +8821,7 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -8805,7 +8887,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -8882,7 +8964,7 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -8915,7 +8997,7 @@
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -8937,7 +9019,7 @@
         <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -8959,7 +9041,7 @@
         <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -9014,7 +9096,7 @@
         <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -9025,7 +9107,7 @@
         <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -9058,7 +9140,7 @@
         <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -9069,7 +9151,7 @@
         <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -9083,7 +9165,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:N187"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.7265625" style="5" bestFit="1" customWidth="1"/>
@@ -9092,17 +9174,16 @@
     <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="144" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="59.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="50.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9128,25 +9209,22 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>917</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>44123</v>
       </c>
@@ -9163,28 +9241,25 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="H2" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="I2" t="s">
-        <v>919</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="2">
+      <c r="L2" s="2">
         <v>44146</v>
       </c>
-      <c r="N2" t="s">
+      <c r="M2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>44123</v>
       </c>
@@ -9201,28 +9276,25 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="H3" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="I3" t="s">
-        <v>918</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s">
         <v>162</v>
       </c>
-      <c r="M3" s="2">
+      <c r="L3" s="2">
         <v>44146</v>
       </c>
-      <c r="N3" t="s">
+      <c r="M3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>44120</v>
       </c>
@@ -9239,28 +9311,25 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="H4" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="I4" t="s">
-        <v>925</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="2">
+      <c r="L4" s="2">
         <v>44187</v>
       </c>
-      <c r="N4" t="s">
+      <c r="M4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>44120</v>
       </c>
@@ -9277,28 +9346,25 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H5" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="I5" t="s">
-        <v>922</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="2">
+      <c r="L5" s="2">
         <v>44187</v>
       </c>
-      <c r="N5" t="s">
+      <c r="M5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>44166</v>
       </c>
@@ -9315,28 +9381,25 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H6" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="I6" t="s">
-        <v>925</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="2">
+      <c r="L6" s="2">
         <v>44186</v>
       </c>
-      <c r="N6" t="s">
+      <c r="M6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>44167</v>
       </c>
@@ -9353,28 +9416,25 @@
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H7" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="I7" t="s">
-        <v>922</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" t="s">
         <v>18</v>
       </c>
-      <c r="M7" s="2">
+      <c r="L7" s="2">
         <v>44187</v>
       </c>
-      <c r="N7" t="s">
+      <c r="M7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>44167</v>
       </c>
@@ -9391,28 +9451,25 @@
         <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="H8" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="I8" t="s">
-        <v>925</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="2">
+      <c r="L8" s="2">
         <v>44187</v>
       </c>
-      <c r="N8" t="s">
+      <c r="M8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>44167</v>
       </c>
@@ -9429,25 +9486,25 @@
         <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="H9" t="s">
-        <v>926</v>
+        <v>918</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" t="s">
         <v>339</v>
       </c>
-      <c r="M9" s="2">
+      <c r="L9" s="2">
         <v>44186</v>
       </c>
-      <c r="N9" t="s">
+      <c r="M9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>52</v>
       </c>
@@ -9464,25 +9521,25 @@
         <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="H10" t="s">
-        <v>932</v>
+        <v>924</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" t="s">
         <v>57</v>
       </c>
+      <c r="L10" t="s">
+        <v>58</v>
+      </c>
       <c r="M10" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>52</v>
       </c>
@@ -9499,25 +9556,25 @@
         <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="H11" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" t="s">
         <v>63</v>
       </c>
+      <c r="L11" t="s">
+        <v>64</v>
+      </c>
       <c r="M11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
@@ -9534,22 +9591,22 @@
         <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="H12" t="s">
-        <v>1022</v>
-      </c>
-      <c r="J12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I12" t="s">
         <v>70</v>
       </c>
+      <c r="L12" t="s">
+        <v>64</v>
+      </c>
       <c r="M12" t="s">
-        <v>64</v>
-      </c>
-      <c r="N12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>71</v>
       </c>
@@ -9566,25 +9623,25 @@
         <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H13" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" t="s">
         <v>76</v>
       </c>
+      <c r="L13" t="s">
+        <v>77</v>
+      </c>
       <c r="M13" t="s">
-        <v>77</v>
-      </c>
-      <c r="N13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>78</v>
       </c>
@@ -9601,25 +9658,25 @@
         <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="H14" t="s">
-        <v>926</v>
+        <v>918</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" t="s">
         <v>83</v>
       </c>
+      <c r="L14" t="s">
+        <v>84</v>
+      </c>
       <c r="M14" t="s">
-        <v>84</v>
-      </c>
-      <c r="N14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -9636,22 +9693,22 @@
         <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="H15" t="s">
-        <v>932</v>
-      </c>
-      <c r="J15" t="s">
+        <v>924</v>
+      </c>
+      <c r="I15" t="s">
         <v>17</v>
       </c>
+      <c r="L15" t="s">
+        <v>64</v>
+      </c>
       <c r="M15" t="s">
-        <v>64</v>
-      </c>
-      <c r="N15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>78</v>
       </c>
@@ -9668,25 +9725,25 @@
         <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H16" t="s">
-        <v>942</v>
+        <v>934</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
       </c>
       <c r="J16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" t="s">
         <v>92</v>
       </c>
+      <c r="L16" t="s">
+        <v>93</v>
+      </c>
       <c r="M16" t="s">
-        <v>93</v>
-      </c>
-      <c r="N16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>78</v>
       </c>
@@ -9703,25 +9760,25 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H17" t="s">
-        <v>942</v>
+        <v>934</v>
+      </c>
+      <c r="I17" t="s">
+        <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" t="s">
         <v>98</v>
       </c>
+      <c r="L17" t="s">
+        <v>99</v>
+      </c>
       <c r="M17" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>78</v>
       </c>
@@ -9738,25 +9795,25 @@
         <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H18" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" t="s">
         <v>104</v>
       </c>
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
       <c r="M18" t="s">
-        <v>58</v>
-      </c>
-      <c r="N18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>78</v>
       </c>
@@ -9773,22 +9830,22 @@
         <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="H19" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I19" t="s">
         <v>70</v>
       </c>
+      <c r="L19" t="s">
+        <v>58</v>
+      </c>
       <c r="M19" t="s">
-        <v>58</v>
-      </c>
-      <c r="N19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>78</v>
       </c>
@@ -9805,25 +9862,25 @@
         <v>112</v>
       </c>
       <c r="G20" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H20" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" t="s">
         <v>113</v>
       </c>
+      <c r="L20" t="s">
+        <v>58</v>
+      </c>
       <c r="M20" t="s">
-        <v>58</v>
-      </c>
-      <c r="N20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>78</v>
       </c>
@@ -9840,25 +9897,25 @@
         <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H21" t="s">
-        <v>946</v>
+        <v>938</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" t="s">
         <v>98</v>
       </c>
+      <c r="L21" t="s">
+        <v>84</v>
+      </c>
       <c r="M21" t="s">
-        <v>84</v>
-      </c>
-      <c r="N21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>78</v>
       </c>
@@ -9875,25 +9932,25 @@
         <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H22" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I22" t="s">
+        <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>51</v>
-      </c>
-      <c r="K22" t="s">
         <v>122</v>
       </c>
+      <c r="L22" t="s">
+        <v>64</v>
+      </c>
       <c r="M22" t="s">
-        <v>64</v>
-      </c>
-      <c r="N22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>78</v>
       </c>
@@ -9910,25 +9967,25 @@
         <v>126</v>
       </c>
       <c r="G23" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="H23" t="s">
-        <v>948</v>
+        <v>940</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" t="s">
         <v>127</v>
       </c>
+      <c r="L23" t="s">
+        <v>77</v>
+      </c>
       <c r="M23" t="s">
-        <v>77</v>
-      </c>
-      <c r="N23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>128</v>
       </c>
@@ -9945,25 +10002,25 @@
         <v>132</v>
       </c>
       <c r="G24" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="H24" t="s">
-        <v>926</v>
+        <v>918</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
       </c>
       <c r="J24" t="s">
-        <v>51</v>
-      </c>
-      <c r="K24" t="s">
         <v>133</v>
       </c>
+      <c r="L24" t="s">
+        <v>58</v>
+      </c>
       <c r="M24" t="s">
-        <v>58</v>
-      </c>
-      <c r="N24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>128</v>
       </c>
@@ -9980,25 +10037,25 @@
         <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H25" t="s">
-        <v>921</v>
+        <v>915</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" t="s">
         <v>138</v>
       </c>
+      <c r="L25" t="s">
+        <v>84</v>
+      </c>
       <c r="M25" t="s">
-        <v>84</v>
-      </c>
-      <c r="N25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>128</v>
       </c>
@@ -10015,25 +10072,25 @@
         <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="H26" t="s">
-        <v>927</v>
+        <v>919</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" t="s">
         <v>143</v>
       </c>
+      <c r="L26" t="s">
+        <v>58</v>
+      </c>
       <c r="M26" t="s">
-        <v>58</v>
-      </c>
-      <c r="N26" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>128</v>
       </c>
@@ -10050,25 +10107,25 @@
         <v>148</v>
       </c>
       <c r="G27" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="H27" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I27" t="s">
+        <v>51</v>
       </c>
       <c r="J27" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" t="s">
         <v>133</v>
       </c>
+      <c r="L27" t="s">
+        <v>58</v>
+      </c>
       <c r="M27" t="s">
-        <v>58</v>
-      </c>
-      <c r="N27" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>128</v>
       </c>
@@ -10085,22 +10142,22 @@
         <v>152</v>
       </c>
       <c r="G28" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="H28" t="s">
-        <v>932</v>
-      </c>
-      <c r="J28" t="s">
+        <v>924</v>
+      </c>
+      <c r="I28" t="s">
         <v>17</v>
       </c>
+      <c r="L28" t="s">
+        <v>64</v>
+      </c>
       <c r="M28" t="s">
-        <v>64</v>
-      </c>
-      <c r="N28" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>154</v>
       </c>
@@ -10114,22 +10171,22 @@
         <v>157</v>
       </c>
       <c r="F29" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="G29" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="H29" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>154</v>
       </c>
@@ -10146,19 +10203,19 @@
         <v>161</v>
       </c>
       <c r="G30" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H30" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>154</v>
       </c>
@@ -10175,19 +10232,19 @@
         <v>166</v>
       </c>
       <c r="G31" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="H31" t="s">
-        <v>952</v>
+        <v>944</v>
+      </c>
+      <c r="I31" t="s">
+        <v>51</v>
       </c>
       <c r="J31" t="s">
-        <v>51</v>
-      </c>
-      <c r="K31" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>154</v>
       </c>
@@ -10204,19 +10261,19 @@
         <v>171</v>
       </c>
       <c r="G32" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="H32" t="s">
-        <v>932</v>
+        <v>924</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>154</v>
       </c>
@@ -10230,22 +10287,22 @@
         <v>175</v>
       </c>
       <c r="F33" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="G33" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="H33" t="s">
-        <v>955</v>
+        <v>947</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
       </c>
       <c r="J33" t="s">
-        <v>51</v>
-      </c>
-      <c r="K33" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>177</v>
       </c>
@@ -10262,16 +10319,16 @@
         <v>181</v>
       </c>
       <c r="G34" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="H34" t="s">
-        <v>934</v>
-      </c>
-      <c r="J34" t="s">
+        <v>926</v>
+      </c>
+      <c r="I34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>177</v>
       </c>
@@ -10288,19 +10345,19 @@
         <v>185</v>
       </c>
       <c r="G35" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="H35" t="s">
-        <v>923</v>
+        <v>916</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>187</v>
       </c>
@@ -10317,19 +10374,19 @@
         <v>191</v>
       </c>
       <c r="G36" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="H36" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J36" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I36" t="s">
         <v>70</v>
       </c>
-      <c r="M36" s="2">
+      <c r="L36" s="2">
         <v>44503</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>187</v>
       </c>
@@ -10346,19 +10403,19 @@
         <v>195</v>
       </c>
       <c r="G37" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="H37" t="s">
-        <v>1025</v>
-      </c>
-      <c r="J37" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I37" t="s">
         <v>70</v>
       </c>
-      <c r="M37" s="2">
+      <c r="L37" s="2">
         <v>44504</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>196</v>
       </c>
@@ -10372,19 +10429,19 @@
         <v>199</v>
       </c>
       <c r="F38" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="G38" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="H38" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J38" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I38" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>200</v>
       </c>
@@ -10398,22 +10455,22 @@
         <v>203</v>
       </c>
       <c r="F39" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="G39" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="H39" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>205</v>
       </c>
@@ -10430,19 +10487,19 @@
         <v>209</v>
       </c>
       <c r="G40" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H40" t="s">
-        <v>927</v>
+        <v>919</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>205</v>
       </c>
@@ -10459,19 +10516,19 @@
         <v>214</v>
       </c>
       <c r="G41" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="H41" t="s">
-        <v>932</v>
+        <v>924</v>
+      </c>
+      <c r="I41" t="s">
+        <v>51</v>
       </c>
       <c r="J41" t="s">
-        <v>51</v>
-      </c>
-      <c r="K41" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>205</v>
       </c>
@@ -10488,19 +10545,19 @@
         <v>218</v>
       </c>
       <c r="G42" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H42" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>205</v>
       </c>
@@ -10514,22 +10571,22 @@
         <v>222</v>
       </c>
       <c r="F43" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="G43" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="H43" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I43" t="s">
+        <v>51</v>
       </c>
       <c r="J43" t="s">
-        <v>51</v>
-      </c>
-      <c r="K43" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>205</v>
       </c>
@@ -10546,19 +10603,19 @@
         <v>226</v>
       </c>
       <c r="G44" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="H44" t="s">
-        <v>926</v>
+        <v>918</v>
+      </c>
+      <c r="I44" t="s">
+        <v>51</v>
       </c>
       <c r="J44" t="s">
-        <v>51</v>
-      </c>
-      <c r="K44" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>227</v>
       </c>
@@ -10575,22 +10632,22 @@
         <v>231</v>
       </c>
       <c r="G45" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="H45" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I45" t="s">
+        <v>51</v>
       </c>
       <c r="J45" t="s">
-        <v>51</v>
+        <v>232</v>
       </c>
       <c r="K45" t="s">
-        <v>232</v>
-      </c>
-      <c r="L45" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>227</v>
       </c>
@@ -10607,19 +10664,19 @@
         <v>237</v>
       </c>
       <c r="G46" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="H46" t="s">
-        <v>927</v>
-      </c>
-      <c r="J46" t="s">
+        <v>919</v>
+      </c>
+      <c r="I46" t="s">
         <v>17</v>
       </c>
-      <c r="L46" t="s">
+      <c r="K46" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>227</v>
       </c>
@@ -10636,22 +10693,22 @@
         <v>241</v>
       </c>
       <c r="G47" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H47" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
+        <v>242</v>
       </c>
       <c r="K47" t="s">
-        <v>242</v>
-      </c>
-      <c r="L47" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>44524</v>
       </c>
@@ -10668,22 +10725,22 @@
         <v>246</v>
       </c>
       <c r="G48" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="H48" t="s">
-        <v>962</v>
+        <v>954</v>
+      </c>
+      <c r="I48" t="s">
+        <v>17</v>
       </c>
       <c r="J48" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="K48" t="s">
-        <v>247</v>
-      </c>
-      <c r="L48" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>44191</v>
       </c>
@@ -10700,16 +10757,16 @@
         <v>251</v>
       </c>
       <c r="G49" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="H49" t="s">
-        <v>952</v>
-      </c>
-      <c r="J49" t="s">
+        <v>944</v>
+      </c>
+      <c r="I49" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>44526</v>
       </c>
@@ -10726,22 +10783,22 @@
         <v>255</v>
       </c>
       <c r="G50" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="H50" t="s">
-        <v>955</v>
+        <v>947</v>
+      </c>
+      <c r="I50" t="s">
+        <v>51</v>
       </c>
       <c r="J50" t="s">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="K50" t="s">
-        <v>256</v>
-      </c>
-      <c r="L50" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>44191</v>
       </c>
@@ -10758,22 +10815,22 @@
         <v>261</v>
       </c>
       <c r="G51" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="H51" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I51" t="s">
+        <v>51</v>
       </c>
       <c r="J51" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="K51" t="s">
-        <v>262</v>
-      </c>
-      <c r="L51" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>44612</v>
       </c>
@@ -10790,22 +10847,22 @@
         <v>266</v>
       </c>
       <c r="G52" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="H52" t="s">
-        <v>921</v>
+        <v>915</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
+        <v>267</v>
       </c>
       <c r="K52" t="s">
-        <v>267</v>
-      </c>
-      <c r="L52" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>44620</v>
       </c>
@@ -10822,22 +10879,22 @@
         <v>272</v>
       </c>
       <c r="G53" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="H53" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I53" t="s">
+        <v>51</v>
       </c>
       <c r="J53" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="K53" t="s">
-        <v>98</v>
-      </c>
-      <c r="L53" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>44620</v>
       </c>
@@ -10854,22 +10911,22 @@
         <v>275</v>
       </c>
       <c r="G54" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="H54" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I54" t="s">
+        <v>51</v>
       </c>
       <c r="J54" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="K54" t="s">
-        <v>262</v>
-      </c>
-      <c r="L54" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>44255</v>
       </c>
@@ -10886,22 +10943,22 @@
         <v>279</v>
       </c>
       <c r="G55" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="H55" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I55" t="s">
+        <v>51</v>
       </c>
       <c r="J55" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="K55" t="s">
-        <v>262</v>
-      </c>
-      <c r="L55" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>44255</v>
       </c>
@@ -10918,22 +10975,22 @@
         <v>284</v>
       </c>
       <c r="G56" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="H56" t="s">
-        <v>923</v>
+        <v>916</v>
+      </c>
+      <c r="I56" t="s">
+        <v>51</v>
       </c>
       <c r="J56" t="s">
-        <v>51</v>
+        <v>285</v>
       </c>
       <c r="K56" t="s">
-        <v>285</v>
-      </c>
-      <c r="L56" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>44255</v>
       </c>
@@ -10947,22 +11004,22 @@
         <v>289</v>
       </c>
       <c r="F57" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="G57" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H57" t="s">
-        <v>921</v>
-      </c>
-      <c r="J57" t="s">
+        <v>915</v>
+      </c>
+      <c r="I57" t="s">
         <v>17</v>
       </c>
-      <c r="L57" t="s">
+      <c r="K57" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>44255</v>
       </c>
@@ -10979,22 +11036,22 @@
         <v>293</v>
       </c>
       <c r="G58" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="H58" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="K58" t="s">
-        <v>98</v>
-      </c>
-      <c r="L58" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>44255</v>
       </c>
@@ -11011,22 +11068,22 @@
         <v>297</v>
       </c>
       <c r="G59" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="H59" t="s">
-        <v>926</v>
+        <v>918</v>
+      </c>
+      <c r="I59" t="s">
+        <v>51</v>
       </c>
       <c r="J59" t="s">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="K59" t="s">
-        <v>339</v>
-      </c>
-      <c r="L59" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>44620</v>
       </c>
@@ -11043,22 +11100,22 @@
         <v>301</v>
       </c>
       <c r="G60" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="H60" t="s">
-        <v>952</v>
+        <v>944</v>
+      </c>
+      <c r="I60" t="s">
+        <v>51</v>
       </c>
       <c r="J60" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="K60" t="s">
-        <v>113</v>
-      </c>
-      <c r="L60" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>44620</v>
       </c>
@@ -11075,22 +11132,22 @@
         <v>305</v>
       </c>
       <c r="G61" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="H61" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I61" t="s">
+        <v>51</v>
       </c>
       <c r="J61" t="s">
-        <v>51</v>
+        <v>306</v>
       </c>
       <c r="K61" t="s">
-        <v>306</v>
-      </c>
-      <c r="L61" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>44620</v>
       </c>
@@ -11107,19 +11164,19 @@
         <v>310</v>
       </c>
       <c r="G62" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="H62" t="s">
-        <v>988</v>
-      </c>
-      <c r="J62" t="s">
+        <v>980</v>
+      </c>
+      <c r="I62" t="s">
         <v>51</v>
       </c>
-      <c r="L62" t="s">
+      <c r="K62" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>44620</v>
       </c>
@@ -11136,22 +11193,22 @@
         <v>315</v>
       </c>
       <c r="G63" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="H63" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I63" t="s">
+        <v>51</v>
       </c>
       <c r="J63" t="s">
-        <v>51</v>
+        <v>316</v>
       </c>
       <c r="K63" t="s">
-        <v>316</v>
-      </c>
-      <c r="L63" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>44620</v>
       </c>
@@ -11168,19 +11225,19 @@
         <v>320</v>
       </c>
       <c r="G64" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="H64" t="s">
-        <v>1025</v>
-      </c>
-      <c r="J64" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I64" t="s">
         <v>70</v>
       </c>
-      <c r="L64" t="s">
+      <c r="K64" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>44620</v>
       </c>
@@ -11197,22 +11254,22 @@
         <v>325</v>
       </c>
       <c r="G65" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="H65" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I65" t="s">
+        <v>51</v>
       </c>
       <c r="J65" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="K65" t="s">
-        <v>262</v>
-      </c>
-      <c r="L65" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>44620</v>
       </c>
@@ -11229,19 +11286,19 @@
         <v>329</v>
       </c>
       <c r="G66" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="H66" t="s">
-        <v>942</v>
-      </c>
-      <c r="J66" t="s">
+        <v>934</v>
+      </c>
+      <c r="I66" t="s">
         <v>51</v>
       </c>
-      <c r="L66" t="s">
+      <c r="K66" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>44623</v>
       </c>
@@ -11258,19 +11315,19 @@
         <v>334</v>
       </c>
       <c r="G67" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="H67" t="s">
-        <v>1030</v>
-      </c>
-      <c r="J67" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I67" t="s">
         <v>70</v>
       </c>
-      <c r="L67" t="s">
+      <c r="K67" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>44833</v>
       </c>
@@ -11287,25 +11344,25 @@
         <v>767469615</v>
       </c>
       <c r="F68" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="G68" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="H68" t="s">
-        <v>926</v>
+        <v>918</v>
+      </c>
+      <c r="I68" t="s">
+        <v>51</v>
       </c>
       <c r="J68" t="s">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="K68" t="s">
-        <v>339</v>
-      </c>
-      <c r="L68" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>44833</v>
       </c>
@@ -11322,22 +11379,22 @@
         <v>343</v>
       </c>
       <c r="G69" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="H69" t="s">
-        <v>921</v>
+        <v>915</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
       </c>
       <c r="J69" t="s">
-        <v>17</v>
+        <v>344</v>
       </c>
       <c r="K69" t="s">
-        <v>344</v>
-      </c>
-      <c r="L69" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>44844</v>
       </c>
@@ -11357,22 +11414,22 @@
         <v>347</v>
       </c>
       <c r="G70" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="H70" t="s">
-        <v>948</v>
+        <v>940</v>
+      </c>
+      <c r="I70" t="s">
+        <v>17</v>
       </c>
       <c r="J70" t="s">
-        <v>17</v>
+        <v>348</v>
       </c>
       <c r="K70" t="s">
-        <v>348</v>
-      </c>
-      <c r="L70" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>44620</v>
       </c>
@@ -11389,19 +11446,19 @@
         <v>353</v>
       </c>
       <c r="G71" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="H71" t="s">
-        <v>934</v>
-      </c>
-      <c r="J71" t="s">
+        <v>926</v>
+      </c>
+      <c r="I71" t="s">
         <v>17</v>
       </c>
-      <c r="L71" t="s">
+      <c r="K71" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>44844</v>
       </c>
@@ -11421,19 +11478,19 @@
         <v>358</v>
       </c>
       <c r="G72" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="H72" t="s">
-        <v>1032</v>
-      </c>
-      <c r="J72" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I72" t="s">
         <v>70</v>
       </c>
-      <c r="L72" t="s">
+      <c r="K72" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>44844</v>
       </c>
@@ -11453,19 +11510,19 @@
         <v>363</v>
       </c>
       <c r="G73" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="H73" t="s">
-        <v>1034</v>
-      </c>
-      <c r="J73" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I73" t="s">
         <v>70</v>
       </c>
-      <c r="L73" t="s">
+      <c r="K73" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>44844</v>
       </c>
@@ -11485,19 +11542,19 @@
         <v>367</v>
       </c>
       <c r="G74" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="H74" t="s">
-        <v>1036</v>
-      </c>
-      <c r="J74" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I74" t="s">
         <v>70</v>
       </c>
-      <c r="L74" t="s">
+      <c r="K74" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>44944</v>
       </c>
@@ -11514,22 +11571,22 @@
         <v>371</v>
       </c>
       <c r="G75" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="H75" t="s">
-        <v>982</v>
+        <v>974</v>
+      </c>
+      <c r="I75" t="s">
+        <v>51</v>
       </c>
       <c r="J75" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="K75" t="s">
-        <v>98</v>
-      </c>
-      <c r="L75" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>44945</v>
       </c>
@@ -11546,19 +11603,19 @@
         <v>376</v>
       </c>
       <c r="G76" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="H76" t="s">
-        <v>1039</v>
-      </c>
-      <c r="J76" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I76" t="s">
         <v>70</v>
       </c>
-      <c r="L76" t="s">
+      <c r="K76" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>44945</v>
       </c>
@@ -11575,19 +11632,19 @@
         <v>380</v>
       </c>
       <c r="G77" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="H77" t="s">
-        <v>932</v>
-      </c>
-      <c r="J77" t="s">
+        <v>924</v>
+      </c>
+      <c r="I77" t="s">
         <v>17</v>
       </c>
-      <c r="L77" t="s">
+      <c r="K77" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>44946</v>
       </c>
@@ -11604,19 +11661,19 @@
         <v>383</v>
       </c>
       <c r="G78" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H78" t="s">
-        <v>934</v>
-      </c>
-      <c r="J78" t="s">
+        <v>926</v>
+      </c>
+      <c r="I78" t="s">
         <v>17</v>
       </c>
-      <c r="L78" t="s">
+      <c r="K78" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>44844</v>
       </c>
@@ -11633,19 +11690,19 @@
         <v>388</v>
       </c>
       <c r="G79" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="H79" t="s">
-        <v>1039</v>
-      </c>
-      <c r="J79" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I79" t="s">
         <v>70</v>
       </c>
-      <c r="L79" t="s">
+      <c r="K79" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>44952</v>
       </c>
@@ -11662,19 +11719,19 @@
         <v>391</v>
       </c>
       <c r="G80" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="H80" t="s">
-        <v>1043</v>
-      </c>
-      <c r="J80" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I80" t="s">
         <v>70</v>
       </c>
-      <c r="L80" t="s">
+      <c r="K80" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>44620</v>
       </c>
@@ -11691,19 +11748,19 @@
         <v>395</v>
       </c>
       <c r="G81" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="H81" t="s">
-        <v>923</v>
-      </c>
-      <c r="J81" t="s">
+        <v>916</v>
+      </c>
+      <c r="I81" t="s">
         <v>17</v>
       </c>
-      <c r="L81" t="s">
+      <c r="K81" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>44957</v>
       </c>
@@ -11723,22 +11780,22 @@
         <v>399</v>
       </c>
       <c r="G82" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="H82" t="s">
-        <v>923</v>
+        <v>916</v>
+      </c>
+      <c r="I82" t="s">
+        <v>17</v>
       </c>
       <c r="J82" t="s">
-        <v>17</v>
+        <v>400</v>
       </c>
       <c r="K82" t="s">
-        <v>400</v>
-      </c>
-      <c r="L82" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>45013</v>
       </c>
@@ -11755,19 +11812,19 @@
         <v>404</v>
       </c>
       <c r="G83" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="H83" t="s">
-        <v>1043</v>
-      </c>
-      <c r="J83" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I83" t="s">
         <v>70</v>
       </c>
-      <c r="L83" t="s">
+      <c r="K83" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>45013</v>
       </c>
@@ -11784,19 +11841,19 @@
         <v>409</v>
       </c>
       <c r="G84" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="H84" t="s">
-        <v>1034</v>
-      </c>
-      <c r="J84" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I84" t="s">
         <v>70</v>
       </c>
-      <c r="L84" t="s">
+      <c r="K84" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>45386</v>
       </c>
@@ -11813,22 +11870,22 @@
         <v>413</v>
       </c>
       <c r="G85" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="H85" t="s">
-        <v>952</v>
+        <v>944</v>
+      </c>
+      <c r="I85" t="s">
+        <v>51</v>
       </c>
       <c r="J85" t="s">
-        <v>51</v>
+        <v>414</v>
       </c>
       <c r="K85" t="s">
-        <v>414</v>
-      </c>
-      <c r="L85" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>45103</v>
       </c>
@@ -11845,22 +11902,22 @@
         <v>419</v>
       </c>
       <c r="G86" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="H86" t="s">
-        <v>952</v>
+        <v>944</v>
+      </c>
+      <c r="I86" t="s">
+        <v>51</v>
       </c>
       <c r="J86" t="s">
-        <v>51</v>
+        <v>420</v>
       </c>
       <c r="K86" t="s">
-        <v>420</v>
-      </c>
-      <c r="L86" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>45107</v>
       </c>
@@ -11877,19 +11934,19 @@
         <v>424</v>
       </c>
       <c r="G87" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="H87" t="s">
-        <v>1025</v>
-      </c>
-      <c r="J87" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I87" t="s">
         <v>70</v>
       </c>
-      <c r="L87" t="s">
+      <c r="K87" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>45107</v>
       </c>
@@ -11905,14 +11962,20 @@
       <c r="F88" t="s">
         <v>429</v>
       </c>
-      <c r="J88" t="s">
+      <c r="G88" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I88" t="s">
         <v>70</v>
       </c>
-      <c r="L88" t="s">
+      <c r="K88" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>45107</v>
       </c>
@@ -11928,14 +11991,20 @@
       <c r="F89" t="s">
         <v>433</v>
       </c>
-      <c r="J89" t="s">
+      <c r="G89" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I89" t="s">
         <v>70</v>
       </c>
-      <c r="L89" t="s">
+      <c r="K89" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>45107</v>
       </c>
@@ -11952,19 +12021,19 @@
         <v>437</v>
       </c>
       <c r="G90" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H90" t="s">
-        <v>936</v>
-      </c>
-      <c r="J90" t="s">
+        <v>928</v>
+      </c>
+      <c r="I90" t="s">
         <v>17</v>
       </c>
-      <c r="L90" t="s">
+      <c r="K90" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>45107</v>
       </c>
@@ -11981,22 +12050,22 @@
         <v>441</v>
       </c>
       <c r="G91" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="H91" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I91" t="s">
+        <v>17</v>
       </c>
       <c r="J91" t="s">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="K91" t="s">
-        <v>442</v>
-      </c>
-      <c r="L91" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>45107</v>
       </c>
@@ -12010,48 +12079,54 @@
         <v>445</v>
       </c>
       <c r="F92" t="s">
-        <v>446</v>
-      </c>
-      <c r="J92" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I92" t="s">
         <v>70</v>
       </c>
-      <c r="L92" t="s">
+      <c r="K92" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>45110</v>
       </c>
       <c r="B93" t="s">
+        <v>446</v>
+      </c>
+      <c r="C93" t="s">
         <v>447</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>448</v>
       </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
         <v>449</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
+        <v>978</v>
+      </c>
+      <c r="H93" t="s">
+        <v>926</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" t="s">
         <v>450</v>
       </c>
-      <c r="G93" t="s">
-        <v>986</v>
-      </c>
-      <c r="H93" t="s">
-        <v>934</v>
-      </c>
-      <c r="J93" t="s">
-        <v>17</v>
-      </c>
       <c r="K93" t="s">
-        <v>451</v>
-      </c>
-      <c r="L93" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>45110</v>
       </c>
@@ -12059,205 +12134,205 @@
         <v>178</v>
       </c>
       <c r="C94" t="s">
+        <v>451</v>
+      </c>
+      <c r="D94" t="s">
         <v>452</v>
       </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
         <v>453</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
+        <v>915</v>
+      </c>
+      <c r="H94" t="s">
+        <v>915</v>
+      </c>
+      <c r="I94" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" t="s">
         <v>454</v>
-      </c>
-      <c r="G94" t="s">
-        <v>921</v>
-      </c>
-      <c r="H94" t="s">
-        <v>921</v>
-      </c>
-      <c r="J94" t="s">
-        <v>17</v>
       </c>
       <c r="K94" t="s">
         <v>455</v>
       </c>
-      <c r="L94" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>45110</v>
       </c>
       <c r="B95" t="s">
+        <v>456</v>
+      </c>
+      <c r="C95" t="s">
         <v>457</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>458</v>
       </c>
-      <c r="D95" t="s">
+      <c r="F95" t="s">
         <v>459</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
+        <v>944</v>
+      </c>
+      <c r="H95" t="s">
+        <v>979</v>
+      </c>
+      <c r="I95" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" t="s">
+        <v>420</v>
+      </c>
+      <c r="K95" t="s">
         <v>460</v>
       </c>
-      <c r="G95" t="s">
-        <v>952</v>
-      </c>
-      <c r="H95" t="s">
-        <v>987</v>
-      </c>
-      <c r="J95" t="s">
-        <v>17</v>
-      </c>
-      <c r="K95" t="s">
-        <v>420</v>
-      </c>
-      <c r="L95" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>45110</v>
       </c>
       <c r="B96" t="s">
+        <v>461</v>
+      </c>
+      <c r="C96" t="s">
         <v>462</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>463</v>
       </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
         <v>464</v>
       </c>
-      <c r="F96" t="s">
-        <v>465</v>
-      </c>
       <c r="G96" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="H96" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I96" t="s">
+        <v>17</v>
       </c>
       <c r="J96" t="s">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="K96" t="s">
-        <v>442</v>
-      </c>
-      <c r="L96" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>45110</v>
       </c>
       <c r="B97" t="s">
+        <v>465</v>
+      </c>
+      <c r="C97" t="s">
         <v>466</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>467</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>468</v>
       </c>
-      <c r="F97" t="s">
-        <v>469</v>
-      </c>
       <c r="G97" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H97" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I97" t="s">
+        <v>17</v>
       </c>
       <c r="J97" t="s">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="K97" t="s">
-        <v>442</v>
-      </c>
-      <c r="L97" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>45110</v>
       </c>
       <c r="B98" t="s">
+        <v>469</v>
+      </c>
+      <c r="C98" t="s">
         <v>470</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>471</v>
       </c>
-      <c r="D98" t="s">
+      <c r="F98" t="s">
         <v>472</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
+        <v>925</v>
+      </c>
+      <c r="H98" t="s">
+        <v>926</v>
+      </c>
+      <c r="I98" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" t="s">
         <v>473</v>
       </c>
-      <c r="G98" t="s">
-        <v>933</v>
-      </c>
-      <c r="H98" t="s">
-        <v>934</v>
-      </c>
-      <c r="J98" t="s">
-        <v>17</v>
-      </c>
       <c r="K98" t="s">
-        <v>474</v>
-      </c>
-      <c r="L98" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>45110</v>
       </c>
       <c r="B99" t="s">
+        <v>474</v>
+      </c>
+      <c r="C99" t="s">
         <v>475</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>476</v>
       </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
         <v>477</v>
       </c>
-      <c r="F99" t="s">
-        <v>478</v>
-      </c>
       <c r="G99" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H99" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I99" t="s">
+        <v>51</v>
       </c>
       <c r="J99" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="K99" t="s">
-        <v>113</v>
-      </c>
-      <c r="L99" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>45110</v>
       </c>
       <c r="B100" t="s">
+        <v>478</v>
+      </c>
+      <c r="C100" t="s">
         <v>479</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>480</v>
       </c>
-      <c r="D100" t="s">
+      <c r="F100" t="s">
         <v>481</v>
-      </c>
-      <c r="F100" t="s">
-        <v>482</v>
       </c>
       <c r="G100" t="s">
         <v>17</v>
@@ -12265,28 +12340,28 @@
       <c r="H100" t="s">
         <v>17</v>
       </c>
-      <c r="J100" t="s">
+      <c r="I100" t="s">
         <v>17</v>
       </c>
-      <c r="L100" t="s">
+      <c r="K100" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>45111</v>
       </c>
       <c r="B101" t="s">
+        <v>482</v>
+      </c>
+      <c r="C101" t="s">
         <v>483</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>484</v>
       </c>
-      <c r="D101" t="s">
+      <c r="F101" t="s">
         <v>485</v>
-      </c>
-      <c r="F101" t="s">
-        <v>486</v>
       </c>
       <c r="G101" t="s">
         <v>17</v>
@@ -12294,31 +12369,31 @@
       <c r="H101" t="s">
         <v>17</v>
       </c>
+      <c r="I101" t="s">
+        <v>17</v>
+      </c>
       <c r="J101" t="s">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="K101" t="s">
-        <v>442</v>
-      </c>
-      <c r="L101" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>45112</v>
       </c>
       <c r="B102" t="s">
+        <v>487</v>
+      </c>
+      <c r="C102" t="s">
         <v>488</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>489</v>
       </c>
-      <c r="D102" t="s">
+      <c r="F102" t="s">
         <v>490</v>
-      </c>
-      <c r="F102" t="s">
-        <v>491</v>
       </c>
       <c r="G102" t="s">
         <v>17</v>
@@ -12326,63 +12401,75 @@
       <c r="H102" t="s">
         <v>17</v>
       </c>
+      <c r="I102" t="s">
+        <v>17</v>
+      </c>
       <c r="J102" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="K102" t="s">
-        <v>492</v>
-      </c>
-      <c r="L102" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>45113</v>
       </c>
       <c r="B103" t="s">
+        <v>492</v>
+      </c>
+      <c r="C103" t="s">
         <v>493</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>494</v>
       </c>
-      <c r="D103" t="s">
+      <c r="F103" t="s">
         <v>495</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I103" t="s">
+        <v>70</v>
+      </c>
+      <c r="K103" t="s">
         <v>496</v>
       </c>
-      <c r="J103" t="s">
-        <v>70</v>
-      </c>
-      <c r="L103" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>45116</v>
       </c>
       <c r="B104" t="s">
+        <v>497</v>
+      </c>
+      <c r="C104" t="s">
         <v>498</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>499</v>
       </c>
-      <c r="D104" t="s">
+      <c r="F104" t="s">
         <v>500</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H104" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I104" t="s">
+        <v>70</v>
+      </c>
+      <c r="K104" t="s">
         <v>501</v>
       </c>
-      <c r="J104" t="s">
-        <v>70</v>
-      </c>
-      <c r="L104" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>45240</v>
       </c>
@@ -12390,22 +12477,28 @@
         <v>331</v>
       </c>
       <c r="C105" t="s">
+        <v>502</v>
+      </c>
+      <c r="D105" t="s">
         <v>503</v>
       </c>
-      <c r="D105" t="s">
+      <c r="F105" t="s">
         <v>504</v>
       </c>
-      <c r="F105" t="s">
-        <v>505</v>
-      </c>
-      <c r="J105" t="s">
+      <c r="G105" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I105" t="s">
         <v>70</v>
       </c>
-      <c r="L105" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K105" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>45240</v>
       </c>
@@ -12413,303 +12506,333 @@
         <v>94</v>
       </c>
       <c r="C106" t="s">
+        <v>505</v>
+      </c>
+      <c r="D106" t="s">
         <v>506</v>
       </c>
-      <c r="D106" t="s">
+      <c r="F106" t="s">
         <v>507</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
+        <v>981</v>
+      </c>
+      <c r="H106" t="s">
+        <v>918</v>
+      </c>
+      <c r="I106" t="s">
+        <v>51</v>
+      </c>
+      <c r="J106" t="s">
         <v>508</v>
-      </c>
-      <c r="G106" t="s">
-        <v>989</v>
-      </c>
-      <c r="H106" t="s">
-        <v>926</v>
-      </c>
-      <c r="J106" t="s">
-        <v>51</v>
       </c>
       <c r="K106" t="s">
         <v>509</v>
       </c>
-      <c r="L106" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>45240</v>
       </c>
       <c r="B107" t="s">
+        <v>510</v>
+      </c>
+      <c r="C107" t="s">
         <v>511</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>512</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>513</v>
       </c>
-      <c r="F107" t="s">
-        <v>514</v>
-      </c>
-      <c r="J107" t="s">
+      <c r="G107" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H107" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I107" t="s">
         <v>70</v>
       </c>
-      <c r="L107" t="s">
+      <c r="K107" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>45296</v>
       </c>
       <c r="B108" t="s">
+        <v>514</v>
+      </c>
+      <c r="C108" t="s">
         <v>515</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>516</v>
       </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
         <v>517</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
+        <v>982</v>
+      </c>
+      <c r="H108" t="s">
+        <v>916</v>
+      </c>
+      <c r="I108" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" t="s">
         <v>518</v>
       </c>
-      <c r="G108" t="s">
-        <v>990</v>
-      </c>
-      <c r="H108" t="s">
-        <v>923</v>
-      </c>
-      <c r="J108" t="s">
-        <v>17</v>
-      </c>
       <c r="K108" t="s">
-        <v>519</v>
-      </c>
-      <c r="L108" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>45385</v>
       </c>
       <c r="B109" t="s">
+        <v>519</v>
+      </c>
+      <c r="C109" t="s">
         <v>520</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>521</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>522</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
+        <v>983</v>
+      </c>
+      <c r="H109" t="s">
+        <v>980</v>
+      </c>
+      <c r="I109" t="s">
+        <v>51</v>
+      </c>
+      <c r="J109" t="s">
         <v>523</v>
-      </c>
-      <c r="G109" t="s">
-        <v>991</v>
-      </c>
-      <c r="H109" t="s">
-        <v>988</v>
-      </c>
-      <c r="J109" t="s">
-        <v>51</v>
       </c>
       <c r="K109" t="s">
         <v>524</v>
       </c>
-      <c r="L109" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>45385</v>
       </c>
       <c r="B110" t="s">
+        <v>525</v>
+      </c>
+      <c r="C110" t="s">
         <v>526</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>527</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
         <v>528</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
+        <v>984</v>
+      </c>
+      <c r="H110" t="s">
+        <v>916</v>
+      </c>
+      <c r="I110" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" t="s">
         <v>529</v>
-      </c>
-      <c r="G110" t="s">
-        <v>992</v>
-      </c>
-      <c r="H110" t="s">
-        <v>923</v>
-      </c>
-      <c r="J110" t="s">
-        <v>17</v>
       </c>
       <c r="K110" t="s">
         <v>530</v>
       </c>
-      <c r="L110" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>45385</v>
       </c>
       <c r="B111" t="s">
+        <v>531</v>
+      </c>
+      <c r="C111" t="s">
         <v>532</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>533</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
         <v>534</v>
       </c>
-      <c r="F111" t="s">
-        <v>535</v>
-      </c>
       <c r="G111" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="H111" t="s">
-        <v>929</v>
+        <v>921</v>
+      </c>
+      <c r="I111" t="s">
+        <v>51</v>
       </c>
       <c r="J111" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="K111" t="s">
-        <v>98</v>
-      </c>
-      <c r="L111" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>45385</v>
       </c>
       <c r="B112" t="s">
+        <v>535</v>
+      </c>
+      <c r="C112" t="s">
         <v>536</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>537</v>
       </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>538</v>
       </c>
-      <c r="F112" t="s">
-        <v>539</v>
-      </c>
-      <c r="J112" t="s">
+      <c r="G112" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H112" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I112" t="s">
         <v>70</v>
       </c>
-      <c r="L112" t="s">
+      <c r="K112" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>45385</v>
       </c>
       <c r="B113" t="s">
+        <v>539</v>
+      </c>
+      <c r="C113" t="s">
         <v>540</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>541</v>
       </c>
-      <c r="D113" t="s">
+      <c r="F113" t="s">
         <v>542</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H113" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I113" t="s">
+        <v>70</v>
+      </c>
+      <c r="K113" t="s">
         <v>543</v>
       </c>
-      <c r="J113" t="s">
-        <v>70</v>
-      </c>
-      <c r="L113" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>45385</v>
       </c>
       <c r="B114" t="s">
+        <v>544</v>
+      </c>
+      <c r="C114" t="s">
         <v>545</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>546</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
         <v>547</v>
       </c>
-      <c r="F114" t="s">
-        <v>548</v>
-      </c>
       <c r="G114" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="H114" t="s">
-        <v>988</v>
-      </c>
-      <c r="J114" t="s">
+        <v>980</v>
+      </c>
+      <c r="I114" t="s">
         <v>51</v>
       </c>
-      <c r="L114" t="s">
+      <c r="K114" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>45385</v>
       </c>
       <c r="B115" t="s">
+        <v>548</v>
+      </c>
+      <c r="C115" t="s">
         <v>549</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>550</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>551</v>
       </c>
-      <c r="F115" t="s">
-        <v>552</v>
-      </c>
-      <c r="J115" t="s">
+      <c r="G115" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H115" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I115" t="s">
         <v>70</v>
       </c>
-      <c r="L115" t="s">
+      <c r="K115" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>45385</v>
       </c>
       <c r="B116" t="s">
+        <v>552</v>
+      </c>
+      <c r="C116" t="s">
         <v>553</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>554</v>
       </c>
-      <c r="D116" t="s">
-        <v>555</v>
-      </c>
       <c r="F116" t="s">
-        <v>994</v>
-      </c>
-      <c r="J116" t="s">
+        <v>986</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H116" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I116" t="s">
         <v>70</v>
       </c>
-      <c r="L116" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K116" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>45386</v>
       </c>
@@ -12717,124 +12840,124 @@
         <v>178</v>
       </c>
       <c r="C117" t="s">
+        <v>555</v>
+      </c>
+      <c r="D117" t="s">
         <v>556</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
+        <v>987</v>
+      </c>
+      <c r="G117" t="s">
+        <v>988</v>
+      </c>
+      <c r="H117" t="s">
+        <v>980</v>
+      </c>
+      <c r="I117" t="s">
+        <v>51</v>
+      </c>
+      <c r="J117" t="s">
         <v>557</v>
-      </c>
-      <c r="F117" t="s">
-        <v>995</v>
-      </c>
-      <c r="G117" t="s">
-        <v>996</v>
-      </c>
-      <c r="H117" t="s">
-        <v>988</v>
-      </c>
-      <c r="J117" t="s">
-        <v>51</v>
       </c>
       <c r="K117" t="s">
         <v>558</v>
       </c>
-      <c r="L117" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>45386</v>
       </c>
       <c r="B118" t="s">
+        <v>559</v>
+      </c>
+      <c r="C118" t="s">
         <v>560</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>561</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
         <v>562</v>
       </c>
-      <c r="F118" t="s">
-        <v>563</v>
-      </c>
       <c r="G118" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="H118" t="s">
-        <v>952</v>
+        <v>944</v>
+      </c>
+      <c r="I118" t="s">
+        <v>51</v>
       </c>
       <c r="J118" t="s">
-        <v>51</v>
+        <v>420</v>
       </c>
       <c r="K118" t="s">
-        <v>420</v>
-      </c>
-      <c r="L118" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>45386</v>
       </c>
       <c r="B119" t="s">
+        <v>446</v>
+      </c>
+      <c r="C119" t="s">
         <v>447</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>448</v>
       </c>
-      <c r="D119" t="s">
+      <c r="F119" t="s">
         <v>449</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
+        <v>978</v>
+      </c>
+      <c r="H119" t="s">
+        <v>926</v>
+      </c>
+      <c r="I119" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" t="s">
         <v>450</v>
       </c>
-      <c r="G119" t="s">
-        <v>986</v>
-      </c>
-      <c r="H119" t="s">
-        <v>934</v>
-      </c>
-      <c r="J119" t="s">
-        <v>17</v>
-      </c>
       <c r="K119" t="s">
-        <v>451</v>
-      </c>
-      <c r="L119" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>45386</v>
       </c>
       <c r="B120" t="s">
+        <v>563</v>
+      </c>
+      <c r="C120" t="s">
         <v>564</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>565</v>
       </c>
-      <c r="D120" t="s">
-        <v>566</v>
-      </c>
       <c r="F120" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="G120" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="H120" t="s">
-        <v>921</v>
-      </c>
-      <c r="J120" t="s">
+        <v>915</v>
+      </c>
+      <c r="I120" t="s">
         <v>17</v>
       </c>
-      <c r="L120" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K120" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>45386</v>
       </c>
@@ -12842,776 +12965,788 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
+        <v>566</v>
+      </c>
+      <c r="D121" t="s">
         <v>567</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F121" t="s">
         <v>568</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
+        <v>925</v>
+      </c>
+      <c r="H121" t="s">
+        <v>926</v>
+      </c>
+      <c r="I121" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121" t="s">
         <v>569</v>
       </c>
-      <c r="G121" t="s">
-        <v>933</v>
-      </c>
-      <c r="H121" t="s">
-        <v>934</v>
-      </c>
-      <c r="J121" t="s">
-        <v>17</v>
-      </c>
-      <c r="K121" t="s">
-        <v>18</v>
-      </c>
-      <c r="L121" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>45387</v>
       </c>
       <c r="B122" t="s">
+        <v>570</v>
+      </c>
+      <c r="C122" t="s">
         <v>571</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>572</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>573</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
+        <v>923</v>
+      </c>
+      <c r="H122" t="s">
+        <v>926</v>
+      </c>
+      <c r="I122" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" t="s">
         <v>574</v>
       </c>
-      <c r="G122" t="s">
-        <v>931</v>
-      </c>
-      <c r="H122" t="s">
-        <v>934</v>
-      </c>
-      <c r="J122" t="s">
-        <v>17</v>
-      </c>
       <c r="K122" t="s">
-        <v>575</v>
-      </c>
-      <c r="L122" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>45394</v>
       </c>
       <c r="B123" t="s">
+        <v>575</v>
+      </c>
+      <c r="C123" t="s">
         <v>576</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>577</v>
       </c>
-      <c r="D123" t="s">
+      <c r="F123" t="s">
         <v>578</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H123" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I123" t="s">
+        <v>70</v>
+      </c>
+      <c r="K123" t="s">
         <v>579</v>
       </c>
-      <c r="J123" t="s">
-        <v>70</v>
-      </c>
-      <c r="L123" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>45469</v>
       </c>
       <c r="B124" t="s">
+        <v>580</v>
+      </c>
+      <c r="C124" t="s">
         <v>581</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>582</v>
       </c>
-      <c r="D124" t="s">
+      <c r="F124" t="s">
         <v>583</v>
       </c>
-      <c r="F124" t="s">
-        <v>584</v>
-      </c>
       <c r="G124" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H124" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I124" t="s">
+        <v>51</v>
       </c>
       <c r="J124" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="K124" t="s">
-        <v>29</v>
-      </c>
-      <c r="L124" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>45481</v>
       </c>
       <c r="B125" t="s">
+        <v>584</v>
+      </c>
+      <c r="C125" t="s">
         <v>585</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>586</v>
       </c>
-      <c r="D125" t="s">
+      <c r="F125" t="s">
         <v>587</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
+        <v>991</v>
+      </c>
+      <c r="H125" t="s">
+        <v>938</v>
+      </c>
+      <c r="I125" t="s">
+        <v>51</v>
+      </c>
+      <c r="K125" t="s">
         <v>588</v>
       </c>
-      <c r="G125" t="s">
-        <v>999</v>
-      </c>
-      <c r="H125" t="s">
-        <v>946</v>
-      </c>
-      <c r="J125" t="s">
-        <v>51</v>
-      </c>
-      <c r="L125" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>45483</v>
       </c>
       <c r="B126" t="s">
+        <v>589</v>
+      </c>
+      <c r="C126" t="s">
         <v>590</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>591</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>592</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>593</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
+        <v>946</v>
+      </c>
+      <c r="H126" t="s">
+        <v>947</v>
+      </c>
+      <c r="I126" t="s">
+        <v>51</v>
+      </c>
+      <c r="J126" t="s">
+        <v>262</v>
+      </c>
+      <c r="K126" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A127" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="G126" t="s">
-        <v>954</v>
-      </c>
-      <c r="H126" t="s">
-        <v>955</v>
-      </c>
-      <c r="J126" t="s">
+      <c r="B127" t="s">
+        <v>563</v>
+      </c>
+      <c r="C127" t="s">
+        <v>595</v>
+      </c>
+      <c r="D127" t="s">
+        <v>596</v>
+      </c>
+      <c r="F127" t="s">
+        <v>597</v>
+      </c>
+      <c r="G127" t="s">
+        <v>992</v>
+      </c>
+      <c r="H127" t="s">
+        <v>980</v>
+      </c>
+      <c r="I127" t="s">
         <v>51</v>
       </c>
-      <c r="K126" t="s">
-        <v>262</v>
-      </c>
-      <c r="L126" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A127" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B127" t="s">
-        <v>564</v>
-      </c>
-      <c r="C127" t="s">
-        <v>596</v>
-      </c>
-      <c r="D127" t="s">
-        <v>597</v>
-      </c>
-      <c r="F127" t="s">
-        <v>598</v>
-      </c>
-      <c r="G127" t="s">
-        <v>1000</v>
-      </c>
-      <c r="H127" t="s">
-        <v>988</v>
-      </c>
       <c r="J127" t="s">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="K127" t="s">
-        <v>256</v>
-      </c>
-      <c r="L127" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B128" t="s">
         <v>114</v>
       </c>
       <c r="C128" t="s">
+        <v>598</v>
+      </c>
+      <c r="D128" t="s">
         <v>599</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>600</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>601</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
+        <v>946</v>
+      </c>
+      <c r="H128" t="s">
+        <v>926</v>
+      </c>
+      <c r="I128" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" t="s">
         <v>602</v>
-      </c>
-      <c r="G128" t="s">
-        <v>954</v>
-      </c>
-      <c r="H128" t="s">
-        <v>934</v>
-      </c>
-      <c r="J128" t="s">
-        <v>17</v>
       </c>
       <c r="K128" t="s">
         <v>603</v>
       </c>
-      <c r="L128" t="s">
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A129" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B129" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A129" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>605</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>606</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>607</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>608</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
+        <v>920</v>
+      </c>
+      <c r="H129" t="s">
+        <v>921</v>
+      </c>
+      <c r="I129" t="s">
+        <v>51</v>
+      </c>
+      <c r="J129" t="s">
+        <v>98</v>
+      </c>
+      <c r="K129" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A130" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B130" t="s">
         <v>609</v>
       </c>
-      <c r="G129" t="s">
-        <v>928</v>
-      </c>
-      <c r="H129" t="s">
-        <v>929</v>
-      </c>
-      <c r="J129" t="s">
+      <c r="C130" t="s">
+        <v>610</v>
+      </c>
+      <c r="D130" t="s">
+        <v>611</v>
+      </c>
+      <c r="E130" t="s">
+        <v>612</v>
+      </c>
+      <c r="F130" t="s">
+        <v>613</v>
+      </c>
+      <c r="G130" t="s">
+        <v>993</v>
+      </c>
+      <c r="H130" t="s">
+        <v>980</v>
+      </c>
+      <c r="I130" t="s">
         <v>51</v>
       </c>
-      <c r="K129" t="s">
+      <c r="K130" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A131" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B131" t="s">
+        <v>614</v>
+      </c>
+      <c r="C131" t="s">
+        <v>615</v>
+      </c>
+      <c r="D131" t="s">
+        <v>616</v>
+      </c>
+      <c r="E131" t="s">
+        <v>617</v>
+      </c>
+      <c r="F131" t="s">
+        <v>618</v>
+      </c>
+      <c r="G131" t="s">
+        <v>944</v>
+      </c>
+      <c r="H131" t="s">
+        <v>944</v>
+      </c>
+      <c r="I131" t="s">
+        <v>51</v>
+      </c>
+      <c r="J131" t="s">
+        <v>619</v>
+      </c>
+      <c r="K131" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A132" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B132" t="s">
+        <v>620</v>
+      </c>
+      <c r="C132" t="s">
+        <v>621</v>
+      </c>
+      <c r="D132" t="s">
+        <v>622</v>
+      </c>
+      <c r="E132" t="s">
+        <v>623</v>
+      </c>
+      <c r="F132" t="s">
+        <v>624</v>
+      </c>
+      <c r="G132" t="s">
+        <v>994</v>
+      </c>
+      <c r="H132" t="s">
+        <v>916</v>
+      </c>
+      <c r="I132" t="s">
+        <v>17</v>
+      </c>
+      <c r="K132" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A133" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B133" t="s">
+        <v>625</v>
+      </c>
+      <c r="C133" t="s">
+        <v>626</v>
+      </c>
+      <c r="D133" t="s">
+        <v>627</v>
+      </c>
+      <c r="E133" t="s">
+        <v>628</v>
+      </c>
+      <c r="F133" t="s">
+        <v>629</v>
+      </c>
+      <c r="G133" t="s">
+        <v>995</v>
+      </c>
+      <c r="H133" t="s">
+        <v>934</v>
+      </c>
+      <c r="I133" t="s">
+        <v>51</v>
+      </c>
+      <c r="J133" t="s">
+        <v>630</v>
+      </c>
+      <c r="K133" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A134" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B134" t="s">
+        <v>631</v>
+      </c>
+      <c r="C134" t="s">
+        <v>632</v>
+      </c>
+      <c r="D134" t="s">
+        <v>633</v>
+      </c>
+      <c r="E134" t="s">
+        <v>634</v>
+      </c>
+      <c r="F134" t="s">
+        <v>635</v>
+      </c>
+      <c r="G134" t="s">
+        <v>996</v>
+      </c>
+      <c r="H134" t="s">
+        <v>918</v>
+      </c>
+      <c r="I134" t="s">
+        <v>51</v>
+      </c>
+      <c r="J134" t="s">
+        <v>339</v>
+      </c>
+      <c r="K134" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A135" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B135" t="s">
+        <v>636</v>
+      </c>
+      <c r="C135" t="s">
+        <v>637</v>
+      </c>
+      <c r="D135" t="s">
+        <v>638</v>
+      </c>
+      <c r="E135" t="s">
+        <v>639</v>
+      </c>
+      <c r="F135" t="s">
+        <v>640</v>
+      </c>
+      <c r="G135" t="s">
+        <v>920</v>
+      </c>
+      <c r="H135" t="s">
+        <v>921</v>
+      </c>
+      <c r="I135" t="s">
+        <v>51</v>
+      </c>
+      <c r="J135" t="s">
         <v>98</v>
       </c>
-      <c r="L129" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A130" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B130" t="s">
-        <v>610</v>
-      </c>
-      <c r="C130" t="s">
-        <v>611</v>
-      </c>
-      <c r="D130" t="s">
-        <v>612</v>
-      </c>
-      <c r="E130" t="s">
-        <v>613</v>
-      </c>
-      <c r="F130" t="s">
-        <v>614</v>
-      </c>
-      <c r="G130" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H130" t="s">
-        <v>988</v>
-      </c>
-      <c r="J130" t="s">
+      <c r="K135" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A136" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B136" t="s">
+        <v>641</v>
+      </c>
+      <c r="C136" t="s">
+        <v>642</v>
+      </c>
+      <c r="D136" t="s">
+        <v>643</v>
+      </c>
+      <c r="E136" t="s">
+        <v>644</v>
+      </c>
+      <c r="F136" t="s">
+        <v>645</v>
+      </c>
+      <c r="G136" t="s">
+        <v>915</v>
+      </c>
+      <c r="H136" t="s">
+        <v>980</v>
+      </c>
+      <c r="I136" t="s">
         <v>51</v>
       </c>
-      <c r="L130" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A131" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B131" t="s">
-        <v>615</v>
-      </c>
-      <c r="C131" t="s">
-        <v>616</v>
-      </c>
-      <c r="D131" t="s">
-        <v>617</v>
-      </c>
-      <c r="E131" t="s">
-        <v>618</v>
-      </c>
-      <c r="F131" t="s">
-        <v>619</v>
-      </c>
-      <c r="G131" t="s">
-        <v>952</v>
-      </c>
-      <c r="H131" t="s">
-        <v>952</v>
-      </c>
-      <c r="J131" t="s">
+      <c r="J136" t="s">
+        <v>420</v>
+      </c>
+      <c r="K136" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A137" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B137" t="s">
+        <v>646</v>
+      </c>
+      <c r="C137" t="s">
+        <v>647</v>
+      </c>
+      <c r="D137" t="s">
+        <v>648</v>
+      </c>
+      <c r="E137" t="s">
+        <v>649</v>
+      </c>
+      <c r="F137" t="s">
+        <v>650</v>
+      </c>
+      <c r="G137" t="s">
+        <v>976</v>
+      </c>
+      <c r="H137" t="s">
+        <v>944</v>
+      </c>
+      <c r="I137" t="s">
         <v>51</v>
       </c>
-      <c r="K131" t="s">
-        <v>620</v>
-      </c>
-      <c r="L131" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A132" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B132" t="s">
-        <v>621</v>
-      </c>
-      <c r="C132" t="s">
-        <v>622</v>
-      </c>
-      <c r="D132" t="s">
-        <v>623</v>
-      </c>
-      <c r="E132" t="s">
-        <v>624</v>
-      </c>
-      <c r="F132" t="s">
-        <v>625</v>
-      </c>
-      <c r="G132" t="s">
-        <v>1002</v>
-      </c>
-      <c r="H132" t="s">
-        <v>923</v>
-      </c>
-      <c r="J132" t="s">
-        <v>17</v>
-      </c>
-      <c r="L132" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A133" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B133" t="s">
-        <v>626</v>
-      </c>
-      <c r="C133" t="s">
-        <v>627</v>
-      </c>
-      <c r="D133" t="s">
-        <v>628</v>
-      </c>
-      <c r="E133" t="s">
-        <v>629</v>
-      </c>
-      <c r="F133" t="s">
-        <v>630</v>
-      </c>
-      <c r="G133" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H133" t="s">
-        <v>942</v>
-      </c>
-      <c r="J133" t="s">
-        <v>51</v>
-      </c>
-      <c r="K133" t="s">
-        <v>631</v>
-      </c>
-      <c r="L133" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A134" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B134" t="s">
-        <v>632</v>
-      </c>
-      <c r="C134" t="s">
-        <v>633</v>
-      </c>
-      <c r="D134" t="s">
-        <v>634</v>
-      </c>
-      <c r="E134" t="s">
-        <v>635</v>
-      </c>
-      <c r="F134" t="s">
-        <v>636</v>
-      </c>
-      <c r="G134" t="s">
-        <v>1004</v>
-      </c>
-      <c r="H134" t="s">
-        <v>926</v>
-      </c>
-      <c r="J134" t="s">
-        <v>51</v>
-      </c>
-      <c r="K134" t="s">
-        <v>339</v>
-      </c>
-      <c r="L134" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A135" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B135" t="s">
-        <v>637</v>
-      </c>
-      <c r="C135" t="s">
-        <v>638</v>
-      </c>
-      <c r="D135" t="s">
-        <v>639</v>
-      </c>
-      <c r="E135" t="s">
-        <v>640</v>
-      </c>
-      <c r="F135" t="s">
-        <v>641</v>
-      </c>
-      <c r="G135" t="s">
-        <v>928</v>
-      </c>
-      <c r="H135" t="s">
-        <v>929</v>
-      </c>
-      <c r="J135" t="s">
-        <v>51</v>
-      </c>
-      <c r="K135" t="s">
-        <v>98</v>
-      </c>
-      <c r="L135" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A136" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B136" t="s">
-        <v>642</v>
-      </c>
-      <c r="C136" t="s">
-        <v>643</v>
-      </c>
-      <c r="D136" t="s">
-        <v>644</v>
-      </c>
-      <c r="E136" t="s">
-        <v>645</v>
-      </c>
-      <c r="F136" t="s">
-        <v>646</v>
-      </c>
-      <c r="G136" t="s">
-        <v>921</v>
-      </c>
-      <c r="H136" t="s">
-        <v>988</v>
-      </c>
-      <c r="J136" t="s">
-        <v>51</v>
-      </c>
-      <c r="K136" t="s">
-        <v>420</v>
-      </c>
-      <c r="L136" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A137" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B137" t="s">
-        <v>647</v>
-      </c>
-      <c r="C137" t="s">
-        <v>648</v>
-      </c>
-      <c r="D137" t="s">
-        <v>649</v>
-      </c>
-      <c r="E137" t="s">
-        <v>650</v>
-      </c>
-      <c r="F137" t="s">
+      <c r="J137" t="s">
         <v>651</v>
-      </c>
-      <c r="G137" t="s">
-        <v>984</v>
-      </c>
-      <c r="H137" t="s">
-        <v>952</v>
-      </c>
-      <c r="J137" t="s">
-        <v>51</v>
       </c>
       <c r="K137" t="s">
         <v>652</v>
       </c>
-      <c r="L137" t="s">
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A138" s="5" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A138" s="5" t="s">
+      <c r="B138" t="s">
         <v>654</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>655</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>656</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>657</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>658</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
+        <v>997</v>
+      </c>
+      <c r="H138" t="s">
+        <v>944</v>
+      </c>
+      <c r="I138" t="s">
+        <v>51</v>
+      </c>
+      <c r="J138" t="s">
+        <v>651</v>
+      </c>
+      <c r="K138" t="s">
         <v>659</v>
       </c>
-      <c r="G138" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H138" t="s">
-        <v>952</v>
-      </c>
-      <c r="J138" t="s">
-        <v>51</v>
-      </c>
-      <c r="K138" t="s">
-        <v>652</v>
-      </c>
-      <c r="L138" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B139" t="s">
         <v>234</v>
       </c>
       <c r="C139" t="s">
+        <v>660</v>
+      </c>
+      <c r="D139" t="s">
         <v>661</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>662</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>663</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
+        <v>946</v>
+      </c>
+      <c r="H139" t="s">
+        <v>947</v>
+      </c>
+      <c r="I139" t="s">
+        <v>51</v>
+      </c>
+      <c r="K139" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A140" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B140" t="s">
         <v>664</v>
       </c>
-      <c r="G139" t="s">
-        <v>954</v>
-      </c>
-      <c r="H139" t="s">
-        <v>955</v>
-      </c>
-      <c r="J139" t="s">
+      <c r="C140" t="s">
+        <v>665</v>
+      </c>
+      <c r="D140" t="s">
+        <v>666</v>
+      </c>
+      <c r="E140" t="s">
+        <v>667</v>
+      </c>
+      <c r="F140" t="s">
+        <v>668</v>
+      </c>
+      <c r="G140" t="s">
+        <v>998</v>
+      </c>
+      <c r="H140" t="s">
+        <v>944</v>
+      </c>
+      <c r="I140" t="s">
         <v>51</v>
       </c>
-      <c r="L139" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A140" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="B140" t="s">
-        <v>665</v>
-      </c>
-      <c r="C140" t="s">
-        <v>666</v>
-      </c>
-      <c r="D140" t="s">
-        <v>667</v>
-      </c>
-      <c r="E140" t="s">
-        <v>668</v>
-      </c>
-      <c r="F140" t="s">
+      <c r="K140" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A141" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="G140" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H140" t="s">
-        <v>952</v>
-      </c>
-      <c r="J140" t="s">
-        <v>51</v>
-      </c>
-      <c r="L140" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A141" s="5" t="s">
+      <c r="B141" t="s">
         <v>670</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>671</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141" t="s">
         <v>672</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>673</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>674</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
+        <v>999</v>
+      </c>
+      <c r="H141" t="s">
+        <v>915</v>
+      </c>
+      <c r="I141" t="s">
+        <v>17</v>
+      </c>
+      <c r="K141" t="s">
         <v>675</v>
       </c>
-      <c r="G141" t="s">
-        <v>1007</v>
-      </c>
-      <c r="H141" t="s">
-        <v>921</v>
-      </c>
-      <c r="J141" t="s">
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A142" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B142" t="s">
+        <v>677</v>
+      </c>
+      <c r="C142" t="s">
+        <v>678</v>
+      </c>
+      <c r="D142" t="s">
+        <v>679</v>
+      </c>
+      <c r="E142" t="s">
+        <v>680</v>
+      </c>
+      <c r="F142" t="s">
+        <v>681</v>
+      </c>
+      <c r="G142" t="s">
+        <v>923</v>
+      </c>
+      <c r="H142" t="s">
+        <v>926</v>
+      </c>
+      <c r="I142" t="s">
         <v>17</v>
       </c>
-      <c r="L141" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A142" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="B142" t="s">
-        <v>678</v>
-      </c>
-      <c r="C142" t="s">
-        <v>679</v>
-      </c>
-      <c r="D142" t="s">
-        <v>680</v>
-      </c>
-      <c r="E142" t="s">
-        <v>681</v>
-      </c>
-      <c r="F142" t="s">
+      <c r="J142" t="s">
         <v>682</v>
-      </c>
-      <c r="G142" t="s">
-        <v>931</v>
-      </c>
-      <c r="H142" t="s">
-        <v>934</v>
-      </c>
-      <c r="J142" t="s">
-        <v>17</v>
       </c>
       <c r="K142" t="s">
         <v>683</v>
       </c>
-      <c r="L142" t="s">
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A143" s="5" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A143" s="5" t="s">
+      <c r="B143" t="s">
         <v>685</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>686</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
         <v>687</v>
       </c>
-      <c r="D143" t="s">
+      <c r="F143" t="s">
         <v>688</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H143" t="s">
+        <v>926</v>
+      </c>
+      <c r="I143" t="s">
+        <v>17</v>
+      </c>
+      <c r="K143" t="s">
         <v>689</v>
       </c>
-      <c r="G143" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H143" t="s">
-        <v>934</v>
-      </c>
-      <c r="J143" t="s">
-        <v>17</v>
-      </c>
-      <c r="L143" t="s">
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A144" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="B144" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A144" s="5" t="s">
-        <v>685</v>
-      </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>691</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>692</v>
       </c>
-      <c r="D144" t="s">
+      <c r="F144" t="s">
         <v>693</v>
       </c>
-      <c r="F144" t="s">
-        <v>694</v>
-      </c>
-      <c r="J144" t="s">
+      <c r="G144" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I144" t="s">
         <v>70</v>
       </c>
-      <c r="L144" t="s">
+      <c r="K144" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="4">
         <v>45490</v>
       </c>
@@ -13619,310 +13754,328 @@
         <v>72</v>
       </c>
       <c r="C145" t="s">
+        <v>694</v>
+      </c>
+      <c r="D145" t="s">
         <v>695</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>696</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>697</v>
       </c>
-      <c r="F145" t="s">
-        <v>698</v>
-      </c>
       <c r="G145" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H145" t="s">
-        <v>934</v>
+        <v>926</v>
+      </c>
+      <c r="I145" t="s">
+        <v>17</v>
       </c>
       <c r="J145" t="s">
-        <v>17</v>
+        <v>574</v>
       </c>
       <c r="K145" t="s">
-        <v>575</v>
-      </c>
-      <c r="L145" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="4">
         <v>45490</v>
       </c>
       <c r="B146" t="s">
+        <v>698</v>
+      </c>
+      <c r="C146" t="s">
         <v>699</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>700</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>701</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>702</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H146" t="s">
+        <v>924</v>
+      </c>
+      <c r="I146" t="s">
+        <v>17</v>
+      </c>
+      <c r="K146" t="s">
         <v>703</v>
       </c>
-      <c r="G146" t="s">
-        <v>1009</v>
-      </c>
-      <c r="H146" t="s">
-        <v>932</v>
-      </c>
-      <c r="J146" t="s">
-        <v>17</v>
-      </c>
-      <c r="L146" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="4">
         <v>45490</v>
       </c>
       <c r="B147" t="s">
+        <v>704</v>
+      </c>
+      <c r="C147" t="s">
         <v>705</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>706</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>707</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>708</v>
       </c>
-      <c r="F147" t="s">
-        <v>709</v>
-      </c>
       <c r="G147" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="H147" t="s">
-        <v>923</v>
-      </c>
-      <c r="J147" t="s">
+        <v>916</v>
+      </c>
+      <c r="I147" t="s">
         <v>17</v>
       </c>
-      <c r="L147" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K147" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="4">
         <v>45490</v>
       </c>
       <c r="B148" t="s">
+        <v>709</v>
+      </c>
+      <c r="C148" t="s">
         <v>710</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>711</v>
       </c>
-      <c r="D148" t="s">
+      <c r="E148" t="s">
         <v>712</v>
       </c>
-      <c r="E148" t="s">
+      <c r="F148" t="s">
         <v>713</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
+        <v>915</v>
+      </c>
+      <c r="H148" t="s">
+        <v>980</v>
+      </c>
+      <c r="I148" t="s">
+        <v>51</v>
+      </c>
+      <c r="J148" t="s">
         <v>714</v>
-      </c>
-      <c r="G148" t="s">
-        <v>921</v>
-      </c>
-      <c r="H148" t="s">
-        <v>988</v>
-      </c>
-      <c r="J148" t="s">
-        <v>51</v>
       </c>
       <c r="K148" t="s">
         <v>715</v>
       </c>
-      <c r="L148" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="4">
         <v>45492</v>
       </c>
       <c r="B149" t="s">
+        <v>716</v>
+      </c>
+      <c r="C149" t="s">
         <v>717</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
         <v>718</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
         <v>719</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>720</v>
       </c>
-      <c r="F149" t="s">
-        <v>721</v>
-      </c>
-      <c r="J149" t="s">
+      <c r="G149" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I149" t="s">
         <v>70</v>
       </c>
-      <c r="L149" t="s">
+      <c r="K149" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="4">
         <v>45492</v>
       </c>
       <c r="B150" t="s">
+        <v>721</v>
+      </c>
+      <c r="C150" t="s">
         <v>722</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>723</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
+        <v>719</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I150" t="s">
+        <v>70</v>
+      </c>
+      <c r="K150" t="s">
         <v>724</v>
       </c>
-      <c r="E150" t="s">
-        <v>720</v>
-      </c>
-      <c r="F150" t="s">
-        <v>725</v>
-      </c>
-      <c r="J150" t="s">
-        <v>70</v>
-      </c>
-      <c r="L150" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="4">
         <v>45498</v>
       </c>
       <c r="B151" t="s">
+        <v>725</v>
+      </c>
+      <c r="C151" t="s">
+        <v>726</v>
+      </c>
+      <c r="D151" t="s">
         <v>727</v>
       </c>
-      <c r="C151" t="s">
+      <c r="F151" t="s">
         <v>728</v>
       </c>
-      <c r="D151" t="s">
+      <c r="G151" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I151" t="s">
+        <v>70</v>
+      </c>
+      <c r="K151" t="s">
         <v>729</v>
       </c>
-      <c r="F151" t="s">
-        <v>730</v>
-      </c>
-      <c r="J151" t="s">
-        <v>70</v>
-      </c>
-      <c r="L151" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="4">
         <v>45650</v>
       </c>
       <c r="B152" t="s">
+        <v>730</v>
+      </c>
+      <c r="C152" t="s">
+        <v>731</v>
+      </c>
+      <c r="D152" t="s">
         <v>732</v>
       </c>
-      <c r="C152" t="s">
+      <c r="E152" t="s">
         <v>733</v>
       </c>
-      <c r="D152" t="s">
+      <c r="F152" t="s">
         <v>734</v>
       </c>
-      <c r="E152" t="s">
+      <c r="G152" t="s">
+        <v>925</v>
+      </c>
+      <c r="H152" t="s">
+        <v>926</v>
+      </c>
+      <c r="I152" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" t="s">
         <v>735</v>
       </c>
-      <c r="F152" t="s">
-        <v>736</v>
-      </c>
-      <c r="G152" t="s">
-        <v>933</v>
-      </c>
-      <c r="H152" t="s">
-        <v>934</v>
-      </c>
-      <c r="J152" t="s">
-        <v>17</v>
-      </c>
       <c r="K152" t="s">
-        <v>737</v>
-      </c>
-      <c r="L152" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="4">
         <v>45632</v>
       </c>
       <c r="B153" t="s">
+        <v>736</v>
+      </c>
+      <c r="C153" t="s">
+        <v>737</v>
+      </c>
+      <c r="D153" t="s">
         <v>738</v>
       </c>
-      <c r="C153" t="s">
+      <c r="E153" t="s">
         <v>739</v>
       </c>
-      <c r="D153" t="s">
+      <c r="F153" t="s">
         <v>740</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
+        <v>925</v>
+      </c>
+      <c r="H153" t="s">
+        <v>926</v>
+      </c>
+      <c r="I153" t="s">
+        <v>17</v>
+      </c>
+      <c r="K153" t="s">
         <v>741</v>
       </c>
-      <c r="F153" t="s">
-        <v>742</v>
-      </c>
-      <c r="G153" t="s">
-        <v>933</v>
-      </c>
-      <c r="H153" t="s">
-        <v>934</v>
-      </c>
-      <c r="J153" t="s">
-        <v>17</v>
-      </c>
-      <c r="L153" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="4">
         <v>45632</v>
       </c>
       <c r="B154" t="s">
+        <v>742</v>
+      </c>
+      <c r="C154" t="s">
+        <v>743</v>
+      </c>
+      <c r="D154" t="s">
         <v>744</v>
       </c>
-      <c r="C154" t="s">
+      <c r="E154" t="s">
         <v>745</v>
       </c>
-      <c r="D154" t="s">
+      <c r="F154" t="s">
         <v>746</v>
       </c>
-      <c r="E154" t="s">
+      <c r="G154" t="s">
+        <v>923</v>
+      </c>
+      <c r="H154" t="s">
+        <v>926</v>
+      </c>
+      <c r="I154" t="s">
+        <v>17</v>
+      </c>
+      <c r="J154" t="s">
         <v>747</v>
       </c>
-      <c r="F154" t="s">
+      <c r="K154" t="s">
         <v>748</v>
       </c>
-      <c r="G154" t="s">
-        <v>931</v>
-      </c>
-      <c r="H154" t="s">
-        <v>934</v>
-      </c>
-      <c r="J154" t="s">
-        <v>17</v>
-      </c>
-      <c r="K154" t="s">
-        <v>749</v>
-      </c>
-      <c r="L154" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="4">
         <v>45632</v>
       </c>
@@ -13930,168 +14083,168 @@
         <v>94</v>
       </c>
       <c r="C155" t="s">
+        <v>749</v>
+      </c>
+      <c r="D155" t="s">
+        <v>750</v>
+      </c>
+      <c r="E155" t="s">
         <v>751</v>
       </c>
-      <c r="D155" t="s">
+      <c r="F155" t="s">
         <v>752</v>
       </c>
-      <c r="E155" t="s">
-        <v>753</v>
-      </c>
-      <c r="F155" t="s">
-        <v>754</v>
-      </c>
       <c r="G155" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="H155" t="s">
-        <v>923</v>
-      </c>
-      <c r="J155" t="s">
+        <v>916</v>
+      </c>
+      <c r="I155" t="s">
         <v>17</v>
       </c>
-      <c r="L155" t="s">
+      <c r="K155" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="4">
         <v>45632</v>
       </c>
       <c r="B156" t="s">
+        <v>753</v>
+      </c>
+      <c r="C156" t="s">
+        <v>754</v>
+      </c>
+      <c r="D156" t="s">
         <v>755</v>
       </c>
-      <c r="C156" t="s">
+      <c r="E156" t="s">
         <v>756</v>
       </c>
-      <c r="D156" t="s">
+      <c r="F156" t="s">
         <v>757</v>
       </c>
-      <c r="E156" t="s">
-        <v>758</v>
-      </c>
-      <c r="F156" t="s">
-        <v>759</v>
-      </c>
       <c r="G156" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H156" t="s">
-        <v>936</v>
-      </c>
-      <c r="J156" t="s">
+        <v>928</v>
+      </c>
+      <c r="I156" t="s">
         <v>17</v>
       </c>
-      <c r="L156" t="s">
+      <c r="K156" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="4">
         <v>45632</v>
       </c>
       <c r="B157" t="s">
+        <v>758</v>
+      </c>
+      <c r="C157" t="s">
+        <v>759</v>
+      </c>
+      <c r="D157" t="s">
         <v>760</v>
       </c>
-      <c r="C157" t="s">
+      <c r="E157" t="s">
         <v>761</v>
       </c>
-      <c r="D157" t="s">
+      <c r="F157" t="s">
         <v>762</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
+        <v>923</v>
+      </c>
+      <c r="H157" t="s">
+        <v>915</v>
+      </c>
+      <c r="I157" t="s">
+        <v>17</v>
+      </c>
+      <c r="J157" t="s">
         <v>763</v>
       </c>
-      <c r="F157" t="s">
-        <v>764</v>
-      </c>
-      <c r="G157" t="s">
-        <v>931</v>
-      </c>
-      <c r="H157" t="s">
-        <v>921</v>
-      </c>
-      <c r="J157" t="s">
-        <v>17</v>
-      </c>
       <c r="K157" t="s">
-        <v>765</v>
-      </c>
-      <c r="L157" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="4">
         <v>45635</v>
       </c>
       <c r="B158" t="s">
+        <v>764</v>
+      </c>
+      <c r="C158" t="s">
+        <v>765</v>
+      </c>
+      <c r="D158" t="s">
         <v>766</v>
       </c>
-      <c r="C158" t="s">
+      <c r="E158" t="s">
         <v>767</v>
       </c>
-      <c r="D158" t="s">
+      <c r="F158" t="s">
         <v>768</v>
       </c>
-      <c r="E158" t="s">
+      <c r="G158" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H158" t="s">
+        <v>924</v>
+      </c>
+      <c r="I158" t="s">
+        <v>17</v>
+      </c>
+      <c r="J158" t="s">
         <v>769</v>
       </c>
-      <c r="F158" t="s">
-        <v>770</v>
-      </c>
-      <c r="G158" t="s">
-        <v>1010</v>
-      </c>
-      <c r="H158" t="s">
-        <v>932</v>
-      </c>
-      <c r="J158" t="s">
-        <v>17</v>
-      </c>
       <c r="K158" t="s">
-        <v>771</v>
-      </c>
-      <c r="L158" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="4">
         <v>45635</v>
       </c>
       <c r="B159" t="s">
+        <v>770</v>
+      </c>
+      <c r="C159" t="s">
+        <v>771</v>
+      </c>
+      <c r="D159" t="s">
         <v>772</v>
       </c>
-      <c r="C159" t="s">
+      <c r="E159" t="s">
         <v>773</v>
       </c>
-      <c r="D159" t="s">
+      <c r="F159" t="s">
         <v>774</v>
       </c>
-      <c r="E159" t="s">
-        <v>775</v>
-      </c>
-      <c r="F159" t="s">
-        <v>776</v>
-      </c>
       <c r="G159" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H159" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I159" t="s">
+        <v>51</v>
       </c>
       <c r="J159" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="K159" t="s">
-        <v>262</v>
-      </c>
-      <c r="L159" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="4">
         <v>45761</v>
       </c>
@@ -14099,197 +14252,197 @@
         <v>44</v>
       </c>
       <c r="C160" t="s">
+        <v>775</v>
+      </c>
+      <c r="D160" t="s">
+        <v>776</v>
+      </c>
+      <c r="E160" t="s">
+        <v>773</v>
+      </c>
+      <c r="F160" t="s">
         <v>777</v>
       </c>
-      <c r="D160" t="s">
-        <v>778</v>
-      </c>
-      <c r="E160" t="s">
-        <v>775</v>
-      </c>
-      <c r="F160" t="s">
-        <v>779</v>
-      </c>
       <c r="G160" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="H160" t="s">
-        <v>921</v>
-      </c>
-      <c r="J160" t="s">
+        <v>915</v>
+      </c>
+      <c r="I160" t="s">
         <v>17</v>
       </c>
-      <c r="L160" t="s">
+      <c r="K160" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="4">
         <v>45761</v>
       </c>
       <c r="B161" t="s">
+        <v>778</v>
+      </c>
+      <c r="C161" t="s">
+        <v>779</v>
+      </c>
+      <c r="D161" t="s">
         <v>780</v>
       </c>
-      <c r="C161" t="s">
+      <c r="E161" t="s">
         <v>781</v>
       </c>
-      <c r="D161" t="s">
+      <c r="F161" t="s">
         <v>782</v>
       </c>
-      <c r="E161" t="s">
+      <c r="G161" t="s">
+        <v>925</v>
+      </c>
+      <c r="H161" t="s">
+        <v>926</v>
+      </c>
+      <c r="I161" t="s">
+        <v>17</v>
+      </c>
+      <c r="J161" t="s">
         <v>783</v>
       </c>
-      <c r="F161" t="s">
-        <v>784</v>
-      </c>
-      <c r="G161" t="s">
-        <v>933</v>
-      </c>
-      <c r="H161" t="s">
-        <v>934</v>
-      </c>
-      <c r="J161" t="s">
-        <v>17</v>
-      </c>
       <c r="K161" t="s">
-        <v>785</v>
-      </c>
-      <c r="L161" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="4">
         <v>45761</v>
       </c>
       <c r="B162" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C162" t="s">
+        <v>784</v>
+      </c>
+      <c r="D162" t="s">
+        <v>785</v>
+      </c>
+      <c r="E162" t="s">
         <v>786</v>
       </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
         <v>787</v>
       </c>
-      <c r="E162" t="s">
-        <v>788</v>
-      </c>
-      <c r="F162" t="s">
-        <v>789</v>
-      </c>
       <c r="G162" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="H162" t="s">
-        <v>936</v>
-      </c>
-      <c r="J162" t="s">
+        <v>928</v>
+      </c>
+      <c r="I162" t="s">
         <v>17</v>
       </c>
-      <c r="L162" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K162" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="4">
         <v>45762</v>
       </c>
       <c r="B163" t="s">
+        <v>788</v>
+      </c>
+      <c r="C163" t="s">
+        <v>789</v>
+      </c>
+      <c r="D163" t="s">
         <v>790</v>
       </c>
-      <c r="C163" t="s">
+      <c r="E163" t="s">
         <v>791</v>
       </c>
-      <c r="D163" t="s">
+      <c r="F163" t="s">
         <v>792</v>
       </c>
-      <c r="E163" t="s">
-        <v>793</v>
-      </c>
-      <c r="F163" t="s">
-        <v>794</v>
-      </c>
       <c r="G163" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H163" t="s">
-        <v>934</v>
-      </c>
-      <c r="J163" t="s">
+        <v>926</v>
+      </c>
+      <c r="I163" t="s">
         <v>17</v>
       </c>
-      <c r="L163" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K163" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="4">
-        <v>45386</v>
+        <v>45762</v>
       </c>
       <c r="B164" t="s">
         <v>100</v>
       </c>
       <c r="C164" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D164" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E164" t="s">
-        <v>797</v>
+        <v>1063</v>
       </c>
       <c r="F164" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="G164" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="H164" t="s">
-        <v>921</v>
-      </c>
-      <c r="J164" t="s">
+        <v>915</v>
+      </c>
+      <c r="I164" t="s">
         <v>17</v>
       </c>
-      <c r="L164" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K164" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="4">
         <v>45761</v>
       </c>
       <c r="B165" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C165" t="s">
+        <v>795</v>
+      </c>
+      <c r="D165" t="s">
+        <v>796</v>
+      </c>
+      <c r="E165" t="s">
+        <v>797</v>
+      </c>
+      <c r="F165" t="s">
         <v>798</v>
       </c>
-      <c r="D165" t="s">
+      <c r="G165" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H165" t="s">
+        <v>915</v>
+      </c>
+      <c r="I165" t="s">
+        <v>17</v>
+      </c>
+      <c r="J165" t="s">
         <v>799</v>
       </c>
-      <c r="E165" t="s">
-        <v>800</v>
-      </c>
-      <c r="F165" t="s">
-        <v>801</v>
-      </c>
-      <c r="G165" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H165" t="s">
-        <v>921</v>
-      </c>
-      <c r="J165" t="s">
-        <v>17</v>
-      </c>
       <c r="K165" t="s">
-        <v>802</v>
-      </c>
-      <c r="L165" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="4">
         <v>45762</v>
       </c>
@@ -14297,694 +14450,718 @@
         <v>238</v>
       </c>
       <c r="C166" t="s">
+        <v>800</v>
+      </c>
+      <c r="D166" t="s">
+        <v>801</v>
+      </c>
+      <c r="F166" t="s">
+        <v>802</v>
+      </c>
+      <c r="G166" t="s">
+        <v>927</v>
+      </c>
+      <c r="H166" t="s">
+        <v>928</v>
+      </c>
+      <c r="I166" t="s">
+        <v>17</v>
+      </c>
+      <c r="K166" t="s">
         <v>803</v>
       </c>
-      <c r="D166" t="s">
-        <v>804</v>
-      </c>
-      <c r="F166" t="s">
-        <v>805</v>
-      </c>
-      <c r="G166" t="s">
-        <v>935</v>
-      </c>
-      <c r="H166" t="s">
-        <v>936</v>
-      </c>
-      <c r="J166" t="s">
-        <v>17</v>
-      </c>
-      <c r="L166" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="4">
         <v>45762</v>
       </c>
       <c r="B167" t="s">
+        <v>804</v>
+      </c>
+      <c r="C167" t="s">
+        <v>805</v>
+      </c>
+      <c r="D167" t="s">
+        <v>806</v>
+      </c>
+      <c r="E167" t="s">
         <v>807</v>
       </c>
-      <c r="C167" t="s">
+      <c r="F167" t="s">
         <v>808</v>
       </c>
-      <c r="D167" t="s">
-        <v>809</v>
-      </c>
-      <c r="E167" t="s">
-        <v>810</v>
-      </c>
-      <c r="F167" t="s">
-        <v>811</v>
-      </c>
-      <c r="J167" t="s">
+      <c r="G167" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I167" t="s">
         <v>70</v>
       </c>
-      <c r="L167" t="s">
+      <c r="K167" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="4">
         <v>45762</v>
       </c>
       <c r="B168" t="s">
+        <v>809</v>
+      </c>
+      <c r="C168" t="s">
+        <v>810</v>
+      </c>
+      <c r="D168" t="s">
+        <v>811</v>
+      </c>
+      <c r="E168" t="s">
         <v>812</v>
       </c>
-      <c r="C168" t="s">
+      <c r="F168" t="s">
         <v>813</v>
       </c>
-      <c r="D168" t="s">
-        <v>814</v>
-      </c>
-      <c r="E168" t="s">
-        <v>815</v>
-      </c>
-      <c r="F168" t="s">
-        <v>816</v>
-      </c>
       <c r="G168" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="H168" t="s">
-        <v>934</v>
-      </c>
-      <c r="J168" t="s">
+        <v>926</v>
+      </c>
+      <c r="I168" t="s">
         <v>17</v>
       </c>
-      <c r="L168" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K168" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="4">
         <v>45762</v>
       </c>
       <c r="B169" t="s">
+        <v>814</v>
+      </c>
+      <c r="C169" t="s">
+        <v>815</v>
+      </c>
+      <c r="D169" t="s">
+        <v>816</v>
+      </c>
+      <c r="E169" t="s">
+        <v>719</v>
+      </c>
+      <c r="F169" t="s">
         <v>817</v>
       </c>
-      <c r="C169" t="s">
+      <c r="G169" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H169" t="s">
+        <v>921</v>
+      </c>
+      <c r="I169" t="s">
+        <v>17</v>
+      </c>
+      <c r="K169" t="s">
         <v>818</v>
       </c>
-      <c r="D169" t="s">
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A170" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B170" t="s">
         <v>819</v>
       </c>
-      <c r="E169" t="s">
-        <v>720</v>
-      </c>
-      <c r="F169" t="s">
+      <c r="C170" t="s">
         <v>820</v>
       </c>
-      <c r="G169" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H169" t="s">
-        <v>929</v>
-      </c>
-      <c r="J169" t="s">
+      <c r="D170" t="s">
+        <v>821</v>
+      </c>
+      <c r="E170" t="s">
+        <v>822</v>
+      </c>
+      <c r="F170" t="s">
+        <v>823</v>
+      </c>
+      <c r="G170" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H170" t="s">
+        <v>918</v>
+      </c>
+      <c r="I170" t="s">
+        <v>51</v>
+      </c>
+      <c r="K170" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A171" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B171" t="s">
+        <v>824</v>
+      </c>
+      <c r="C171" t="s">
+        <v>825</v>
+      </c>
+      <c r="D171" t="s">
+        <v>826</v>
+      </c>
+      <c r="E171" t="s">
+        <v>827</v>
+      </c>
+      <c r="F171" t="s">
+        <v>828</v>
+      </c>
+      <c r="G171" t="s">
+        <v>981</v>
+      </c>
+      <c r="H171" t="s">
+        <v>980</v>
+      </c>
+      <c r="I171" t="s">
+        <v>51</v>
+      </c>
+      <c r="J171" t="s">
+        <v>83</v>
+      </c>
+      <c r="K171" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A172" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B172" t="s">
+        <v>539</v>
+      </c>
+      <c r="C172" t="s">
+        <v>829</v>
+      </c>
+      <c r="D172" t="s">
+        <v>830</v>
+      </c>
+      <c r="E172" t="s">
+        <v>831</v>
+      </c>
+      <c r="F172" t="s">
+        <v>832</v>
+      </c>
+      <c r="G172" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H172" t="s">
+        <v>938</v>
+      </c>
+      <c r="I172" t="s">
+        <v>51</v>
+      </c>
+      <c r="J172" t="s">
+        <v>833</v>
+      </c>
+      <c r="K172" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A173" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B173" t="s">
+        <v>835</v>
+      </c>
+      <c r="C173" t="s">
+        <v>836</v>
+      </c>
+      <c r="D173" t="s">
+        <v>837</v>
+      </c>
+      <c r="E173" t="s">
+        <v>838</v>
+      </c>
+      <c r="F173" t="s">
+        <v>839</v>
+      </c>
+      <c r="G173" t="s">
+        <v>919</v>
+      </c>
+      <c r="H173" t="s">
+        <v>919</v>
+      </c>
+      <c r="I173" t="s">
         <v>17</v>
       </c>
-      <c r="L169" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A170" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B170" t="s">
-        <v>822</v>
-      </c>
-      <c r="C170" t="s">
-        <v>823</v>
-      </c>
-      <c r="D170" t="s">
-        <v>824</v>
-      </c>
-      <c r="E170" t="s">
-        <v>825</v>
-      </c>
-      <c r="F170" t="s">
-        <v>826</v>
-      </c>
-      <c r="G170" t="s">
-        <v>1016</v>
-      </c>
-      <c r="H170" t="s">
-        <v>926</v>
-      </c>
-      <c r="J170" t="s">
-        <v>51</v>
-      </c>
-      <c r="L170" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A171" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B171" t="s">
-        <v>827</v>
-      </c>
-      <c r="C171" t="s">
-        <v>828</v>
-      </c>
-      <c r="D171" t="s">
-        <v>829</v>
-      </c>
-      <c r="E171" t="s">
-        <v>830</v>
-      </c>
-      <c r="F171" t="s">
-        <v>831</v>
-      </c>
-      <c r="G171" t="s">
-        <v>989</v>
-      </c>
-      <c r="H171" t="s">
-        <v>988</v>
-      </c>
-      <c r="J171" t="s">
-        <v>51</v>
-      </c>
-      <c r="K171" t="s">
-        <v>83</v>
-      </c>
-      <c r="L171" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A172" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B172" t="s">
-        <v>540</v>
-      </c>
-      <c r="C172" t="s">
-        <v>832</v>
-      </c>
-      <c r="D172" t="s">
-        <v>833</v>
-      </c>
-      <c r="E172" t="s">
-        <v>834</v>
-      </c>
-      <c r="F172" t="s">
-        <v>835</v>
-      </c>
-      <c r="G172" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H172" t="s">
-        <v>946</v>
-      </c>
-      <c r="J172" t="s">
-        <v>51</v>
-      </c>
-      <c r="K172" t="s">
-        <v>836</v>
-      </c>
-      <c r="L172" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A173" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B173" t="s">
-        <v>838</v>
-      </c>
-      <c r="C173" t="s">
-        <v>839</v>
-      </c>
-      <c r="D173" t="s">
-        <v>840</v>
-      </c>
-      <c r="E173" t="s">
-        <v>841</v>
-      </c>
-      <c r="F173" t="s">
-        <v>842</v>
-      </c>
-      <c r="G173" t="s">
-        <v>927</v>
-      </c>
-      <c r="H173" t="s">
-        <v>927</v>
-      </c>
-      <c r="J173" t="s">
-        <v>17</v>
-      </c>
-      <c r="L173" t="s">
+      <c r="K173" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="B174" t="s">
         <v>40</v>
       </c>
       <c r="C174" t="s">
+        <v>840</v>
+      </c>
+      <c r="D174" t="s">
+        <v>841</v>
+      </c>
+      <c r="E174" t="s">
+        <v>842</v>
+      </c>
+      <c r="F174" t="s">
         <v>843</v>
       </c>
-      <c r="D174" t="s">
-        <v>844</v>
-      </c>
-      <c r="E174" t="s">
-        <v>845</v>
-      </c>
-      <c r="F174" t="s">
-        <v>846</v>
-      </c>
       <c r="G174" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H174" t="s">
-        <v>934</v>
-      </c>
-      <c r="J174" t="s">
+        <v>926</v>
+      </c>
+      <c r="I174" t="s">
         <v>17</v>
       </c>
-      <c r="L174" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K174" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="4">
         <v>45762</v>
       </c>
       <c r="B175" t="s">
+        <v>844</v>
+      </c>
+      <c r="C175" t="s">
+        <v>845</v>
+      </c>
+      <c r="D175" t="s">
+        <v>846</v>
+      </c>
+      <c r="E175" t="s">
         <v>847</v>
       </c>
-      <c r="C175" t="s">
+      <c r="F175" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G175" t="s">
+        <v>946</v>
+      </c>
+      <c r="H175" t="s">
+        <v>947</v>
+      </c>
+      <c r="I175" t="s">
+        <v>51</v>
+      </c>
+      <c r="J175" t="s">
         <v>848</v>
       </c>
-      <c r="D175" t="s">
-        <v>849</v>
-      </c>
-      <c r="E175" t="s">
-        <v>850</v>
-      </c>
-      <c r="F175" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G175" t="s">
-        <v>954</v>
-      </c>
-      <c r="H175" t="s">
-        <v>955</v>
-      </c>
-      <c r="J175" t="s">
-        <v>51</v>
-      </c>
       <c r="K175" t="s">
-        <v>851</v>
-      </c>
-      <c r="L175" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="4">
         <v>45762</v>
       </c>
       <c r="B176" t="s">
+        <v>849</v>
+      </c>
+      <c r="C176" t="s">
+        <v>850</v>
+      </c>
+      <c r="D176" t="s">
+        <v>851</v>
+      </c>
+      <c r="E176" t="s">
         <v>852</v>
       </c>
-      <c r="C176" t="s">
+      <c r="F176" t="s">
         <v>853</v>
       </c>
-      <c r="D176" t="s">
+      <c r="G176" t="s">
+        <v>923</v>
+      </c>
+      <c r="H176" t="s">
+        <v>926</v>
+      </c>
+      <c r="I176" t="s">
+        <v>17</v>
+      </c>
+      <c r="J176" t="s">
         <v>854</v>
       </c>
-      <c r="E176" t="s">
-        <v>855</v>
-      </c>
-      <c r="F176" t="s">
-        <v>856</v>
-      </c>
-      <c r="G176" t="s">
-        <v>931</v>
-      </c>
-      <c r="H176" t="s">
-        <v>934</v>
-      </c>
-      <c r="J176" t="s">
-        <v>17</v>
-      </c>
       <c r="K176" t="s">
-        <v>857</v>
-      </c>
-      <c r="L176" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="4">
         <v>45762</v>
       </c>
       <c r="B177" t="s">
+        <v>855</v>
+      </c>
+      <c r="C177" t="s">
+        <v>856</v>
+      </c>
+      <c r="D177" t="s">
+        <v>857</v>
+      </c>
+      <c r="E177" t="s">
         <v>858</v>
       </c>
-      <c r="C177" t="s">
+      <c r="F177" t="s">
         <v>859</v>
       </c>
-      <c r="D177" t="s">
+      <c r="G177" t="s">
+        <v>923</v>
+      </c>
+      <c r="H177" t="s">
+        <v>926</v>
+      </c>
+      <c r="I177" t="s">
+        <v>17</v>
+      </c>
+      <c r="J177" t="s">
         <v>860</v>
       </c>
-      <c r="E177" t="s">
-        <v>861</v>
-      </c>
-      <c r="F177" t="s">
-        <v>862</v>
-      </c>
-      <c r="G177" t="s">
-        <v>931</v>
-      </c>
-      <c r="H177" t="s">
-        <v>934</v>
-      </c>
-      <c r="J177" t="s">
-        <v>17</v>
-      </c>
       <c r="K177" t="s">
-        <v>863</v>
-      </c>
-      <c r="L177" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="4">
         <v>45762</v>
       </c>
       <c r="B178" t="s">
+        <v>861</v>
+      </c>
+      <c r="C178" t="s">
+        <v>862</v>
+      </c>
+      <c r="D178" t="s">
+        <v>863</v>
+      </c>
+      <c r="E178" t="s">
         <v>864</v>
       </c>
-      <c r="C178" t="s">
+      <c r="F178" t="s">
         <v>865</v>
       </c>
-      <c r="D178" t="s">
-        <v>866</v>
-      </c>
-      <c r="E178" t="s">
-        <v>867</v>
-      </c>
-      <c r="F178" t="s">
-        <v>868</v>
-      </c>
       <c r="G178" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H178" t="s">
-        <v>936</v>
-      </c>
-      <c r="J178" t="s">
+        <v>928</v>
+      </c>
+      <c r="I178" t="s">
         <v>17</v>
       </c>
-      <c r="L178" t="s">
+      <c r="K178" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="4">
         <v>45762</v>
       </c>
       <c r="B179" t="s">
+        <v>866</v>
+      </c>
+      <c r="C179" t="s">
+        <v>867</v>
+      </c>
+      <c r="D179" t="s">
+        <v>868</v>
+      </c>
+      <c r="E179" t="s">
         <v>869</v>
       </c>
-      <c r="C179" t="s">
+      <c r="F179" t="s">
         <v>870</v>
       </c>
-      <c r="D179" t="s">
+      <c r="G179" t="s">
+        <v>953</v>
+      </c>
+      <c r="H179" t="s">
+        <v>940</v>
+      </c>
+      <c r="I179" t="s">
+        <v>17</v>
+      </c>
+      <c r="K179" t="s">
         <v>871</v>
       </c>
-      <c r="E179" t="s">
-        <v>872</v>
-      </c>
-      <c r="F179" t="s">
-        <v>873</v>
-      </c>
-      <c r="G179" t="s">
-        <v>961</v>
-      </c>
-      <c r="H179" t="s">
-        <v>948</v>
-      </c>
-      <c r="J179" t="s">
-        <v>17</v>
-      </c>
-      <c r="L179" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="4">
         <v>45762</v>
       </c>
       <c r="B180" t="s">
+        <v>872</v>
+      </c>
+      <c r="C180" t="s">
+        <v>873</v>
+      </c>
+      <c r="D180" t="s">
+        <v>874</v>
+      </c>
+      <c r="E180" t="s">
         <v>875</v>
       </c>
-      <c r="C180" t="s">
+      <c r="F180" t="s">
         <v>876</v>
       </c>
-      <c r="D180" t="s">
-        <v>877</v>
-      </c>
-      <c r="E180" t="s">
-        <v>878</v>
-      </c>
-      <c r="F180" t="s">
-        <v>879</v>
-      </c>
       <c r="G180" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H180" t="s">
-        <v>936</v>
-      </c>
-      <c r="J180" t="s">
+        <v>928</v>
+      </c>
+      <c r="I180" t="s">
         <v>17</v>
       </c>
-      <c r="L180" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K180" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="4">
         <v>45762</v>
       </c>
       <c r="B181" t="s">
+        <v>877</v>
+      </c>
+      <c r="C181" t="s">
+        <v>878</v>
+      </c>
+      <c r="D181" t="s">
+        <v>879</v>
+      </c>
+      <c r="E181" t="s">
         <v>880</v>
       </c>
-      <c r="C181" t="s">
-        <v>881</v>
-      </c>
-      <c r="D181" t="s">
-        <v>882</v>
-      </c>
-      <c r="E181" t="s">
-        <v>883</v>
-      </c>
       <c r="F181" t="s">
-        <v>784</v>
-      </c>
-      <c r="J181" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H181" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I181" t="s">
         <v>70</v>
       </c>
-      <c r="L181" t="s">
+      <c r="K181" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="4">
         <v>45762</v>
       </c>
       <c r="B182" t="s">
+        <v>881</v>
+      </c>
+      <c r="C182" t="s">
+        <v>882</v>
+      </c>
+      <c r="D182" t="s">
+        <v>883</v>
+      </c>
+      <c r="E182" t="s">
+        <v>786</v>
+      </c>
+      <c r="F182" t="s">
         <v>884</v>
       </c>
-      <c r="C182" t="s">
+      <c r="G182" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H182" t="s">
+        <v>918</v>
+      </c>
+      <c r="I182" t="s">
+        <v>51</v>
+      </c>
+      <c r="J182" t="s">
         <v>885</v>
       </c>
-      <c r="D182" t="s">
+      <c r="K182" t="s">
         <v>886</v>
       </c>
-      <c r="E182" t="s">
-        <v>788</v>
-      </c>
-      <c r="F182" t="s">
-        <v>887</v>
-      </c>
-      <c r="G182" t="s">
-        <v>1019</v>
-      </c>
-      <c r="H182" t="s">
-        <v>926</v>
-      </c>
-      <c r="J182" t="s">
-        <v>51</v>
-      </c>
-      <c r="K182" t="s">
-        <v>888</v>
-      </c>
-      <c r="L182" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="4">
         <v>45762</v>
       </c>
       <c r="B183" t="s">
+        <v>887</v>
+      </c>
+      <c r="C183" t="s">
+        <v>888</v>
+      </c>
+      <c r="D183" t="s">
+        <v>889</v>
+      </c>
+      <c r="E183" t="s">
         <v>890</v>
       </c>
-      <c r="C183" t="s">
+      <c r="F183" t="s">
         <v>891</v>
       </c>
-      <c r="D183" t="s">
-        <v>892</v>
-      </c>
-      <c r="E183" t="s">
-        <v>893</v>
-      </c>
-      <c r="F183" t="s">
-        <v>894</v>
-      </c>
       <c r="G183" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="H183" t="s">
-        <v>952</v>
+        <v>944</v>
+      </c>
+      <c r="I183" t="s">
+        <v>51</v>
       </c>
       <c r="J183" t="s">
-        <v>51</v>
+        <v>848</v>
       </c>
       <c r="K183" t="s">
-        <v>851</v>
-      </c>
-      <c r="L183" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="4">
         <v>45762</v>
       </c>
       <c r="B184" t="s">
+        <v>892</v>
+      </c>
+      <c r="C184" t="s">
+        <v>893</v>
+      </c>
+      <c r="D184" t="s">
+        <v>894</v>
+      </c>
+      <c r="F184" t="s">
         <v>895</v>
       </c>
-      <c r="C184" t="s">
-        <v>896</v>
-      </c>
-      <c r="D184" t="s">
-        <v>897</v>
-      </c>
-      <c r="F184" t="s">
-        <v>898</v>
-      </c>
       <c r="G184" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="H184" t="s">
-        <v>988</v>
+        <v>980</v>
+      </c>
+      <c r="I184" t="s">
+        <v>51</v>
       </c>
       <c r="J184" t="s">
-        <v>51</v>
+        <v>848</v>
       </c>
       <c r="K184" t="s">
-        <v>851</v>
-      </c>
-      <c r="L184" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="4">
         <v>45763</v>
       </c>
       <c r="B185" t="s">
+        <v>896</v>
+      </c>
+      <c r="C185" t="s">
+        <v>897</v>
+      </c>
+      <c r="D185" t="s">
+        <v>898</v>
+      </c>
+      <c r="E185" t="s">
         <v>899</v>
       </c>
-      <c r="C185" t="s">
+      <c r="F185" t="s">
         <v>900</v>
       </c>
-      <c r="D185" t="s">
+      <c r="G185" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H185" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I185" t="s">
+        <v>70</v>
+      </c>
+      <c r="K185" t="s">
         <v>901</v>
       </c>
-      <c r="E185" t="s">
-        <v>902</v>
-      </c>
-      <c r="F185" t="s">
-        <v>903</v>
-      </c>
-      <c r="J185" t="s">
-        <v>70</v>
-      </c>
-      <c r="L185" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="4">
         <v>45764</v>
       </c>
       <c r="B186" t="s">
+        <v>902</v>
+      </c>
+      <c r="C186" t="s">
+        <v>903</v>
+      </c>
+      <c r="D186" t="s">
+        <v>904</v>
+      </c>
+      <c r="F186" t="s">
         <v>905</v>
       </c>
-      <c r="C186" t="s">
-        <v>906</v>
-      </c>
-      <c r="D186" t="s">
-        <v>907</v>
-      </c>
-      <c r="F186" t="s">
-        <v>908</v>
-      </c>
-      <c r="J186" t="s">
+      <c r="G186" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H186" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I186" t="s">
         <v>70</v>
       </c>
-      <c r="L186" t="s">
+      <c r="K186" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="4">
         <v>45764</v>
       </c>
       <c r="B187" t="s">
+        <v>906</v>
+      </c>
+      <c r="C187" t="s">
+        <v>907</v>
+      </c>
+      <c r="D187" t="s">
+        <v>908</v>
+      </c>
+      <c r="E187" t="s">
         <v>909</v>
       </c>
-      <c r="C187" t="s">
+      <c r="F187" t="s">
         <v>910</v>
       </c>
-      <c r="D187" t="s">
+      <c r="G187" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H187" t="s">
+        <v>926</v>
+      </c>
+      <c r="I187" t="s">
+        <v>17</v>
+      </c>
+      <c r="J187" t="s">
         <v>911</v>
       </c>
-      <c r="E187" t="s">
+      <c r="K187" t="s">
         <v>912</v>
-      </c>
-      <c r="F187" t="s">
-        <v>913</v>
-      </c>
-      <c r="G187" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H187" t="s">
-        <v>934</v>
-      </c>
-      <c r="J187" t="s">
-        <v>17</v>
-      </c>
-      <c r="K187" t="s">
-        <v>914</v>
-      </c>
-      <c r="L187" t="s">
-        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1064">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -10742,7 +10742,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
-        <v>44191</v>
+        <v>44526</v>
       </c>
       <c r="B49" t="s">
         <v>248</v>
@@ -10764,6 +10764,9 @@
       </c>
       <c r="I49" t="s">
         <v>51</v>
+      </c>
+      <c r="K49" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -10800,7 +10803,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
-        <v>44191</v>
+        <v>44556</v>
       </c>
       <c r="B51" t="s">
         <v>258</v>

--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -10803,7 +10803,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
-        <v>44556</v>
+        <v>44526</v>
       </c>
       <c r="B51" t="s">
         <v>258</v>

--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1065">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -3216,6 +3216,9 @@
   </si>
   <si>
     <t>07-48-24-99-96</t>
+  </si>
+  <si>
+    <t>KOUAME Kouassi Yves Herman</t>
   </si>
 </sst>
 </file>
@@ -9480,7 +9483,7 @@
         <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>1064</v>
       </c>
       <c r="F9" t="s">
         <v>50</v>

--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -1,30 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\père kpoda\env\Pere_kpoda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Python documents\Pere_kpoda\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3B6319-0725-446A-B45B-541F877BF1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graphique1" sheetId="9" r:id="rId1"/>
     <sheet name="Feuil1" sheetId="8" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="2020" sheetId="10" r:id="rId4"/>
+    <sheet name="2021" sheetId="11" r:id="rId5"/>
+    <sheet name="2022" sheetId="12" r:id="rId6"/>
+    <sheet name="2023" sheetId="13" r:id="rId7"/>
+    <sheet name="2024" sheetId="14" r:id="rId8"/>
+    <sheet name="2025" sheetId="15" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3672" uniqueCount="1064">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -3221,7 +3228,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
@@ -3433,6 +3440,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -4656,7 +4704,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Graphique1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4697,7 +4745,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="45794.60682789352" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="45794.60682789352" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:M187" sheet="Sheet1"/>
   </cacheSource>
@@ -7621,7 +7669,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tableau croisé dynamique5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="Tableau croisé dynamique5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:C76" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="13">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -8333,17 +8381,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
   <dimension ref="A3:C76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -8354,7 +8402,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -8365,7 +8413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -8376,7 +8424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -8387,7 +8435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -8398,7 +8446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -8409,7 +8457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -8420,7 +8468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -8431,7 +8479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -8442,7 +8490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -8453,7 +8501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -8464,7 +8512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -8475,7 +8523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -8486,7 +8534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -8497,7 +8545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -8508,7 +8556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -8519,7 +8567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -8530,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -8541,7 +8589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -8552,7 +8600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -8563,7 +8611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -8574,7 +8622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -8585,7 +8633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -8596,7 +8644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -8607,7 +8655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -8618,7 +8666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -8629,7 +8677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -8640,7 +8688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -8651,7 +8699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -8662,7 +8710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -8673,7 +8721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -8684,7 +8732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -8695,7 +8743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -8706,7 +8754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -8717,7 +8765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -8728,7 +8776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -8739,7 +8787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -8750,7 +8798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -8761,7 +8809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -8772,7 +8820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -8783,7 +8831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -8794,7 +8842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -8805,7 +8853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -8816,7 +8864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -8827,7 +8875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -8838,7 +8886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -8849,7 +8897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -8860,7 +8908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -8871,7 +8919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -8882,7 +8930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -8893,7 +8941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -8904,7 +8952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>51</v>
       </c>
@@ -8915,7 +8963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -8926,7 +8974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>51</v>
       </c>
@@ -8937,7 +8985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -8948,7 +8996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -8959,7 +9007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>51</v>
       </c>
@@ -8970,7 +9018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -8981,7 +9029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -8992,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -9003,7 +9051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -9014,7 +9062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>51</v>
       </c>
@@ -9025,7 +9073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -9036,7 +9084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -9047,7 +9095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -9058,7 +9106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>51</v>
       </c>
@@ -9069,7 +9117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>51</v>
       </c>
@@ -9080,7 +9128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -9091,7 +9139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>51</v>
       </c>
@@ -9102,7 +9150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>51</v>
       </c>
@@ -9113,7 +9161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>51</v>
       </c>
@@ -9124,7 +9172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>51</v>
       </c>
@@ -9135,7 +9183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>51</v>
       </c>
@@ -9146,7 +9194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>51</v>
       </c>
@@ -9163,27 +9211,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:M187"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="144" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="59.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9224,7 +9272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>44123</v>
       </c>
@@ -9259,7 +9307,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>44123</v>
       </c>
@@ -9294,7 +9342,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>44120</v>
       </c>
@@ -9329,7 +9377,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>44120</v>
       </c>
@@ -9364,7 +9412,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>44166</v>
       </c>
@@ -9399,7 +9447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>44167</v>
       </c>
@@ -9434,7 +9482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>44167</v>
       </c>
@@ -9469,7 +9517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>44167</v>
       </c>
@@ -9504,7 +9552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>52</v>
       </c>
@@ -9539,7 +9587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>52</v>
       </c>
@@ -9574,7 +9622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
@@ -9606,7 +9654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>71</v>
       </c>
@@ -9641,7 +9689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>78</v>
       </c>
@@ -9676,7 +9724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -9708,7 +9756,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>78</v>
       </c>
@@ -9743,7 +9791,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>78</v>
       </c>
@@ -9778,7 +9826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>78</v>
       </c>
@@ -9813,7 +9861,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>78</v>
       </c>
@@ -9845,7 +9893,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>78</v>
       </c>
@@ -9880,7 +9928,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>78</v>
       </c>
@@ -9915,7 +9963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>78</v>
       </c>
@@ -9950,7 +9998,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>78</v>
       </c>
@@ -9985,7 +10033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>128</v>
       </c>
@@ -10020,7 +10068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>128</v>
       </c>
@@ -10055,7 +10103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>128</v>
       </c>
@@ -10090,7 +10138,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>128</v>
       </c>
@@ -10125,7 +10173,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>128</v>
       </c>
@@ -10157,7 +10205,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>154</v>
       </c>
@@ -10186,7 +10234,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>154</v>
       </c>
@@ -10215,7 +10263,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>154</v>
       </c>
@@ -10244,7 +10292,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>154</v>
       </c>
@@ -10273,7 +10321,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>154</v>
       </c>
@@ -10302,7 +10350,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>177</v>
       </c>
@@ -10328,7 +10376,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>177</v>
       </c>
@@ -10357,7 +10405,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>187</v>
       </c>
@@ -10386,7 +10434,7 @@
         <v>44503</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>187</v>
       </c>
@@ -10415,7 +10463,7 @@
         <v>44504</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>196</v>
       </c>
@@ -10441,7 +10489,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>200</v>
       </c>
@@ -10470,7 +10518,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>205</v>
       </c>
@@ -10499,7 +10547,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>205</v>
       </c>
@@ -10528,7 +10576,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>205</v>
       </c>
@@ -10557,7 +10605,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>205</v>
       </c>
@@ -10586,7 +10634,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>205</v>
       </c>
@@ -10615,7 +10663,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>227</v>
       </c>
@@ -10647,7 +10695,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>227</v>
       </c>
@@ -10676,7 +10724,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>227</v>
       </c>
@@ -10708,7 +10756,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>44524</v>
       </c>
@@ -10740,7 +10788,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>44526</v>
       </c>
@@ -10769,7 +10817,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>44526</v>
       </c>
@@ -10801,7 +10849,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>44526</v>
       </c>
@@ -10833,7 +10881,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>44612</v>
       </c>
@@ -10865,7 +10913,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>44620</v>
       </c>
@@ -10897,7 +10945,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>44620</v>
       </c>
@@ -10929,7 +10977,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>44255</v>
       </c>
@@ -10961,7 +11009,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>44255</v>
       </c>
@@ -10993,7 +11041,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>44255</v>
       </c>
@@ -11022,7 +11070,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>44255</v>
       </c>
@@ -11054,7 +11102,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>44255</v>
       </c>
@@ -11086,7 +11134,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>44620</v>
       </c>
@@ -11118,7 +11166,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>44620</v>
       </c>
@@ -11150,7 +11198,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>44620</v>
       </c>
@@ -11179,7 +11227,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>44620</v>
       </c>
@@ -11211,7 +11259,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>44620</v>
       </c>
@@ -11240,7 +11288,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>44620</v>
       </c>
@@ -11272,7 +11320,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>44620</v>
       </c>
@@ -11301,7 +11349,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>44623</v>
       </c>
@@ -11330,7 +11378,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>44833</v>
       </c>
@@ -11365,7 +11413,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>44833</v>
       </c>
@@ -11397,7 +11445,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>44844</v>
       </c>
@@ -11432,7 +11480,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>44620</v>
       </c>
@@ -11461,7 +11509,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>44844</v>
       </c>
@@ -11493,7 +11541,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>44844</v>
       </c>
@@ -11525,7 +11573,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>44844</v>
       </c>
@@ -11557,7 +11605,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>44944</v>
       </c>
@@ -11589,7 +11637,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>44945</v>
       </c>
@@ -11618,7 +11666,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>44945</v>
       </c>
@@ -11647,7 +11695,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>44946</v>
       </c>
@@ -11676,7 +11724,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>44844</v>
       </c>
@@ -11705,7 +11753,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>44952</v>
       </c>
@@ -11734,7 +11782,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>44620</v>
       </c>
@@ -11763,7 +11811,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>44957</v>
       </c>
@@ -11798,7 +11846,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>45013</v>
       </c>
@@ -11827,7 +11875,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>45013</v>
       </c>
@@ -11856,7 +11904,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>45386</v>
       </c>
@@ -11888,7 +11936,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>45103</v>
       </c>
@@ -11920,7 +11968,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>45107</v>
       </c>
@@ -11949,7 +11997,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>45107</v>
       </c>
@@ -11978,7 +12026,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>45107</v>
       </c>
@@ -12007,7 +12055,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>45107</v>
       </c>
@@ -12036,7 +12084,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>45107</v>
       </c>
@@ -12068,7 +12116,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>45107</v>
       </c>
@@ -12097,7 +12145,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>45110</v>
       </c>
@@ -12129,7 +12177,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>45110</v>
       </c>
@@ -12161,7 +12209,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>45110</v>
       </c>
@@ -12193,7 +12241,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>45110</v>
       </c>
@@ -12225,7 +12273,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>45110</v>
       </c>
@@ -12257,7 +12305,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>45110</v>
       </c>
@@ -12289,7 +12337,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>45110</v>
       </c>
@@ -12321,7 +12369,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>45110</v>
       </c>
@@ -12350,7 +12398,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>45111</v>
       </c>
@@ -12382,7 +12430,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>45112</v>
       </c>
@@ -12414,7 +12462,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>45113</v>
       </c>
@@ -12443,7 +12491,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>45116</v>
       </c>
@@ -12472,7 +12520,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>45240</v>
       </c>
@@ -12501,7 +12549,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>45240</v>
       </c>
@@ -12533,7 +12581,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>45240</v>
       </c>
@@ -12562,7 +12610,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>45296</v>
       </c>
@@ -12594,7 +12642,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>45385</v>
       </c>
@@ -12626,7 +12674,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>45385</v>
       </c>
@@ -12658,7 +12706,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>45385</v>
       </c>
@@ -12690,7 +12738,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>45385</v>
       </c>
@@ -12719,7 +12767,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>45385</v>
       </c>
@@ -12748,7 +12796,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>45385</v>
       </c>
@@ -12777,7 +12825,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>45385</v>
       </c>
@@ -12806,7 +12854,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>45385</v>
       </c>
@@ -12835,7 +12883,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>45386</v>
       </c>
@@ -12867,7 +12915,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>45386</v>
       </c>
@@ -12899,7 +12947,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>45386</v>
       </c>
@@ -12931,7 +12979,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>45386</v>
       </c>
@@ -12960,7 +13008,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>45386</v>
       </c>
@@ -12992,7 +13040,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>45387</v>
       </c>
@@ -13024,7 +13072,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>45394</v>
       </c>
@@ -13053,7 +13101,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>45469</v>
       </c>
@@ -13085,7 +13133,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>45481</v>
       </c>
@@ -13114,7 +13162,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>45483</v>
       </c>
@@ -13149,7 +13197,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>594</v>
       </c>
@@ -13181,7 +13229,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>594</v>
       </c>
@@ -13216,7 +13264,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>594</v>
       </c>
@@ -13251,7 +13299,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>594</v>
       </c>
@@ -13283,7 +13331,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>594</v>
       </c>
@@ -13318,7 +13366,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>594</v>
       </c>
@@ -13350,7 +13398,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>594</v>
       </c>
@@ -13385,7 +13433,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>594</v>
       </c>
@@ -13420,7 +13468,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>594</v>
       </c>
@@ -13455,7 +13503,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>594</v>
       </c>
@@ -13490,7 +13538,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>594</v>
       </c>
@@ -13525,7 +13573,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>653</v>
       </c>
@@ -13560,7 +13608,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>653</v>
       </c>
@@ -13592,7 +13640,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>653</v>
       </c>
@@ -13624,7 +13672,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>669</v>
       </c>
@@ -13656,7 +13704,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>676</v>
       </c>
@@ -13691,7 +13739,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>684</v>
       </c>
@@ -13720,7 +13768,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>684</v>
       </c>
@@ -13749,7 +13797,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>45490</v>
       </c>
@@ -13784,7 +13832,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>45490</v>
       </c>
@@ -13816,7 +13864,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>45490</v>
       </c>
@@ -13848,7 +13896,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>45490</v>
       </c>
@@ -13883,7 +13931,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>45492</v>
       </c>
@@ -13915,7 +13963,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>45492</v>
       </c>
@@ -13947,7 +13995,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>45498</v>
       </c>
@@ -13976,7 +14024,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>45650</v>
       </c>
@@ -14011,7 +14059,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>45632</v>
       </c>
@@ -14043,7 +14091,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>45632</v>
       </c>
@@ -14078,7 +14126,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>45632</v>
       </c>
@@ -14110,7 +14158,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>45632</v>
       </c>
@@ -14142,7 +14190,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>45632</v>
       </c>
@@ -14177,7 +14225,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>45635</v>
       </c>
@@ -14212,7 +14260,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>45635</v>
       </c>
@@ -14247,7 +14295,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>45761</v>
       </c>
@@ -14279,7 +14327,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>45761</v>
       </c>
@@ -14314,7 +14362,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>45761</v>
       </c>
@@ -14346,7 +14394,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>45762</v>
       </c>
@@ -14378,7 +14426,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>45762</v>
       </c>
@@ -14410,7 +14458,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>45761</v>
       </c>
@@ -14445,7 +14493,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>45762</v>
       </c>
@@ -14474,7 +14522,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>45762</v>
       </c>
@@ -14506,7 +14554,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>45762</v>
       </c>
@@ -14538,7 +14586,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>45762</v>
       </c>
@@ -14570,7 +14618,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>1007</v>
       </c>
@@ -14602,7 +14650,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>1007</v>
       </c>
@@ -14637,7 +14685,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>1007</v>
       </c>
@@ -14672,7 +14720,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>1007</v>
       </c>
@@ -14704,7 +14752,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>1007</v>
       </c>
@@ -14736,7 +14784,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>45762</v>
       </c>
@@ -14771,7 +14819,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>45762</v>
       </c>
@@ -14806,7 +14854,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>45762</v>
       </c>
@@ -14841,7 +14889,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>45762</v>
       </c>
@@ -14873,7 +14921,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>45762</v>
       </c>
@@ -14905,7 +14953,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>45762</v>
       </c>
@@ -14937,7 +14985,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>45762</v>
       </c>
@@ -14969,7 +15017,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>45762</v>
       </c>
@@ -15004,7 +15052,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>45762</v>
       </c>
@@ -15039,7 +15087,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>45762</v>
       </c>
@@ -15071,7 +15119,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>45763</v>
       </c>
@@ -15103,7 +15151,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>45764</v>
       </c>
@@ -15132,7 +15180,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>45764</v>
       </c>
@@ -15170,4 +15218,6282 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B5CEBA7-4988-445F-8C0C-6B7805C98E47}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>44123</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>922</v>
+      </c>
+      <c r="H2" t="s">
+        <v>916</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="2">
+        <v>44146</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>44123</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>923</v>
+      </c>
+      <c r="H3" t="s">
+        <v>926</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>162</v>
+      </c>
+      <c r="L3" s="2">
+        <v>44146</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>44120</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>914</v>
+      </c>
+      <c r="H4" t="s">
+        <v>924</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="2">
+        <v>44187</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>44120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>925</v>
+      </c>
+      <c r="H5" t="s">
+        <v>926</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="2">
+        <v>44187</v>
+      </c>
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>44166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H6" t="s">
+        <v>915</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="2">
+        <v>44186</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>44167</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>927</v>
+      </c>
+      <c r="H7" t="s">
+        <v>928</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="2">
+        <v>44187</v>
+      </c>
+      <c r="M7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>44167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>914</v>
+      </c>
+      <c r="H8" t="s">
+        <v>924</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="2">
+        <v>44187</v>
+      </c>
+      <c r="M8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>44167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>917</v>
+      </c>
+      <c r="H9" t="s">
+        <v>918</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>339</v>
+      </c>
+      <c r="L9" s="2">
+        <v>44186</v>
+      </c>
+      <c r="M9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91876A21-A10C-4342-9CE0-5F7A054FF9C9}">
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>929</v>
+      </c>
+      <c r="H2" t="s">
+        <v>924</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>920</v>
+      </c>
+      <c r="H3" t="s">
+        <v>921</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" t="s">
+        <v>931</v>
+      </c>
+      <c r="H5" t="s">
+        <v>926</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H6" t="s">
+        <v>918</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" t="s">
+        <v>933</v>
+      </c>
+      <c r="H7" t="s">
+        <v>924</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" t="s">
+        <v>915</v>
+      </c>
+      <c r="H8" t="s">
+        <v>934</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" t="s">
+        <v>915</v>
+      </c>
+      <c r="H9" t="s">
+        <v>934</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" t="s">
+        <v>935</v>
+      </c>
+      <c r="H10" t="s">
+        <v>980</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" t="s">
+        <v>936</v>
+      </c>
+      <c r="H12" t="s">
+        <v>980</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>113</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" t="s">
+        <v>937</v>
+      </c>
+      <c r="H13" t="s">
+        <v>938</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" t="s">
+        <v>915</v>
+      </c>
+      <c r="H14" t="s">
+        <v>980</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" t="s">
+        <v>939</v>
+      </c>
+      <c r="H15" t="s">
+        <v>940</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>127</v>
+      </c>
+      <c r="L15" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" t="s">
+        <v>918</v>
+      </c>
+      <c r="H16" t="s">
+        <v>918</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" t="s">
+        <v>133</v>
+      </c>
+      <c r="L16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" t="s">
+        <v>915</v>
+      </c>
+      <c r="H17" t="s">
+        <v>915</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" t="s">
+        <v>84</v>
+      </c>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" t="s">
+        <v>919</v>
+      </c>
+      <c r="H18" t="s">
+        <v>919</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" t="s">
+        <v>920</v>
+      </c>
+      <c r="H19" t="s">
+        <v>921</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" t="s">
+        <v>133</v>
+      </c>
+      <c r="L19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" t="s">
+        <v>941</v>
+      </c>
+      <c r="H20" t="s">
+        <v>924</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" t="s">
+        <v>942</v>
+      </c>
+      <c r="G21" t="s">
+        <v>923</v>
+      </c>
+      <c r="H21" t="s">
+        <v>926</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" t="s">
+        <v>925</v>
+      </c>
+      <c r="H22" t="s">
+        <v>926</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+      <c r="F23" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" t="s">
+        <v>943</v>
+      </c>
+      <c r="H23" t="s">
+        <v>944</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" t="s">
+        <v>930</v>
+      </c>
+      <c r="H24" t="s">
+        <v>924</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" t="s">
+        <v>945</v>
+      </c>
+      <c r="G25" t="s">
+        <v>946</v>
+      </c>
+      <c r="H25" t="s">
+        <v>947</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" t="s">
+        <v>948</v>
+      </c>
+      <c r="H26" t="s">
+        <v>926</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" t="s">
+        <v>185</v>
+      </c>
+      <c r="G27" t="s">
+        <v>949</v>
+      </c>
+      <c r="H27" t="s">
+        <v>916</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" t="s">
+        <v>191</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I28" t="s">
+        <v>70</v>
+      </c>
+      <c r="L28" s="2">
+        <v>44503</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29" t="s">
+        <v>194</v>
+      </c>
+      <c r="F29" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I29" t="s">
+        <v>70</v>
+      </c>
+      <c r="L29" s="2">
+        <v>44504</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" t="s">
+        <v>199</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" t="s">
+        <v>203</v>
+      </c>
+      <c r="F31" t="s">
+        <v>950</v>
+      </c>
+      <c r="G31" t="s">
+        <v>923</v>
+      </c>
+      <c r="H31" t="s">
+        <v>926</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" t="s">
+        <v>206</v>
+      </c>
+      <c r="C32" t="s">
+        <v>207</v>
+      </c>
+      <c r="D32" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" t="s">
+        <v>209</v>
+      </c>
+      <c r="G32" t="s">
+        <v>951</v>
+      </c>
+      <c r="H32" t="s">
+        <v>919</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D33" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G33" t="s">
+        <v>920</v>
+      </c>
+      <c r="H33" t="s">
+        <v>924</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G34" t="s">
+        <v>925</v>
+      </c>
+      <c r="H34" t="s">
+        <v>926</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D35" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" t="s">
+        <v>952</v>
+      </c>
+      <c r="G35" t="s">
+        <v>920</v>
+      </c>
+      <c r="H35" t="s">
+        <v>921</v>
+      </c>
+      <c r="I35" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" t="s">
+        <v>225</v>
+      </c>
+      <c r="F36" t="s">
+        <v>226</v>
+      </c>
+      <c r="G36" t="s">
+        <v>981</v>
+      </c>
+      <c r="H36" t="s">
+        <v>918</v>
+      </c>
+      <c r="I36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" t="s">
+        <v>229</v>
+      </c>
+      <c r="D37" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G37" t="s">
+        <v>920</v>
+      </c>
+      <c r="H37" t="s">
+        <v>921</v>
+      </c>
+      <c r="I37" t="s">
+        <v>51</v>
+      </c>
+      <c r="J37" t="s">
+        <v>232</v>
+      </c>
+      <c r="K37" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" t="s">
+        <v>237</v>
+      </c>
+      <c r="G38" t="s">
+        <v>919</v>
+      </c>
+      <c r="H38" t="s">
+        <v>919</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" t="s">
+        <v>240</v>
+      </c>
+      <c r="F39" t="s">
+        <v>241</v>
+      </c>
+      <c r="G39" t="s">
+        <v>925</v>
+      </c>
+      <c r="H39" t="s">
+        <v>926</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>242</v>
+      </c>
+      <c r="K39" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>44524</v>
+      </c>
+      <c r="B40" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" t="s">
+        <v>245</v>
+      </c>
+      <c r="F40" t="s">
+        <v>246</v>
+      </c>
+      <c r="G40" t="s">
+        <v>953</v>
+      </c>
+      <c r="H40" t="s">
+        <v>954</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s">
+        <v>247</v>
+      </c>
+      <c r="K40" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>44526</v>
+      </c>
+      <c r="B41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" t="s">
+        <v>249</v>
+      </c>
+      <c r="D41" t="s">
+        <v>250</v>
+      </c>
+      <c r="F41" t="s">
+        <v>251</v>
+      </c>
+      <c r="G41" t="s">
+        <v>955</v>
+      </c>
+      <c r="H41" t="s">
+        <v>944</v>
+      </c>
+      <c r="I41" t="s">
+        <v>51</v>
+      </c>
+      <c r="K41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>44526</v>
+      </c>
+      <c r="B42" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" t="s">
+        <v>253</v>
+      </c>
+      <c r="D42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" t="s">
+        <v>255</v>
+      </c>
+      <c r="G42" t="s">
+        <v>956</v>
+      </c>
+      <c r="H42" t="s">
+        <v>947</v>
+      </c>
+      <c r="I42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" t="s">
+        <v>256</v>
+      </c>
+      <c r="K42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>44526</v>
+      </c>
+      <c r="B43" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D43" t="s">
+        <v>260</v>
+      </c>
+      <c r="F43" t="s">
+        <v>261</v>
+      </c>
+      <c r="G43" t="s">
+        <v>957</v>
+      </c>
+      <c r="H43" t="s">
+        <v>980</v>
+      </c>
+      <c r="I43" t="s">
+        <v>51</v>
+      </c>
+      <c r="J43" t="s">
+        <v>262</v>
+      </c>
+      <c r="K43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>44612</v>
+      </c>
+      <c r="B44" t="s">
+        <v>263</v>
+      </c>
+      <c r="C44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
+        <v>265</v>
+      </c>
+      <c r="F44" t="s">
+        <v>266</v>
+      </c>
+      <c r="G44" t="s">
+        <v>957</v>
+      </c>
+      <c r="H44" t="s">
+        <v>915</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" t="s">
+        <v>267</v>
+      </c>
+      <c r="K44" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B45" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" t="s">
+        <v>271</v>
+      </c>
+      <c r="F45" t="s">
+        <v>272</v>
+      </c>
+      <c r="G45" t="s">
+        <v>958</v>
+      </c>
+      <c r="H45" t="s">
+        <v>921</v>
+      </c>
+      <c r="I45" t="s">
+        <v>51</v>
+      </c>
+      <c r="J45" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>273</v>
+      </c>
+      <c r="D46" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" t="s">
+        <v>275</v>
+      </c>
+      <c r="G46" t="s">
+        <v>959</v>
+      </c>
+      <c r="H46" t="s">
+        <v>921</v>
+      </c>
+      <c r="I46" t="s">
+        <v>51</v>
+      </c>
+      <c r="J46" t="s">
+        <v>262</v>
+      </c>
+      <c r="K46" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C47" t="s">
+        <v>277</v>
+      </c>
+      <c r="D47" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" t="s">
+        <v>279</v>
+      </c>
+      <c r="G47" t="s">
+        <v>960</v>
+      </c>
+      <c r="H47" t="s">
+        <v>921</v>
+      </c>
+      <c r="I47" t="s">
+        <v>51</v>
+      </c>
+      <c r="J47" t="s">
+        <v>262</v>
+      </c>
+      <c r="K47" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B48" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" t="s">
+        <v>282</v>
+      </c>
+      <c r="D48" t="s">
+        <v>283</v>
+      </c>
+      <c r="F48" t="s">
+        <v>284</v>
+      </c>
+      <c r="G48" t="s">
+        <v>914</v>
+      </c>
+      <c r="H48" t="s">
+        <v>916</v>
+      </c>
+      <c r="I48" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" t="s">
+        <v>285</v>
+      </c>
+      <c r="K48" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B49" t="s">
+        <v>287</v>
+      </c>
+      <c r="C49" t="s">
+        <v>288</v>
+      </c>
+      <c r="D49" t="s">
+        <v>289</v>
+      </c>
+      <c r="F49" t="s">
+        <v>961</v>
+      </c>
+      <c r="G49" t="s">
+        <v>951</v>
+      </c>
+      <c r="H49" t="s">
+        <v>915</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B50" t="s">
+        <v>290</v>
+      </c>
+      <c r="C50" t="s">
+        <v>291</v>
+      </c>
+      <c r="D50" t="s">
+        <v>292</v>
+      </c>
+      <c r="F50" t="s">
+        <v>293</v>
+      </c>
+      <c r="G50" t="s">
+        <v>962</v>
+      </c>
+      <c r="H50" t="s">
+        <v>926</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>98</v>
+      </c>
+      <c r="K50" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>44255</v>
+      </c>
+      <c r="B51" t="s">
+        <v>294</v>
+      </c>
+      <c r="C51" t="s">
+        <v>295</v>
+      </c>
+      <c r="D51" t="s">
+        <v>296</v>
+      </c>
+      <c r="F51" t="s">
+        <v>297</v>
+      </c>
+      <c r="G51" t="s">
+        <v>918</v>
+      </c>
+      <c r="H51" t="s">
+        <v>918</v>
+      </c>
+      <c r="I51" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" t="s">
+        <v>339</v>
+      </c>
+      <c r="K51" t="s">
+        <v>268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856F361A-2AB7-4DC6-A260-9422ED6D89EA}">
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G2" t="s">
+        <v>963</v>
+      </c>
+      <c r="H2" t="s">
+        <v>944</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G3" t="s">
+        <v>964</v>
+      </c>
+      <c r="H3" t="s">
+        <v>980</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" t="s">
+        <v>965</v>
+      </c>
+      <c r="H4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F5" t="s">
+        <v>315</v>
+      </c>
+      <c r="G5" t="s">
+        <v>966</v>
+      </c>
+      <c r="H5" t="s">
+        <v>980</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>316</v>
+      </c>
+      <c r="K5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" t="s">
+        <v>967</v>
+      </c>
+      <c r="H7" t="s">
+        <v>980</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>262</v>
+      </c>
+      <c r="K7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" t="s">
+        <v>328</v>
+      </c>
+      <c r="F8" t="s">
+        <v>329</v>
+      </c>
+      <c r="G8" t="s">
+        <v>968</v>
+      </c>
+      <c r="H8" t="s">
+        <v>934</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>44623</v>
+      </c>
+      <c r="B9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D9" t="s">
+        <v>333</v>
+      </c>
+      <c r="F9" t="s">
+        <v>334</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>44833</v>
+      </c>
+      <c r="B10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C10" t="s">
+        <v>337</v>
+      </c>
+      <c r="D10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10">
+        <v>767469615</v>
+      </c>
+      <c r="F10" t="s">
+        <v>969</v>
+      </c>
+      <c r="G10" t="s">
+        <v>970</v>
+      </c>
+      <c r="H10" t="s">
+        <v>918</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>44833</v>
+      </c>
+      <c r="B11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" t="s">
+        <v>971</v>
+      </c>
+      <c r="H11" t="s">
+        <v>915</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>344</v>
+      </c>
+      <c r="K11" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" t="s">
+        <v>346</v>
+      </c>
+      <c r="E12">
+        <v>102989154</v>
+      </c>
+      <c r="F12" t="s">
+        <v>347</v>
+      </c>
+      <c r="G12" t="s">
+        <v>972</v>
+      </c>
+      <c r="H12" t="s">
+        <v>940</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>348</v>
+      </c>
+      <c r="K12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C13" t="s">
+        <v>351</v>
+      </c>
+      <c r="D13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F13" t="s">
+        <v>353</v>
+      </c>
+      <c r="G13" t="s">
+        <v>973</v>
+      </c>
+      <c r="H13" t="s">
+        <v>926</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D14" t="s">
+        <v>357</v>
+      </c>
+      <c r="E14">
+        <v>787347707</v>
+      </c>
+      <c r="F14" t="s">
+        <v>358</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C15" t="s">
+        <v>361</v>
+      </c>
+      <c r="D15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15">
+        <v>141583425</v>
+      </c>
+      <c r="F15" t="s">
+        <v>363</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E16">
+        <v>758422493</v>
+      </c>
+      <c r="F16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A1EF91-BFEF-488A-857A-F98A43A8988B}">
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>44944</v>
+      </c>
+      <c r="B2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G2" t="s">
+        <v>974</v>
+      </c>
+      <c r="H2" t="s">
+        <v>974</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>44945</v>
+      </c>
+      <c r="B3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>44945</v>
+      </c>
+      <c r="B4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" t="s">
+        <v>914</v>
+      </c>
+      <c r="H4" t="s">
+        <v>924</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>44946</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G5" t="s">
+        <v>925</v>
+      </c>
+      <c r="H5" t="s">
+        <v>926</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>44844</v>
+      </c>
+      <c r="B6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F6" t="s">
+        <v>388</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>44952</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F7" t="s">
+        <v>391</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>44620</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" t="s">
+        <v>395</v>
+      </c>
+      <c r="G8" t="s">
+        <v>975</v>
+      </c>
+      <c r="H8" t="s">
+        <v>916</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>44957</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>397</v>
+      </c>
+      <c r="D9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E9">
+        <v>767469615</v>
+      </c>
+      <c r="F9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G9" t="s">
+        <v>940</v>
+      </c>
+      <c r="H9" t="s">
+        <v>916</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>400</v>
+      </c>
+      <c r="K9" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>45013</v>
+      </c>
+      <c r="B10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F10" t="s">
+        <v>404</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>45013</v>
+      </c>
+      <c r="B11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" t="s">
+        <v>408</v>
+      </c>
+      <c r="F11" t="s">
+        <v>409</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B12" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" t="s">
+        <v>411</v>
+      </c>
+      <c r="D12" t="s">
+        <v>412</v>
+      </c>
+      <c r="F12" t="s">
+        <v>413</v>
+      </c>
+      <c r="G12" t="s">
+        <v>976</v>
+      </c>
+      <c r="H12" t="s">
+        <v>944</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>414</v>
+      </c>
+      <c r="K12" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>45103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" t="s">
+        <v>417</v>
+      </c>
+      <c r="D13" t="s">
+        <v>418</v>
+      </c>
+      <c r="F13" t="s">
+        <v>419</v>
+      </c>
+      <c r="G13" t="s">
+        <v>976</v>
+      </c>
+      <c r="H13" t="s">
+        <v>944</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" t="s">
+        <v>420</v>
+      </c>
+      <c r="K13" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>422</v>
+      </c>
+      <c r="D14" t="s">
+        <v>423</v>
+      </c>
+      <c r="F14" t="s">
+        <v>424</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F15" t="s">
+        <v>429</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" t="s">
+        <v>431</v>
+      </c>
+      <c r="D16" t="s">
+        <v>432</v>
+      </c>
+      <c r="F16" t="s">
+        <v>433</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B17" t="s">
+        <v>434</v>
+      </c>
+      <c r="C17" t="s">
+        <v>435</v>
+      </c>
+      <c r="D17" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" t="s">
+        <v>437</v>
+      </c>
+      <c r="G17" t="s">
+        <v>927</v>
+      </c>
+      <c r="H17" t="s">
+        <v>928</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>439</v>
+      </c>
+      <c r="D18" t="s">
+        <v>440</v>
+      </c>
+      <c r="F18" t="s">
+        <v>441</v>
+      </c>
+      <c r="G18" t="s">
+        <v>977</v>
+      </c>
+      <c r="H18" t="s">
+        <v>926</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>442</v>
+      </c>
+      <c r="K18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>45107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>443</v>
+      </c>
+      <c r="C19" t="s">
+        <v>444</v>
+      </c>
+      <c r="D19" t="s">
+        <v>445</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C20" t="s">
+        <v>447</v>
+      </c>
+      <c r="D20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F20" t="s">
+        <v>449</v>
+      </c>
+      <c r="G20" t="s">
+        <v>978</v>
+      </c>
+      <c r="H20" t="s">
+        <v>926</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s">
+        <v>450</v>
+      </c>
+      <c r="K20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" t="s">
+        <v>451</v>
+      </c>
+      <c r="D21" t="s">
+        <v>452</v>
+      </c>
+      <c r="F21" t="s">
+        <v>453</v>
+      </c>
+      <c r="G21" t="s">
+        <v>915</v>
+      </c>
+      <c r="H21" t="s">
+        <v>915</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s">
+        <v>454</v>
+      </c>
+      <c r="K21" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B22" t="s">
+        <v>456</v>
+      </c>
+      <c r="C22" t="s">
+        <v>457</v>
+      </c>
+      <c r="D22" t="s">
+        <v>458</v>
+      </c>
+      <c r="F22" t="s">
+        <v>459</v>
+      </c>
+      <c r="G22" t="s">
+        <v>944</v>
+      </c>
+      <c r="H22" t="s">
+        <v>979</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>420</v>
+      </c>
+      <c r="K22" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>461</v>
+      </c>
+      <c r="C23" t="s">
+        <v>462</v>
+      </c>
+      <c r="D23" t="s">
+        <v>463</v>
+      </c>
+      <c r="F23" t="s">
+        <v>464</v>
+      </c>
+      <c r="G23" t="s">
+        <v>977</v>
+      </c>
+      <c r="H23" t="s">
+        <v>926</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s">
+        <v>442</v>
+      </c>
+      <c r="K23" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B24" t="s">
+        <v>465</v>
+      </c>
+      <c r="C24" t="s">
+        <v>466</v>
+      </c>
+      <c r="D24" t="s">
+        <v>467</v>
+      </c>
+      <c r="F24" t="s">
+        <v>468</v>
+      </c>
+      <c r="G24" t="s">
+        <v>925</v>
+      </c>
+      <c r="H24" t="s">
+        <v>926</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s">
+        <v>442</v>
+      </c>
+      <c r="K24" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B25" t="s">
+        <v>469</v>
+      </c>
+      <c r="C25" t="s">
+        <v>470</v>
+      </c>
+      <c r="D25" t="s">
+        <v>471</v>
+      </c>
+      <c r="F25" t="s">
+        <v>472</v>
+      </c>
+      <c r="G25" t="s">
+        <v>925</v>
+      </c>
+      <c r="H25" t="s">
+        <v>926</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s">
+        <v>473</v>
+      </c>
+      <c r="K25" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B26" t="s">
+        <v>474</v>
+      </c>
+      <c r="C26" t="s">
+        <v>475</v>
+      </c>
+      <c r="D26" t="s">
+        <v>476</v>
+      </c>
+      <c r="F26" t="s">
+        <v>477</v>
+      </c>
+      <c r="G26" t="s">
+        <v>936</v>
+      </c>
+      <c r="H26" t="s">
+        <v>980</v>
+      </c>
+      <c r="I26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>45110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>478</v>
+      </c>
+      <c r="C27" t="s">
+        <v>479</v>
+      </c>
+      <c r="D27" t="s">
+        <v>480</v>
+      </c>
+      <c r="F27" t="s">
+        <v>481</v>
+      </c>
+      <c r="G27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>45111</v>
+      </c>
+      <c r="B28" t="s">
+        <v>482</v>
+      </c>
+      <c r="C28" t="s">
+        <v>483</v>
+      </c>
+      <c r="D28" t="s">
+        <v>484</v>
+      </c>
+      <c r="F28" t="s">
+        <v>485</v>
+      </c>
+      <c r="G28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s">
+        <v>442</v>
+      </c>
+      <c r="K28" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>45112</v>
+      </c>
+      <c r="B29" t="s">
+        <v>487</v>
+      </c>
+      <c r="C29" t="s">
+        <v>488</v>
+      </c>
+      <c r="D29" t="s">
+        <v>489</v>
+      </c>
+      <c r="F29" t="s">
+        <v>490</v>
+      </c>
+      <c r="G29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s">
+        <v>491</v>
+      </c>
+      <c r="K29" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>45113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>492</v>
+      </c>
+      <c r="C30" t="s">
+        <v>493</v>
+      </c>
+      <c r="D30" t="s">
+        <v>494</v>
+      </c>
+      <c r="F30" t="s">
+        <v>495</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>45116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>497</v>
+      </c>
+      <c r="C31" t="s">
+        <v>498</v>
+      </c>
+      <c r="D31" t="s">
+        <v>499</v>
+      </c>
+      <c r="F31" t="s">
+        <v>500</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I31" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>45240</v>
+      </c>
+      <c r="B32" t="s">
+        <v>331</v>
+      </c>
+      <c r="C32" t="s">
+        <v>502</v>
+      </c>
+      <c r="D32" t="s">
+        <v>503</v>
+      </c>
+      <c r="F32" t="s">
+        <v>504</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I32" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>45240</v>
+      </c>
+      <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>505</v>
+      </c>
+      <c r="D33" t="s">
+        <v>506</v>
+      </c>
+      <c r="F33" t="s">
+        <v>507</v>
+      </c>
+      <c r="G33" t="s">
+        <v>981</v>
+      </c>
+      <c r="H33" t="s">
+        <v>918</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" t="s">
+        <v>508</v>
+      </c>
+      <c r="K33" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>45240</v>
+      </c>
+      <c r="B34" t="s">
+        <v>510</v>
+      </c>
+      <c r="C34" t="s">
+        <v>511</v>
+      </c>
+      <c r="D34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F34" t="s">
+        <v>513</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" t="s">
+        <v>392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C83FDEBF-48AC-4774-BDEE-DCB4F39CAC34}">
+  <dimension ref="A1:M53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>45296</v>
+      </c>
+      <c r="B2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F2" t="s">
+        <v>517</v>
+      </c>
+      <c r="G2" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2" t="s">
+        <v>916</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>518</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F3" t="s">
+        <v>522</v>
+      </c>
+      <c r="G3" t="s">
+        <v>983</v>
+      </c>
+      <c r="H3" t="s">
+        <v>980</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>523</v>
+      </c>
+      <c r="K3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D4" t="s">
+        <v>527</v>
+      </c>
+      <c r="F4" t="s">
+        <v>528</v>
+      </c>
+      <c r="G4" t="s">
+        <v>984</v>
+      </c>
+      <c r="H4" t="s">
+        <v>916</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>529</v>
+      </c>
+      <c r="K4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B5" t="s">
+        <v>531</v>
+      </c>
+      <c r="C5" t="s">
+        <v>532</v>
+      </c>
+      <c r="D5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F5" t="s">
+        <v>534</v>
+      </c>
+      <c r="G5" t="s">
+        <v>920</v>
+      </c>
+      <c r="H5" t="s">
+        <v>921</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D6" t="s">
+        <v>537</v>
+      </c>
+      <c r="F6" t="s">
+        <v>538</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C7" t="s">
+        <v>540</v>
+      </c>
+      <c r="D7" t="s">
+        <v>541</v>
+      </c>
+      <c r="F7" t="s">
+        <v>542</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B8" t="s">
+        <v>544</v>
+      </c>
+      <c r="C8" t="s">
+        <v>545</v>
+      </c>
+      <c r="D8" t="s">
+        <v>546</v>
+      </c>
+      <c r="F8" t="s">
+        <v>547</v>
+      </c>
+      <c r="G8" t="s">
+        <v>985</v>
+      </c>
+      <c r="H8" t="s">
+        <v>980</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B9" t="s">
+        <v>548</v>
+      </c>
+      <c r="C9" t="s">
+        <v>549</v>
+      </c>
+      <c r="D9" t="s">
+        <v>550</v>
+      </c>
+      <c r="F9" t="s">
+        <v>551</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B10" t="s">
+        <v>552</v>
+      </c>
+      <c r="C10" t="s">
+        <v>553</v>
+      </c>
+      <c r="D10" t="s">
+        <v>554</v>
+      </c>
+      <c r="F10" t="s">
+        <v>986</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" t="s">
+        <v>555</v>
+      </c>
+      <c r="D11" t="s">
+        <v>556</v>
+      </c>
+      <c r="F11" t="s">
+        <v>987</v>
+      </c>
+      <c r="G11" t="s">
+        <v>988</v>
+      </c>
+      <c r="H11" t="s">
+        <v>980</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" t="s">
+        <v>557</v>
+      </c>
+      <c r="K11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B12" t="s">
+        <v>559</v>
+      </c>
+      <c r="C12" t="s">
+        <v>560</v>
+      </c>
+      <c r="D12" t="s">
+        <v>561</v>
+      </c>
+      <c r="F12" t="s">
+        <v>562</v>
+      </c>
+      <c r="G12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H12" t="s">
+        <v>944</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B13" t="s">
+        <v>446</v>
+      </c>
+      <c r="C13" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" t="s">
+        <v>448</v>
+      </c>
+      <c r="F13" t="s">
+        <v>449</v>
+      </c>
+      <c r="G13" t="s">
+        <v>978</v>
+      </c>
+      <c r="H13" t="s">
+        <v>926</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" t="s">
+        <v>450</v>
+      </c>
+      <c r="K13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B14" t="s">
+        <v>563</v>
+      </c>
+      <c r="C14" t="s">
+        <v>564</v>
+      </c>
+      <c r="D14" t="s">
+        <v>565</v>
+      </c>
+      <c r="F14" t="s">
+        <v>989</v>
+      </c>
+      <c r="G14" t="s">
+        <v>990</v>
+      </c>
+      <c r="H14" t="s">
+        <v>915</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>566</v>
+      </c>
+      <c r="D15" t="s">
+        <v>567</v>
+      </c>
+      <c r="F15" t="s">
+        <v>568</v>
+      </c>
+      <c r="G15" t="s">
+        <v>925</v>
+      </c>
+      <c r="H15" t="s">
+        <v>926</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>45387</v>
+      </c>
+      <c r="B16" t="s">
+        <v>570</v>
+      </c>
+      <c r="C16" t="s">
+        <v>571</v>
+      </c>
+      <c r="D16" t="s">
+        <v>572</v>
+      </c>
+      <c r="F16" t="s">
+        <v>573</v>
+      </c>
+      <c r="G16" t="s">
+        <v>923</v>
+      </c>
+      <c r="H16" t="s">
+        <v>926</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K16" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>45394</v>
+      </c>
+      <c r="B17" t="s">
+        <v>575</v>
+      </c>
+      <c r="C17" t="s">
+        <v>576</v>
+      </c>
+      <c r="D17" t="s">
+        <v>577</v>
+      </c>
+      <c r="F17" t="s">
+        <v>578</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>45469</v>
+      </c>
+      <c r="B18" t="s">
+        <v>580</v>
+      </c>
+      <c r="C18" t="s">
+        <v>581</v>
+      </c>
+      <c r="D18" t="s">
+        <v>582</v>
+      </c>
+      <c r="F18" t="s">
+        <v>583</v>
+      </c>
+      <c r="G18" t="s">
+        <v>915</v>
+      </c>
+      <c r="H18" t="s">
+        <v>980</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>45481</v>
+      </c>
+      <c r="B19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C19" t="s">
+        <v>585</v>
+      </c>
+      <c r="D19" t="s">
+        <v>586</v>
+      </c>
+      <c r="F19" t="s">
+        <v>587</v>
+      </c>
+      <c r="G19" t="s">
+        <v>991</v>
+      </c>
+      <c r="H19" t="s">
+        <v>938</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>45483</v>
+      </c>
+      <c r="B20" t="s">
+        <v>589</v>
+      </c>
+      <c r="C20" t="s">
+        <v>590</v>
+      </c>
+      <c r="D20" t="s">
+        <v>591</v>
+      </c>
+      <c r="E20" t="s">
+        <v>592</v>
+      </c>
+      <c r="F20" t="s">
+        <v>593</v>
+      </c>
+      <c r="G20" t="s">
+        <v>946</v>
+      </c>
+      <c r="H20" t="s">
+        <v>947</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" t="s">
+        <v>262</v>
+      </c>
+      <c r="K20" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B21" t="s">
+        <v>563</v>
+      </c>
+      <c r="C21" t="s">
+        <v>595</v>
+      </c>
+      <c r="D21" t="s">
+        <v>596</v>
+      </c>
+      <c r="F21" t="s">
+        <v>597</v>
+      </c>
+      <c r="G21" t="s">
+        <v>992</v>
+      </c>
+      <c r="H21" t="s">
+        <v>980</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
+        <v>256</v>
+      </c>
+      <c r="K21" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>598</v>
+      </c>
+      <c r="D22" t="s">
+        <v>599</v>
+      </c>
+      <c r="E22" t="s">
+        <v>600</v>
+      </c>
+      <c r="F22" t="s">
+        <v>601</v>
+      </c>
+      <c r="G22" t="s">
+        <v>946</v>
+      </c>
+      <c r="H22" t="s">
+        <v>926</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>602</v>
+      </c>
+      <c r="K22" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B23" t="s">
+        <v>604</v>
+      </c>
+      <c r="C23" t="s">
+        <v>605</v>
+      </c>
+      <c r="D23" t="s">
+        <v>606</v>
+      </c>
+      <c r="E23" t="s">
+        <v>607</v>
+      </c>
+      <c r="F23" t="s">
+        <v>608</v>
+      </c>
+      <c r="G23" t="s">
+        <v>920</v>
+      </c>
+      <c r="H23" t="s">
+        <v>921</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B24" t="s">
+        <v>609</v>
+      </c>
+      <c r="C24" t="s">
+        <v>610</v>
+      </c>
+      <c r="D24" t="s">
+        <v>611</v>
+      </c>
+      <c r="E24" t="s">
+        <v>612</v>
+      </c>
+      <c r="F24" t="s">
+        <v>613</v>
+      </c>
+      <c r="G24" t="s">
+        <v>993</v>
+      </c>
+      <c r="H24" t="s">
+        <v>980</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="K24" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B25" t="s">
+        <v>614</v>
+      </c>
+      <c r="C25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D25" t="s">
+        <v>616</v>
+      </c>
+      <c r="E25" t="s">
+        <v>617</v>
+      </c>
+      <c r="F25" t="s">
+        <v>618</v>
+      </c>
+      <c r="G25" t="s">
+        <v>944</v>
+      </c>
+      <c r="H25" t="s">
+        <v>944</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" t="s">
+        <v>619</v>
+      </c>
+      <c r="K25" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B26" t="s">
+        <v>620</v>
+      </c>
+      <c r="C26" t="s">
+        <v>621</v>
+      </c>
+      <c r="D26" t="s">
+        <v>622</v>
+      </c>
+      <c r="E26" t="s">
+        <v>623</v>
+      </c>
+      <c r="F26" t="s">
+        <v>624</v>
+      </c>
+      <c r="G26" t="s">
+        <v>994</v>
+      </c>
+      <c r="H26" t="s">
+        <v>916</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B27" t="s">
+        <v>625</v>
+      </c>
+      <c r="C27" t="s">
+        <v>626</v>
+      </c>
+      <c r="D27" t="s">
+        <v>627</v>
+      </c>
+      <c r="E27" t="s">
+        <v>628</v>
+      </c>
+      <c r="F27" t="s">
+        <v>629</v>
+      </c>
+      <c r="G27" t="s">
+        <v>995</v>
+      </c>
+      <c r="H27" t="s">
+        <v>934</v>
+      </c>
+      <c r="I27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" t="s">
+        <v>630</v>
+      </c>
+      <c r="K27" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B28" t="s">
+        <v>631</v>
+      </c>
+      <c r="C28" t="s">
+        <v>632</v>
+      </c>
+      <c r="D28" t="s">
+        <v>633</v>
+      </c>
+      <c r="E28" t="s">
+        <v>634</v>
+      </c>
+      <c r="F28" t="s">
+        <v>635</v>
+      </c>
+      <c r="G28" t="s">
+        <v>996</v>
+      </c>
+      <c r="H28" t="s">
+        <v>918</v>
+      </c>
+      <c r="I28" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B29" t="s">
+        <v>636</v>
+      </c>
+      <c r="C29" t="s">
+        <v>637</v>
+      </c>
+      <c r="D29" t="s">
+        <v>638</v>
+      </c>
+      <c r="E29" t="s">
+        <v>639</v>
+      </c>
+      <c r="F29" t="s">
+        <v>640</v>
+      </c>
+      <c r="G29" t="s">
+        <v>920</v>
+      </c>
+      <c r="H29" t="s">
+        <v>921</v>
+      </c>
+      <c r="I29" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" t="s">
+        <v>98</v>
+      </c>
+      <c r="K29" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B30" t="s">
+        <v>641</v>
+      </c>
+      <c r="C30" t="s">
+        <v>642</v>
+      </c>
+      <c r="D30" t="s">
+        <v>643</v>
+      </c>
+      <c r="E30" t="s">
+        <v>644</v>
+      </c>
+      <c r="F30" t="s">
+        <v>645</v>
+      </c>
+      <c r="G30" t="s">
+        <v>915</v>
+      </c>
+      <c r="H30" t="s">
+        <v>980</v>
+      </c>
+      <c r="I30" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" t="s">
+        <v>420</v>
+      </c>
+      <c r="K30" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B31" t="s">
+        <v>646</v>
+      </c>
+      <c r="C31" t="s">
+        <v>647</v>
+      </c>
+      <c r="D31" t="s">
+        <v>648</v>
+      </c>
+      <c r="E31" t="s">
+        <v>649</v>
+      </c>
+      <c r="F31" t="s">
+        <v>650</v>
+      </c>
+      <c r="G31" t="s">
+        <v>976</v>
+      </c>
+      <c r="H31" t="s">
+        <v>944</v>
+      </c>
+      <c r="I31" t="s">
+        <v>51</v>
+      </c>
+      <c r="J31" t="s">
+        <v>651</v>
+      </c>
+      <c r="K31" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B32" t="s">
+        <v>654</v>
+      </c>
+      <c r="C32" t="s">
+        <v>655</v>
+      </c>
+      <c r="D32" t="s">
+        <v>656</v>
+      </c>
+      <c r="E32" t="s">
+        <v>657</v>
+      </c>
+      <c r="F32" t="s">
+        <v>658</v>
+      </c>
+      <c r="G32" t="s">
+        <v>997</v>
+      </c>
+      <c r="H32" t="s">
+        <v>944</v>
+      </c>
+      <c r="I32" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" t="s">
+        <v>651</v>
+      </c>
+      <c r="K32" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33" t="s">
+        <v>660</v>
+      </c>
+      <c r="D33" t="s">
+        <v>661</v>
+      </c>
+      <c r="E33" t="s">
+        <v>662</v>
+      </c>
+      <c r="F33" t="s">
+        <v>663</v>
+      </c>
+      <c r="G33" t="s">
+        <v>946</v>
+      </c>
+      <c r="H33" t="s">
+        <v>947</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="K33" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B34" t="s">
+        <v>664</v>
+      </c>
+      <c r="C34" t="s">
+        <v>665</v>
+      </c>
+      <c r="D34" t="s">
+        <v>666</v>
+      </c>
+      <c r="E34" t="s">
+        <v>667</v>
+      </c>
+      <c r="F34" t="s">
+        <v>668</v>
+      </c>
+      <c r="G34" t="s">
+        <v>998</v>
+      </c>
+      <c r="H34" t="s">
+        <v>944</v>
+      </c>
+      <c r="I34" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="B35" t="s">
+        <v>670</v>
+      </c>
+      <c r="C35" t="s">
+        <v>671</v>
+      </c>
+      <c r="D35" t="s">
+        <v>672</v>
+      </c>
+      <c r="E35" t="s">
+        <v>673</v>
+      </c>
+      <c r="F35" t="s">
+        <v>674</v>
+      </c>
+      <c r="G35" t="s">
+        <v>999</v>
+      </c>
+      <c r="H35" t="s">
+        <v>915</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B36" t="s">
+        <v>677</v>
+      </c>
+      <c r="C36" t="s">
+        <v>678</v>
+      </c>
+      <c r="D36" t="s">
+        <v>679</v>
+      </c>
+      <c r="E36" t="s">
+        <v>680</v>
+      </c>
+      <c r="F36" t="s">
+        <v>681</v>
+      </c>
+      <c r="G36" t="s">
+        <v>923</v>
+      </c>
+      <c r="H36" t="s">
+        <v>926</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
+        <v>682</v>
+      </c>
+      <c r="K36" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="B37" t="s">
+        <v>685</v>
+      </c>
+      <c r="C37" t="s">
+        <v>686</v>
+      </c>
+      <c r="D37" t="s">
+        <v>687</v>
+      </c>
+      <c r="F37" t="s">
+        <v>688</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H37" t="s">
+        <v>926</v>
+      </c>
+      <c r="I37" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="B38" t="s">
+        <v>690</v>
+      </c>
+      <c r="C38" t="s">
+        <v>691</v>
+      </c>
+      <c r="D38" t="s">
+        <v>692</v>
+      </c>
+      <c r="F38" t="s">
+        <v>693</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I38" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>45490</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>694</v>
+      </c>
+      <c r="D39" t="s">
+        <v>695</v>
+      </c>
+      <c r="E39" t="s">
+        <v>696</v>
+      </c>
+      <c r="F39" t="s">
+        <v>697</v>
+      </c>
+      <c r="G39" t="s">
+        <v>925</v>
+      </c>
+      <c r="H39" t="s">
+        <v>926</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>574</v>
+      </c>
+      <c r="K39" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>45490</v>
+      </c>
+      <c r="B40" t="s">
+        <v>698</v>
+      </c>
+      <c r="C40" t="s">
+        <v>699</v>
+      </c>
+      <c r="D40" t="s">
+        <v>700</v>
+      </c>
+      <c r="E40" t="s">
+        <v>701</v>
+      </c>
+      <c r="F40" t="s">
+        <v>702</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H40" t="s">
+        <v>924</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>45490</v>
+      </c>
+      <c r="B41" t="s">
+        <v>704</v>
+      </c>
+      <c r="C41" t="s">
+        <v>705</v>
+      </c>
+      <c r="D41" t="s">
+        <v>706</v>
+      </c>
+      <c r="E41" t="s">
+        <v>707</v>
+      </c>
+      <c r="F41" t="s">
+        <v>708</v>
+      </c>
+      <c r="G41" t="s">
+        <v>940</v>
+      </c>
+      <c r="H41" t="s">
+        <v>916</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>45490</v>
+      </c>
+      <c r="B42" t="s">
+        <v>709</v>
+      </c>
+      <c r="C42" t="s">
+        <v>710</v>
+      </c>
+      <c r="D42" t="s">
+        <v>711</v>
+      </c>
+      <c r="E42" t="s">
+        <v>712</v>
+      </c>
+      <c r="F42" t="s">
+        <v>713</v>
+      </c>
+      <c r="G42" t="s">
+        <v>915</v>
+      </c>
+      <c r="H42" t="s">
+        <v>980</v>
+      </c>
+      <c r="I42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" t="s">
+        <v>714</v>
+      </c>
+      <c r="K42" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>45492</v>
+      </c>
+      <c r="B43" t="s">
+        <v>716</v>
+      </c>
+      <c r="C43" t="s">
+        <v>717</v>
+      </c>
+      <c r="D43" t="s">
+        <v>718</v>
+      </c>
+      <c r="E43" t="s">
+        <v>719</v>
+      </c>
+      <c r="F43" t="s">
+        <v>720</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I43" t="s">
+        <v>70</v>
+      </c>
+      <c r="K43" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>45492</v>
+      </c>
+      <c r="B44" t="s">
+        <v>721</v>
+      </c>
+      <c r="C44" t="s">
+        <v>722</v>
+      </c>
+      <c r="D44" t="s">
+        <v>723</v>
+      </c>
+      <c r="E44" t="s">
+        <v>719</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I44" t="s">
+        <v>70</v>
+      </c>
+      <c r="K44" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>45498</v>
+      </c>
+      <c r="B45" t="s">
+        <v>725</v>
+      </c>
+      <c r="C45" t="s">
+        <v>726</v>
+      </c>
+      <c r="D45" t="s">
+        <v>727</v>
+      </c>
+      <c r="F45" t="s">
+        <v>728</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I45" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>45650</v>
+      </c>
+      <c r="B46" t="s">
+        <v>730</v>
+      </c>
+      <c r="C46" t="s">
+        <v>731</v>
+      </c>
+      <c r="D46" t="s">
+        <v>732</v>
+      </c>
+      <c r="E46" t="s">
+        <v>733</v>
+      </c>
+      <c r="F46" t="s">
+        <v>734</v>
+      </c>
+      <c r="G46" t="s">
+        <v>925</v>
+      </c>
+      <c r="H46" t="s">
+        <v>926</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" t="s">
+        <v>735</v>
+      </c>
+      <c r="K46" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>45632</v>
+      </c>
+      <c r="B47" t="s">
+        <v>736</v>
+      </c>
+      <c r="C47" t="s">
+        <v>737</v>
+      </c>
+      <c r="D47" t="s">
+        <v>738</v>
+      </c>
+      <c r="E47" t="s">
+        <v>739</v>
+      </c>
+      <c r="F47" t="s">
+        <v>740</v>
+      </c>
+      <c r="G47" t="s">
+        <v>925</v>
+      </c>
+      <c r="H47" t="s">
+        <v>926</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>45632</v>
+      </c>
+      <c r="B48" t="s">
+        <v>742</v>
+      </c>
+      <c r="C48" t="s">
+        <v>743</v>
+      </c>
+      <c r="D48" t="s">
+        <v>744</v>
+      </c>
+      <c r="E48" t="s">
+        <v>745</v>
+      </c>
+      <c r="F48" t="s">
+        <v>746</v>
+      </c>
+      <c r="G48" t="s">
+        <v>923</v>
+      </c>
+      <c r="H48" t="s">
+        <v>926</v>
+      </c>
+      <c r="I48" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" t="s">
+        <v>747</v>
+      </c>
+      <c r="K48" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>45632</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>749</v>
+      </c>
+      <c r="D49" t="s">
+        <v>750</v>
+      </c>
+      <c r="E49" t="s">
+        <v>751</v>
+      </c>
+      <c r="F49" t="s">
+        <v>752</v>
+      </c>
+      <c r="G49" t="s">
+        <v>962</v>
+      </c>
+      <c r="H49" t="s">
+        <v>916</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>45632</v>
+      </c>
+      <c r="B50" t="s">
+        <v>753</v>
+      </c>
+      <c r="C50" t="s">
+        <v>754</v>
+      </c>
+      <c r="D50" t="s">
+        <v>755</v>
+      </c>
+      <c r="E50" t="s">
+        <v>756</v>
+      </c>
+      <c r="F50" t="s">
+        <v>757</v>
+      </c>
+      <c r="G50" t="s">
+        <v>927</v>
+      </c>
+      <c r="H50" t="s">
+        <v>928</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>45632</v>
+      </c>
+      <c r="B51" t="s">
+        <v>758</v>
+      </c>
+      <c r="C51" t="s">
+        <v>759</v>
+      </c>
+      <c r="D51" t="s">
+        <v>760</v>
+      </c>
+      <c r="E51" t="s">
+        <v>761</v>
+      </c>
+      <c r="F51" t="s">
+        <v>762</v>
+      </c>
+      <c r="G51" t="s">
+        <v>923</v>
+      </c>
+      <c r="H51" t="s">
+        <v>915</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" t="s">
+        <v>763</v>
+      </c>
+      <c r="K51" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>45635</v>
+      </c>
+      <c r="B52" t="s">
+        <v>764</v>
+      </c>
+      <c r="C52" t="s">
+        <v>765</v>
+      </c>
+      <c r="D52" t="s">
+        <v>766</v>
+      </c>
+      <c r="E52" t="s">
+        <v>767</v>
+      </c>
+      <c r="F52" t="s">
+        <v>768</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H52" t="s">
+        <v>924</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" t="s">
+        <v>769</v>
+      </c>
+      <c r="K52" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>45635</v>
+      </c>
+      <c r="B53" t="s">
+        <v>770</v>
+      </c>
+      <c r="C53" t="s">
+        <v>771</v>
+      </c>
+      <c r="D53" t="s">
+        <v>772</v>
+      </c>
+      <c r="E53" t="s">
+        <v>773</v>
+      </c>
+      <c r="F53" t="s">
+        <v>774</v>
+      </c>
+      <c r="G53" t="s">
+        <v>915</v>
+      </c>
+      <c r="H53" t="s">
+        <v>980</v>
+      </c>
+      <c r="I53" t="s">
+        <v>51</v>
+      </c>
+      <c r="J53" t="s">
+        <v>262</v>
+      </c>
+      <c r="K53" t="s">
+        <v>530</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC4E81B-4689-40BE-BF49-7086A5EE985C}">
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="154" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>45761</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>775</v>
+      </c>
+      <c r="D2" t="s">
+        <v>776</v>
+      </c>
+      <c r="E2" t="s">
+        <v>773</v>
+      </c>
+      <c r="F2" t="s">
+        <v>777</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H2" t="s">
+        <v>915</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>45761</v>
+      </c>
+      <c r="B3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C3" t="s">
+        <v>779</v>
+      </c>
+      <c r="D3" t="s">
+        <v>780</v>
+      </c>
+      <c r="E3" t="s">
+        <v>781</v>
+      </c>
+      <c r="F3" t="s">
+        <v>782</v>
+      </c>
+      <c r="G3" t="s">
+        <v>925</v>
+      </c>
+      <c r="H3" t="s">
+        <v>926</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>783</v>
+      </c>
+      <c r="K3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>45761</v>
+      </c>
+      <c r="B4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C4" t="s">
+        <v>784</v>
+      </c>
+      <c r="D4" t="s">
+        <v>785</v>
+      </c>
+      <c r="E4" t="s">
+        <v>786</v>
+      </c>
+      <c r="F4" t="s">
+        <v>787</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H4" t="s">
+        <v>928</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B5" t="s">
+        <v>788</v>
+      </c>
+      <c r="C5" t="s">
+        <v>789</v>
+      </c>
+      <c r="D5" t="s">
+        <v>790</v>
+      </c>
+      <c r="E5" t="s">
+        <v>791</v>
+      </c>
+      <c r="F5" t="s">
+        <v>792</v>
+      </c>
+      <c r="G5" t="s">
+        <v>925</v>
+      </c>
+      <c r="H5" t="s">
+        <v>926</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>793</v>
+      </c>
+      <c r="D6" t="s">
+        <v>794</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F6" t="s">
+        <v>989</v>
+      </c>
+      <c r="G6" t="s">
+        <v>990</v>
+      </c>
+      <c r="H6" t="s">
+        <v>915</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>45761</v>
+      </c>
+      <c r="B7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C7" t="s">
+        <v>795</v>
+      </c>
+      <c r="D7" t="s">
+        <v>796</v>
+      </c>
+      <c r="E7" t="s">
+        <v>797</v>
+      </c>
+      <c r="F7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H7" t="s">
+        <v>915</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>799</v>
+      </c>
+      <c r="K7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>800</v>
+      </c>
+      <c r="D8" t="s">
+        <v>801</v>
+      </c>
+      <c r="F8" t="s">
+        <v>802</v>
+      </c>
+      <c r="G8" t="s">
+        <v>927</v>
+      </c>
+      <c r="H8" t="s">
+        <v>928</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B9" t="s">
+        <v>804</v>
+      </c>
+      <c r="C9" t="s">
+        <v>805</v>
+      </c>
+      <c r="D9" t="s">
+        <v>806</v>
+      </c>
+      <c r="E9" t="s">
+        <v>807</v>
+      </c>
+      <c r="F9" t="s">
+        <v>808</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B10" t="s">
+        <v>809</v>
+      </c>
+      <c r="C10" t="s">
+        <v>810</v>
+      </c>
+      <c r="D10" t="s">
+        <v>811</v>
+      </c>
+      <c r="E10" t="s">
+        <v>812</v>
+      </c>
+      <c r="F10" t="s">
+        <v>813</v>
+      </c>
+      <c r="G10" t="s">
+        <v>978</v>
+      </c>
+      <c r="H10" t="s">
+        <v>926</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B11" t="s">
+        <v>814</v>
+      </c>
+      <c r="C11" t="s">
+        <v>815</v>
+      </c>
+      <c r="D11" t="s">
+        <v>816</v>
+      </c>
+      <c r="E11" t="s">
+        <v>719</v>
+      </c>
+      <c r="F11" t="s">
+        <v>817</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H11" t="s">
+        <v>921</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B12" t="s">
+        <v>819</v>
+      </c>
+      <c r="C12" t="s">
+        <v>820</v>
+      </c>
+      <c r="D12" t="s">
+        <v>821</v>
+      </c>
+      <c r="E12" t="s">
+        <v>822</v>
+      </c>
+      <c r="F12" t="s">
+        <v>823</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H12" t="s">
+        <v>918</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B13" t="s">
+        <v>824</v>
+      </c>
+      <c r="C13" t="s">
+        <v>825</v>
+      </c>
+      <c r="D13" t="s">
+        <v>826</v>
+      </c>
+      <c r="E13" t="s">
+        <v>827</v>
+      </c>
+      <c r="F13" t="s">
+        <v>828</v>
+      </c>
+      <c r="G13" t="s">
+        <v>981</v>
+      </c>
+      <c r="H13" t="s">
+        <v>980</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B14" t="s">
+        <v>539</v>
+      </c>
+      <c r="C14" t="s">
+        <v>829</v>
+      </c>
+      <c r="D14" t="s">
+        <v>830</v>
+      </c>
+      <c r="E14" t="s">
+        <v>831</v>
+      </c>
+      <c r="F14" t="s">
+        <v>832</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H14" t="s">
+        <v>938</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" t="s">
+        <v>833</v>
+      </c>
+      <c r="K14" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B15" t="s">
+        <v>835</v>
+      </c>
+      <c r="C15" t="s">
+        <v>836</v>
+      </c>
+      <c r="D15" t="s">
+        <v>837</v>
+      </c>
+      <c r="E15" t="s">
+        <v>838</v>
+      </c>
+      <c r="F15" t="s">
+        <v>839</v>
+      </c>
+      <c r="G15" t="s">
+        <v>919</v>
+      </c>
+      <c r="H15" t="s">
+        <v>919</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>840</v>
+      </c>
+      <c r="D16" t="s">
+        <v>841</v>
+      </c>
+      <c r="E16" t="s">
+        <v>842</v>
+      </c>
+      <c r="F16" t="s">
+        <v>843</v>
+      </c>
+      <c r="G16" t="s">
+        <v>925</v>
+      </c>
+      <c r="H16" t="s">
+        <v>926</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B17" t="s">
+        <v>844</v>
+      </c>
+      <c r="C17" t="s">
+        <v>845</v>
+      </c>
+      <c r="D17" t="s">
+        <v>846</v>
+      </c>
+      <c r="E17" t="s">
+        <v>847</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G17" t="s">
+        <v>946</v>
+      </c>
+      <c r="H17" t="s">
+        <v>947</v>
+      </c>
+      <c r="I17" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" t="s">
+        <v>848</v>
+      </c>
+      <c r="K17" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B18" t="s">
+        <v>849</v>
+      </c>
+      <c r="C18" t="s">
+        <v>850</v>
+      </c>
+      <c r="D18" t="s">
+        <v>851</v>
+      </c>
+      <c r="E18" t="s">
+        <v>852</v>
+      </c>
+      <c r="F18" t="s">
+        <v>853</v>
+      </c>
+      <c r="G18" t="s">
+        <v>923</v>
+      </c>
+      <c r="H18" t="s">
+        <v>926</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>854</v>
+      </c>
+      <c r="K18" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B19" t="s">
+        <v>855</v>
+      </c>
+      <c r="C19" t="s">
+        <v>856</v>
+      </c>
+      <c r="D19" t="s">
+        <v>857</v>
+      </c>
+      <c r="E19" t="s">
+        <v>858</v>
+      </c>
+      <c r="F19" t="s">
+        <v>859</v>
+      </c>
+      <c r="G19" t="s">
+        <v>923</v>
+      </c>
+      <c r="H19" t="s">
+        <v>926</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>860</v>
+      </c>
+      <c r="K19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B20" t="s">
+        <v>861</v>
+      </c>
+      <c r="C20" t="s">
+        <v>862</v>
+      </c>
+      <c r="D20" t="s">
+        <v>863</v>
+      </c>
+      <c r="E20" t="s">
+        <v>864</v>
+      </c>
+      <c r="F20" t="s">
+        <v>865</v>
+      </c>
+      <c r="G20" t="s">
+        <v>927</v>
+      </c>
+      <c r="H20" t="s">
+        <v>928</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B21" t="s">
+        <v>866</v>
+      </c>
+      <c r="C21" t="s">
+        <v>867</v>
+      </c>
+      <c r="D21" t="s">
+        <v>868</v>
+      </c>
+      <c r="E21" t="s">
+        <v>869</v>
+      </c>
+      <c r="F21" t="s">
+        <v>870</v>
+      </c>
+      <c r="G21" t="s">
+        <v>953</v>
+      </c>
+      <c r="H21" t="s">
+        <v>940</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B22" t="s">
+        <v>872</v>
+      </c>
+      <c r="C22" t="s">
+        <v>873</v>
+      </c>
+      <c r="D22" t="s">
+        <v>874</v>
+      </c>
+      <c r="E22" t="s">
+        <v>875</v>
+      </c>
+      <c r="F22" t="s">
+        <v>876</v>
+      </c>
+      <c r="G22" t="s">
+        <v>927</v>
+      </c>
+      <c r="H22" t="s">
+        <v>928</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B23" t="s">
+        <v>877</v>
+      </c>
+      <c r="C23" t="s">
+        <v>878</v>
+      </c>
+      <c r="D23" t="s">
+        <v>879</v>
+      </c>
+      <c r="E23" t="s">
+        <v>880</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B24" t="s">
+        <v>881</v>
+      </c>
+      <c r="C24" t="s">
+        <v>882</v>
+      </c>
+      <c r="D24" t="s">
+        <v>883</v>
+      </c>
+      <c r="E24" t="s">
+        <v>786</v>
+      </c>
+      <c r="F24" t="s">
+        <v>884</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H24" t="s">
+        <v>918</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" t="s">
+        <v>885</v>
+      </c>
+      <c r="K24" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B25" t="s">
+        <v>887</v>
+      </c>
+      <c r="C25" t="s">
+        <v>888</v>
+      </c>
+      <c r="D25" t="s">
+        <v>889</v>
+      </c>
+      <c r="E25" t="s">
+        <v>890</v>
+      </c>
+      <c r="F25" t="s">
+        <v>891</v>
+      </c>
+      <c r="G25" t="s">
+        <v>944</v>
+      </c>
+      <c r="H25" t="s">
+        <v>944</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" t="s">
+        <v>848</v>
+      </c>
+      <c r="K25" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B26" t="s">
+        <v>892</v>
+      </c>
+      <c r="C26" t="s">
+        <v>893</v>
+      </c>
+      <c r="D26" t="s">
+        <v>894</v>
+      </c>
+      <c r="F26" t="s">
+        <v>895</v>
+      </c>
+      <c r="G26" t="s">
+        <v>915</v>
+      </c>
+      <c r="H26" t="s">
+        <v>980</v>
+      </c>
+      <c r="I26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" t="s">
+        <v>848</v>
+      </c>
+      <c r="K26" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>45763</v>
+      </c>
+      <c r="B27" t="s">
+        <v>896</v>
+      </c>
+      <c r="C27" t="s">
+        <v>897</v>
+      </c>
+      <c r="D27" t="s">
+        <v>898</v>
+      </c>
+      <c r="E27" t="s">
+        <v>899</v>
+      </c>
+      <c r="F27" t="s">
+        <v>900</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>45764</v>
+      </c>
+      <c r="B28" t="s">
+        <v>902</v>
+      </c>
+      <c r="C28" t="s">
+        <v>903</v>
+      </c>
+      <c r="D28" t="s">
+        <v>904</v>
+      </c>
+      <c r="F28" t="s">
+        <v>905</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I28" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>45764</v>
+      </c>
+      <c r="B29" t="s">
+        <v>906</v>
+      </c>
+      <c r="C29" t="s">
+        <v>907</v>
+      </c>
+      <c r="D29" t="s">
+        <v>908</v>
+      </c>
+      <c r="E29" t="s">
+        <v>909</v>
+      </c>
+      <c r="F29" t="s">
+        <v>910</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H29" t="s">
+        <v>926</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s">
+        <v>911</v>
+      </c>
+      <c r="K29" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/bd1-1.xlsx
+++ b/bd1-1.xlsx
@@ -11580,7 +11580,7 @@
         <v>974</v>
       </c>
       <c r="H75" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="I75" t="s">
         <v>51</v>
@@ -12344,7 +12344,7 @@
         <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>17</v>
+        <v>926</v>
       </c>
       <c r="I100" t="s">
         <v>17</v>
@@ -12373,7 +12373,7 @@
         <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>17</v>
+        <v>926</v>
       </c>
       <c r="I101" t="s">
         <v>17</v>
@@ -12405,7 +12405,7 @@
         <v>17</v>
       </c>
       <c r="H102" t="s">
-        <v>17</v>
+        <v>926</v>
       </c>
       <c r="I102" t="s">
         <v>17</v>
